--- a/output_with_coordinates.xlsx
+++ b/output_with_coordinates.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,102 +417,102 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>S.No</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Property ID</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Land Area</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Curation</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>QUOTED PRICE</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>GOOGLE MAP</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Location</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Sub -Location</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>MEDIATOR / LANDLORD</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>NAME OF THE MEDIATOR / LANDLORD</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>SOURCE NAME</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>CONTACT NUMBER</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>CLASSIFICATION</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Jayapalan Sir's Comment</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Remarks</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>PPT Link</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Expanded_URL</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Latitude</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Longitude</t>
         </is>
@@ -656,8 +644,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/11%25C2%25B003%2731.3%2522N%2B77%25C2%25B002%2716.8%2522E/%4011.058699,77.037994,855m/data%3D!3m2!1e3!4b1!4m4!3m3!8m2!3d11.058699!4d77.037994%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MDMzMC4wIPu8ASoASAFQAw%253D%253D%26skid%3Df64db591-3af6-4af9-8458-91b844db54dc&amp;q=EhAkBQIB4C7guzR74cqdAFF6GMrKy88GIjBnlai_S_CZyy4GEzVclu2HPFO2udqcdGuwtnDxNppeYqcST63gyBRkjv1IiAq6KW4yAnJSWgFD</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr"/>
-      <c r="T3" t="inlineStr"/>
+      <c r="S3" t="n">
+        <v>11.058699</v>
+      </c>
+      <c r="T3" t="n">
+        <v>77.037994</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -716,8 +708,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/11%25C2%25B001%2702.7%2522N%2B77%25C2%25B005%2735.8%2522E/%4011.017408,77.093281,855m/data%3D!3m2!1e3!4b1!4m4!3m3!8m2!3d11.017408!4d77.093281%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MDMzMC4wIPu8ASoASAFQAw%253D%253D%26skid%3D51867af0-4b0a-47d7-9cdc-82cef79ce478&amp;q=EhAkBQIB4C7guzR74cqdAFF6GMzKy88GIjByBK_nGus_xZNf7RBPjvaZ2fZpRjJImuu3VGCNGI--5q8wZMpKQ-a0evT0ez26cnMyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr"/>
-      <c r="T4" t="inlineStr"/>
+      <c r="S4" t="n">
+        <v>11.017408</v>
+      </c>
+      <c r="T4" t="n">
+        <v>77.093281</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -781,8 +777,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/11%25C2%25B004%2757.4%2522N%2B76%25C2%25B059%2709.7%2522E/%4011.0814477,76.9851373,1709m/data%3D!3m1!1e3!4m4!3m3!8m2!3d11.0826111!4d76.9860278!5m1!1e4%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MDMzMC4wIPu8ASoASAFQAw%253D%253D%26skid%3Da983116c-90be-449d-8e0c-4cfb0f2dfafd&amp;q=EhAkBQIB4C7guzR74cqdAFF6GM7Ky88GIjCL3L6cwOJ7iiUy4CG50mFvnwXktHn3YcrqB8mw8Ry94P4NExrBCibS8PWodFFriZQyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr"/>
-      <c r="T5" t="inlineStr"/>
+      <c r="S5" t="n">
+        <v>11.0814477</v>
+      </c>
+      <c r="T5" t="n">
+        <v>76.98513730000001</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -841,8 +841,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/10%25C2%25B052%2748.4%2522N%2B77%25C2%25B000%2709.7%2522E/%4010.880116,77.0001301,855m/data%3D!3m2!1e3!4b1!4m4!3m3!8m2!3d10.880116!4d77.002705%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MDMzMC4wIPu8ASoASAFQAw%253D%253D%26skid%3Df1206ec9-ebef-405c-bb51-1f792ab0e8d1&amp;q=EhAkBQIB4C7guzR74cqdAFF6GM_Ky88GIjCkpJVggoaKjWYuZJ2V5EgEL20RjRxzPprKAfoRXbGym4VFwd14rvtVzIZbM4N6IwkyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr"/>
-      <c r="T6" t="inlineStr"/>
+      <c r="S6" t="n">
+        <v>10.880116</v>
+      </c>
+      <c r="T6" t="n">
+        <v>77.00013010000001</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -905,8 +909,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/Mahendra%2BPumps%2BPrivate%2BLimited%2B(Unit-2)/%4011.0115049,76.991918,427m/data%3D!3m1!1e3!4m6!3m5!1s0x3ba859cba6889019:0xf93270343ffc7168!8m2!3d11.0114573!4d76.9915299!16s%252Fg%252F11gfn83mww%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MDMzMC4wIPu8ASoASAFQAw%253D%253D%26skid%3D410903d8-fbcd-42a5-afb7-6297c1562630&amp;q=EhAkBQIB4C7guzR74cqdAFF6GNDKy88GIjAoOHWTTXkYzpb9sNr3qXRmeYdlvAkDdgxdSGjLsVoes9Wn7XYWqKBpROmES1xf77UyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr"/>
-      <c r="T7" t="inlineStr"/>
+      <c r="S7" t="n">
+        <v>11.0115049</v>
+      </c>
+      <c r="T7" t="n">
+        <v>76.991918</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -957,8 +965,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/11%25C2%25B001%2736.4%2522N%2B76%25C2%25B056%2758.0%2522E/%4011.0267172,76.9494312,107m/data%3D!3m1!1e3!4m4!3m3!8m2!3d11.0267778!4d76.9494444%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MDMzMC4wIPu8ASoASAFQAw%253D%253D%26skid%3D3d6a2e15-7b33-49a3-abd7-847ad86941a6&amp;q=EhAkBQIB4C7guzR74cqdAFF6GNHKy88GIjA6LAsXrKGhl2EYzIdvGLLpeUBAtMLAC2OVimB5ncqYHCTxKJ7FixV6QPQhA6k2POkyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr"/>
-      <c r="T8" t="inlineStr"/>
+      <c r="S8" t="n">
+        <v>11.0267172</v>
+      </c>
+      <c r="T8" t="n">
+        <v>76.94943120000001</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1027,8 +1039,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/11%25C2%25B000%2747.8%2522N%2B76%25C2%25B054%2716.5%2522E/%4011.013271,76.904578,855m/data%3D!3m2!1e3!4b1!4m4!3m3!8m2!3d11.013271!4d76.904578%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MDMzMC4wIPu8ASoASAFQAw%253D%253D%26skid%3D82facfcb-6715-42d4-90cc-135d56ed5c03&amp;q=EhAkBQIB4C7guzR74cqdAFF6GNPKy88GIjBW6Ex76mWI8kB1prdTcqZII_SYe4uuMfo7dNhMyXOk96qqN558Lv03HzNd1ZybW00yAnJSWgFD</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr"/>
-      <c r="T9" t="inlineStr"/>
+      <c r="S9" t="n">
+        <v>11.013271</v>
+      </c>
+      <c r="T9" t="n">
+        <v>76.904578</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1093,8 +1109,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/11%25C2%25B002%2711.3%2522N%2B76%25C2%25B056%2730.9%2522E/%4011.0364716,76.9234626,2679m/data%3D!3m2!1e3!4b1!4m4!3m3!8m2!3d11.0364722!4d76.9419167%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MDgxMy4wIPu8ASoASAFQAw%253D%253D%26skid%3D34e2b37d-eb8b-40ce-b36b-7cc8bcffe23c&amp;q=EhAkBQIB4C7guzR74cqdAFF6GNTKy88GIjAJy2IMeEQ86kKPdfv2U7xQB6VznIG1QypSi8nuI2_Sd9L2RMfgKM9MefLBkfQmPEgyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr"/>
-      <c r="T10" t="inlineStr"/>
+      <c r="S10" t="n">
+        <v>11.0364716</v>
+      </c>
+      <c r="T10" t="n">
+        <v>76.92346259999999</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1161,8 +1181,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/Point%2BIndustries,%2BS.F%2BNo.%2B330%252F2B2-1,%2BPoint%2BAarcade,%2BSharp%2BNagar,%2BKalapatti,%2BTamil%2BNadu%2B641048/data%3D!4m6!3m5!1s0x3ba8579d73aaad17:0xf2ab9fc1b535452a!7e2!8m2!3d11.0587629!4d77.0379621%3Futm_source%3Dmstt_1%26entry%3Dgps%26coh%3D192189%26g_ep%3DCAESCjExLjE1NS4xMDEYACCIJyqHASw5NDI0MjUzOCw5NDIyMzI5OSw5NDIxNjQxMyw5NDIxMjQ5Niw5NDIxMjY2NSw5NDIwNzM5NCw5NDIwNzUwNiw5NDIwODUwNiw5NDIxNzUyMyw5NDIxODY1Myw5NDIyOTgzOSw5NDIzOTEyMSw0NzA4NzExOCw0NzA4NDM5Myw5NDIxMzIwMEICSU4%253D&amp;q=EhAkBQIB4C7guzR74cqdAFF6GNXKy88GIjB3-sBqC0glNbhoC4rZExLLoVg1-k1BRNj5IGplkJWEGCEu9sIUxM5YoInI9LuWynEyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr"/>
-      <c r="T11" t="inlineStr"/>
+      <c r="S11" t="n">
+        <v>11.0587629</v>
+      </c>
+      <c r="T11" t="n">
+        <v>77.0379621</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1225,8 +1249,12 @@
           <t>https://www.google.com/sorry/index?continue=https://maps.google.com/%3Fq%3D11.064763,77.035348%26entry%3Dgps%26g_ep%3DCAESCjExLjE1NS4xMDEYACDXggMqhwEsOTQyNDI1MzgsOTQyMjMyOTksOTQyMTY0MTMsOTQyMTI0OTYsOTQyMTI2NjUsOTQyMDczOTQsOTQyMDc1MDYsOTQyMDg1MDYsOTQyMTc1MjMsOTQyMTg2NTMsOTQyMjk4MzksOTQyMzkxMjEsNDcwODcxMTgsNDcwODQzOTMsOTQyMTMyMDBCAklO%26shorturl%3D1&amp;q=EhAkBQIB4C7guzR74cqdAFF6GNbKy88GIi0XsnzcKF6CyJD8h69aYIAJmHNzt7YPDtcDETcYjEqbXoc6mlCAESc6iKJf_-EyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr"/>
-      <c r="T12" t="inlineStr"/>
+      <c r="S12" t="n">
+        <v>11.064763</v>
+      </c>
+      <c r="T12" t="n">
+        <v>77.035348</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1289,8 +1317,12 @@
           <t>https://www.google.com/sorry/index?continue=https://maps.google.com/%3Fq%3D11.063025,77.045583%26entry%3Dgps%26g_ep%3DCAESCjExLjE1NS4xMDEYACCIJyqHASw5NDI0MjUzOCw5NDIyMzI5OSw5NDIxNjQxMyw5NDIxMjQ5Niw5NDIxMjY2NSw5NDIwNzM5NCw5NDIwNzUwNiw5NDIwODUwNiw5NDIxNzUyMyw5NDIxODY1Myw5NDIyOTgzOSw5NDIzOTEyMSw0NzA4NzExOCw0NzA4NDM5Myw5NDIxMzIwMEICSU4%253D%26shorturl%3D1&amp;q=EhAkBQIB4C7guzR74cqdAFF6GNnKy88GIi3-Axqkr-d7KcY0pTv39CIhSt8G4FYkyA1elnZZyCG55Sa1ft7jo8osYWoejFIyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S13" t="inlineStr"/>
-      <c r="T13" t="inlineStr"/>
+      <c r="S13" t="n">
+        <v>11.063025</v>
+      </c>
+      <c r="T13" t="n">
+        <v>77.04558299999999</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1357,8 +1389,12 @@
           <t>https://www.google.com/sorry/index?continue=https://maps.google.com/%3Fq%3D11.050319,77.038504%26entry%3Dgps%26g_ep%3DCAESCjExLjE1NS4xMDEYACCIJyqHASw5NDI0MjUzOCw5NDIyMzI5OSw5NDIxNjQxMyw5NDIxMjQ5Niw5NDIxMjY2NSw5NDIwNzM5NCw5NDIwNzUwNiw5NDIwODUwNiw5NDIxNzUyMyw5NDIxODY1Myw5NDIyOTgzOSw5NDIzOTEyMSw0NzA4NzExOCw0NzA4NDM5Myw5NDIxMzIwMEICSU4%253D%26shorturl%3D1&amp;q=EhAkBQIB4C7guzR74cqdAFF6GNrKy88GIi3ifOwI1ahbY2UqcFJ6y5oAT_Q0RfGjGGJUEpPLMYFlfllyKAqSgXTpoYD_z9AyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S14" t="inlineStr"/>
-      <c r="T14" t="inlineStr"/>
+      <c r="S14" t="n">
+        <v>11.050319</v>
+      </c>
+      <c r="T14" t="n">
+        <v>77.038504</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -1613,8 +1649,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/11.011268,76.867644/data%3D!4m6!3m5!1s0!7e2!8m2!3d11.0112679!4d76.8676442%3Futm_source%3Dmstt_1%26entry%3Dgps%26coh%3D192189%26g_ep%3DCAESBzI1LjE2LjYYACDl7Q0qbCw5NDIyMzI5OSw5NDIxNjQxMyw5NDIxMjQ5Niw5NDIwNzM5NCw5NDIwNzUwNiw5NDIwODUwNiw5NDIxNzUyMyw5NDIxODY1Myw5NDIyOTgzOSw0NzA4NDM5Myw5NDIxMzIwMCw5NDI1ODMyNUICSU4%253D%26skid%3Dcfdd6fa6-150f-4630-bd82-09bc9dd0f614%26g_st%3Daw&amp;q=EhAkBQIB4C7guzR74cqdAFF6GN_Ky88GIjDtpWeOtCeCRE5bFVuOMwO6WIWcVFNU9hijT0HGgxOlKweg0TZCTWa6PtMu0ho7DwoyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S18" t="inlineStr"/>
-      <c r="T18" t="inlineStr"/>
+      <c r="S18" t="n">
+        <v>11.0112679</v>
+      </c>
+      <c r="T18" t="n">
+        <v>76.8676442</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -1683,8 +1723,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/Masagoundenchettipalayam,%2BTamil%2BNadu%2B641107/data%3D!4m6!3m5!1s0x3ba8f97910f3f4f9:0xc3407b6f07854c18!7e2!8m2!3d11.1431831!4d77.06008729999999%3Futm_source%3Dmstt_1%26entry%3Dgps%26coh%3D192189%26g_ep%3DCAESBzI1LjI1LjAYACDXggMqfiw5NDI3NTQwNyw5NDIyMzI5OSw5NDIxNjQxMyw5NDIxMjQ5Niw5NDIwNzM5NCw5NDIwNzUwNiw5NDIwODUwNiw5NDIxNzUyMyw5NDIxODY1Myw5NDIyOTgzOSw5NDI3NTE2OCw0NzA4NDM5Myw5NDIxMzIwMCw5NDI1ODMyNUICSU4%253D%26skid%3D762698e9-9710-4948-8001-d9b98cd5d3cc%26g_st%3Daw&amp;q=EhAkBQIB4C7guzR74cqdAFF6GODKy88GIjA0WHn_RBaGS-iWWJMkWgYVd9QQ7rxrYnvfmVBwSfS5w5FZqCZoVKPWdNpPycUIf-8yAnJSWgFD</t>
         </is>
       </c>
-      <c r="S19" t="inlineStr"/>
-      <c r="T19" t="inlineStr"/>
+      <c r="S19" t="n">
+        <v>11.1431831</v>
+      </c>
+      <c r="T19" t="n">
+        <v>77.06008729999999</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -1753,8 +1797,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/10%25C2%25B058%2733.1%2522N%2B76%25C2%25B048%2751.3%2522E/%4010.9758588,76.8112355,813m/data%3D!3m1!1e3!4m4!3m3!8m2!3d10.9758538!4d76.8142459%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MDcxNS4xIPu8ASoASAFQAw%253D%253D%26skid%3Dc521bfa7-8d36-48d4-bbbe-4a3e2ae9b6ad&amp;q=EhAkBQIB4C7guzR74cqdAFF6GOLKy88GIjCFZNG7qOTdiNKuWGDgV2xURaFPtjHCwXIDw2OqbrCPrqsJU0p-Mln1Nv389kAKDvwyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S20" t="inlineStr"/>
-      <c r="T20" t="inlineStr"/>
+      <c r="S20" t="n">
+        <v>10.9758588</v>
+      </c>
+      <c r="T20" t="n">
+        <v>76.8112355</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -1823,8 +1871,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/11%25C2%25B006%2738.7%2522N%2B77%25C2%25B008%2725.9%2522E/%4011.1107471,77.1379466,739m/data%3D!3m2!1e3!4b1!4m4!3m3!8m2!3d11.1107471!4d77.1405215%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MDcxMy4wIPu8ASoASAFQAw%253D%253D%26skid%3Dde5773cc-ce7b-45e9-b7c2-8ae92647e12c&amp;q=EhAkBQIB4C7guzR74cqdAFF6GOPKy88GIjDszsdsXO95AsxXeNCbzDv7twF7_olctPLUbMaVZXU6-kIcH4BUC51kQHbQZQkAjzAyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S21" t="inlineStr"/>
-      <c r="T21" t="inlineStr"/>
+      <c r="S21" t="n">
+        <v>11.1107471</v>
+      </c>
+      <c r="T21" t="n">
+        <v>77.13794660000001</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -1891,8 +1943,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/11%25C2%25B005%2701.0%2522N%2B76%25C2%25B058%2710.0%2522E/%4011.0836062,76.9668641,739m/data%3D!3m2!1e3!4b1!4m4!3m3!8m2!3d11.0836062!4d76.969439%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MDcxNS4xIPu8ASoASAFQAw%253D%253D%26skid%3D63ecb06c-892d-43a9-bdc7-2792e982f17d&amp;q=EhAkBQIB4C7guzR74cqdAFF6GOXKy88GIjANUW6yg-5773D7k42UhERjJk9kDCCRpDEP4lAQAwGOH9R4MjA_kEGqi7myUUXr2-kyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S22" t="inlineStr"/>
-      <c r="T22" t="inlineStr"/>
+      <c r="S22" t="n">
+        <v>11.0836062</v>
+      </c>
+      <c r="T22" t="n">
+        <v>76.9668641</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -1961,8 +2017,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/11%25C2%25B000%2736.6%2522N%2B76%25C2%25B049%2716.4%2522E/%4011.0101757,76.8186531,813m/data%3D!3m1!1e3!4m4!3m3!8m2!3d11.0101757!4d76.821228%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MDcxMy4wIPu8ASoASAFQAw%253D%253D%26skid%3Df5a1f479-6202-4cd4-a286-d8c9554eb23b&amp;q=EhAkBQIB4C7guzR74cqdAFF6GOfKy88GIjClTbpT1lj0L7qcWuJSuXF8yT7mPNd9jebmQlWoNJ49AUhJEm8ccMTyaant7bKChwAyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S23" t="inlineStr"/>
-      <c r="T23" t="inlineStr"/>
+      <c r="S23" t="n">
+        <v>11.0101757</v>
+      </c>
+      <c r="T23" t="n">
+        <v>76.81865310000001</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2027,8 +2087,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/11%25C2%25B005%2723.7%2522N%2B77%25C2%25B005%2704.0%2522E/%4011.0899243,77.08187,739m/data%3D!3m2!1e3!4b1!4m4!3m3!8m2!3d11.0899243!4d77.0844449%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MDcxNS4xIPu8ASoASAFQAw%253D%253D%26skid%3Def775e88-e896-46a9-8066-1e8bacfb4256&amp;q=EhAkBQIB4C7guzR74cqdAFF6GOjKy88GIjDzL8FaU_w8_ZnLOc-_YjzFdWypXs-LDc4QfXAdsrAR3Dt4fjF5_bmX_RkLXoAiNDwyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S24" t="inlineStr"/>
-      <c r="T24" t="inlineStr"/>
+      <c r="S24" t="n">
+        <v>11.0899243</v>
+      </c>
+      <c r="T24" t="n">
+        <v>77.08187</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -2097,8 +2161,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/11%25C2%25B006%2706.5%2522N%2B77%25C2%25B007%2747.2%2522E/%4011.1018051,77.1271888,812m/data%3D!3m2!1e3!4b1!4m4!3m3!8m2!3d11.1018051!4d77.1297637%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MDcxMy4wIPu8ASoASAFQAw%253D%253D%26skid%3D00310b3f-daca-425c-b75e-47dba21e1086&amp;q=EhAkBQIB4C7guzR74cqdAFF6GOnKy88GIjDnkre2JP3b2hCHSshd12byaVU9jpTTCsP02RvocMjAb-XqA0M6lk18U1h3I42MMqIyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S25" t="inlineStr"/>
-      <c r="T25" t="inlineStr"/>
+      <c r="S25" t="n">
+        <v>11.1018051</v>
+      </c>
+      <c r="T25" t="n">
+        <v>77.1271888</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -2163,8 +2231,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/11%25C2%25B006%2739.5%2522N%2B77%25C2%25B011%2714.2%2522E/%4011.113728,77.1807237,1625m/data%3D!3m1!1e3!4m4!3m3!8m2!3d11.1109803!4d77.1872737%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MDcxNS4xIPu8ASoASAFQAw%253D%253D%26skid%3Dad342eef-715c-49a9-b63f-2037d562ae6d&amp;q=EhAkBQIB4C7guzR74cqdAFF6GOrKy88GIjABhmEXB_NTiaptXsEzpw_AtYK8xtK0NFPDznbaiMWqvg4N514aL5g2Sb3LA8jmsaEyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S26" t="inlineStr"/>
-      <c r="T26" t="inlineStr"/>
+      <c r="S26" t="n">
+        <v>11.113728</v>
+      </c>
+      <c r="T26" t="n">
+        <v>77.1807237</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -2299,8 +2371,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/11.103215,76.996410/data%3D!4m6!3m5!1s0!7e2!8m2!3d11.1032146!4d76.99640959999999%3Futm_source%3Dmstt_1%26entry%3Dgps%26coh%3D192189%26g_ep%3DCAESBjI1LjguMRgAIPrsDSp-LDk0MjU1NDQ3LDk0MjQyNTc0LDk0MjIzMjk5LDk0MjE2NDEzLDk0MjEyNDk2LDk0MjA3Mzk0LDk0MjA3NTA2LDk0MjA4NTA2LDk0MjE3NTIzLDk0MjE4NjUzLDk0MjI5ODM5LDQ3MDg0MzkzLDk0MjEzMjAwLDk0MjU4MzI1QgJJTg%253D%253D%26skid%3Dd379d75d-a801-44f3-a6b5-4c1a49ba9421%26g_st%3Daw&amp;q=EhAkBQIB4C7guzR74cqdAFF6GOzKy88GIjASrExDKD7w478FkwuD23woKZthgsaDOByN09sNh8StmJE3OZOJY0hpPBeHziPb6ocyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S28" t="inlineStr"/>
-      <c r="T28" t="inlineStr"/>
+      <c r="S28" t="n">
+        <v>11.1032146</v>
+      </c>
+      <c r="T28" t="n">
+        <v>76.99640959999999</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -2369,8 +2445,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/10%25C2%25B052%2712.0%2522N%2B76%25C2%25B056%2708.3%2522E/%4010.8700113,76.9330566,739m/data%3D!3m2!1e3!4b1!4m4!3m3!8m2!3d10.8700113!4d76.9356315%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MDcxMy4wIPu8ASoASAFQAw%253D%253D%26skid%3Dc5c00e3d-c38e-4ef0-a6de-12a79a04550b&amp;q=EhAkBQIB4C7guzR74cqdAFF6GO3Ky88GIjABORHKCgY5KkknqvCLrm2gitp8qx5NHkq1UtQz84WEuH1RXE2ob9pV-lQPO5Lv2bIyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S29" t="inlineStr"/>
-      <c r="T29" t="inlineStr"/>
+      <c r="S29" t="n">
+        <v>10.8700113</v>
+      </c>
+      <c r="T29" t="n">
+        <v>76.9330566</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -2439,8 +2519,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/10%25C2%25B030%2706.3%2522N%2B77%25C2%25B033%2741.5%2522E/%4010.5017581,77.5589532,814m/data%3D!3m2!1e3!4b1!4m4!3m3!8m2!3d10.5017581!4d77.5615281%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MDcxNS4xIPu8ASoASAFQAw%253D%253D%26skid%3D84e5da05-0acf-415b-8339-a0555c85e0b1&amp;q=EhAkBQIB4C7guzR74cqdAFF6GO_Ky88GIjB4DYcPO_HyRZ9PBKUGF1x3AyrCW3TbmVUVrUS6iyBmtf7wXQMcm1qZQZjhmlJmajsyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S30" t="inlineStr"/>
-      <c r="T30" t="inlineStr"/>
+      <c r="S30" t="n">
+        <v>10.5017581</v>
+      </c>
+      <c r="T30" t="n">
+        <v>77.5589532</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -2509,8 +2593,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/11%25C2%25B008%2754.4%2522N%2B77%25C2%25B002%2710.8%2522E/%4011.1484298,77.0337533,739m/data%3D!3m1!1e3!4m4!3m3!8m2!3d11.1484298!4d77.0363282%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MDcxNS4xIPu8ASoASAFQAw%253D%253D%26skid%3Df46a277a-2d4e-4aa7-a04f-b1f2737a163e&amp;q=EhAkBQIB4C7guzR74cqdAFF6GPDKy88GIjDLD4fvLHBRnu-9Od9enCjlnwcRupPLlQ-auAuMxXpGmx5HOl7Jqi1DQAsjTAQR7_gyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S31" t="inlineStr"/>
-      <c r="T31" t="inlineStr"/>
+      <c r="S31" t="n">
+        <v>11.1484298</v>
+      </c>
+      <c r="T31" t="n">
+        <v>77.0337533</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -2580,8 +2668,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/10%25C2%25B052%2745.1%2522N%2B76%25C2%25B055%2727.6%2522E/%4010.8791937,76.9217493,739m/data%3D!3m1!1e3!4m4!3m3!8m2!3d10.8791937!4d76.9243242%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MDcxNS4xIPu8ASoASAFQAw%253D%253D%26skid%3Dfdf830d0-906d-45b1-a5d6-2b3b8fdf66cc&amp;q=EhAkBQIB4C7guzR74cqdAFF6GPHKy88GIjC3OtmSjOjGVtupqDg3xOJv8UvmqL3jxRq6cGFEepIx0TvcZXWzGweTYMq-OuBKPK0yAnJSWgFD</t>
         </is>
       </c>
-      <c r="S32" t="inlineStr"/>
-      <c r="T32" t="inlineStr"/>
+      <c r="S32" t="n">
+        <v>10.8791937</v>
+      </c>
+      <c r="T32" t="n">
+        <v>76.9217493</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -2650,8 +2742,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/Cheenu%2BAmma%2BAalloy%2B(P)%2BLtd/%4010.9571791,77.1264802,620m/data%3D!3m1!1e3!4m6!3m5!1s0x3ba853943680522b:0x1ab162ed504c6843!8m2!3d10.957629!4d77.13001!16s%252Fg%252F12cpng1q0%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MDcxNS4xIPu8ASoASAFQAw%253D%253D%26skid%3D12f2e448-75b2-4c63-bd34-dffd489f68c4&amp;q=EhAkBQIB4C7guzR74cqdAFF6GPPKy88GIjBymZPtUlpQzutyeorr_Ch4O7rG5iHPt8NeoEL21djKBoPc7cA0gpEtIPwTjQSGY_EyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S33" t="inlineStr"/>
-      <c r="T33" t="inlineStr"/>
+      <c r="S33" t="n">
+        <v>10.9571791</v>
+      </c>
+      <c r="T33" t="n">
+        <v>77.1264802</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -2720,8 +2816,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/11%25C2%25B009%2707.2%2522N%2B76%25C2%25B058%2742.0%2522E/%4011.1520011,76.9757496,812m/data%3D!3m2!1e3!4b1!4m4!3m3!8m2!3d11.1520011!4d76.9783245%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MDcxNS4xIPu8ASoASAFQAw%253D%253D%26skid%3D90f66ff3-b32f-456a-bb55-e1853269a7d2&amp;q=EhAkBQIB4C7guzR74cqdAFF6GPXKy88GIjAugeT-Ff8jqMFTK9CrbnBVuXHvJ34aKu5wLP46vi7P8UgrC15Hdz_5xF-R02-8H7AyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S34" t="inlineStr"/>
-      <c r="T34" t="inlineStr"/>
+      <c r="S34" t="n">
+        <v>11.1520011</v>
+      </c>
+      <c r="T34" t="n">
+        <v>76.9757496</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -2780,8 +2880,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/11%25C2%25B000%2723.2%2522N%2B77%25C2%25B000%2735.1%2522E/%4011.0064474,77.0071846,813m/data%3D!3m2!1e3!4b1!4m4!3m3!8m2!3d11.0064474!4d77.0097595%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MDcxMy4wIPu8ASoASAFQAw%253D%253D%26skid%3D4fda6185-5bde-4101-8546-ea5282760959&amp;q=EhAkBQIB4C7guzR74cqdAFF6GPbKy88GIjAUlXGEr8AqVM_poncmRqFWX8c0GvEEHQFl3bhMhFS8hIEiHxeJRubU22fGIkl09xQyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S35" t="inlineStr"/>
-      <c r="T35" t="inlineStr"/>
+      <c r="S35" t="n">
+        <v>11.0064474</v>
+      </c>
+      <c r="T35" t="n">
+        <v>77.0071846</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -2850,8 +2954,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/10%25C2%25B055%2754.1%2522N%2B77%25C2%25B003%2754.5%2522E/%4010.9316892,77.06257,739m/data%3D!3m1!1e3!4m4!3m3!8m2!3d10.9316892!4d77.0651449%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MDcxNS4xIPu8ASoASAFQAw%253D%253D%26skid%3D652a08b8-7fcf-4bbb-974f-af77455041a4&amp;q=EhAkBQIB4C7guzR74cqdAFF6GPjKy88GIjDd_0Cpz4uYxh8DPxFz1TISaLy2wNWYcBnxCM-MpZSGwkPH4qHGvcoCtcgUGdF-yv0yAnJSWgFD</t>
         </is>
       </c>
-      <c r="S36" t="inlineStr"/>
-      <c r="T36" t="inlineStr"/>
+      <c r="S36" t="n">
+        <v>10.9316892</v>
+      </c>
+      <c r="T36" t="n">
+        <v>77.06256999999999</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -2918,8 +3026,12 @@
           <t>https://www.google.com/sorry/index?continue=https://maps.google.com/%3Fq%3D11.444716,76.818371%26entry%3Dgps%26g_ep%3DCAESCjExLjE1NC4xMDMYACDXggMqfiw5NDI0MjU5NSw5NDIyMzI5OSw5NDIxNjQxMyw5NDIxMjQ5Niw5NDIwNzM5NCw5NDIwNzUwNiw5NDIwODUwNiw5NDIxNzUyMyw5NDIxODY1Myw5NDIyOTgzOSw5NDIzOTEyNyw0NzA4NzExOCw0NzA4NDM5Myw5NDIxMzIwMEICSU4%253D%26shorturl%3D1&amp;q=EhAkBQIB4C7guzR74cqdAFF6GPvKy88GIi2oQD-j2WJp7nuujFPA2d6VjnXzavaKP4mnBkNvpxvBgRt_34yuQUFlVDY_3TgyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S37" t="inlineStr"/>
-      <c r="T37" t="inlineStr"/>
+      <c r="S37" t="n">
+        <v>11.444716</v>
+      </c>
+      <c r="T37" t="n">
+        <v>76.818371</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -2988,8 +3100,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/11%25C2%25B023%2701.5%2522N%2B76%25C2%25B051%2738.7%2522E/%4011.3837407,76.8581841,17z/data%3D!4m4!3m3!8m2!3d11.3837407!4d76.860759%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MDYwMi4wIPu8ASoASAFQAw%253D%253D%26skid%3D227bfd37-e1a0-4e66-8521-4f57ba86ac23&amp;q=EhAkBQIB4C7guzR74cqdAFF6GPzKy88GIjDDpolnSVpoWCI4sCohJmmgS-rSz2WU6CtSm5-cw0TLBwTHTrAylKfRxGX-HvMdDAYyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S38" t="inlineStr"/>
-      <c r="T38" t="inlineStr"/>
+      <c r="S38" t="n">
+        <v>11.3837407</v>
+      </c>
+      <c r="T38" t="n">
+        <v>76.8581841</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -3058,8 +3174,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/11%25C2%25B016%2719.6%2522N%2B76%25C2%25B037%2736.6%2522E/%4011.2721176,76.6242696,17z/data%3D!3m1!4b1!4m4!3m3!8m2!3d11.2721176!4d76.6268445%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MDYwMi4wIPu8ASoASAFQAw%253D%253D%26skid%3D8c8d403e-3cb3-4bc9-aa61-c824aab4510a&amp;q=EhAkBQIB4C7guzR74cqdAFF6GP3Ky88GIjCYOkvQXEIgVqxKHeuwPzDiEhwN4xhINiXZE5bHt6hfYRHpeddpHuqBb1PAV54K22MyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S39" t="inlineStr"/>
-      <c r="T39" t="inlineStr"/>
+      <c r="S39" t="n">
+        <v>11.2721176</v>
+      </c>
+      <c r="T39" t="n">
+        <v>76.62426960000001</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -3126,8 +3246,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/11%25C2%25B028%2725.2%2522N%2B76%25C2%25B054%2734.5%2522E/%4011.473667,76.909575,738m/data%3D!3m2!1e3!4b1!4m4!3m3!8m2!3d11.473667!4d76.909575%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MDcxNS4xIPu8ASoASAFQAw%253D%253D%26skid%3Dfeb2ae18-83c1-4767-98bf-833cdde868dc&amp;q=EhAkBQIB4C7guzR74cqdAFF6GP7Ky88GIjDDlPadQuqtObKoPjIAEgZKf-SH8qnbXPpThm4C_n50kY-qeXpVOEYS2-GWeD1wt0IyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S40" t="inlineStr"/>
-      <c r="T40" t="inlineStr"/>
+      <c r="S40" t="n">
+        <v>11.473667</v>
+      </c>
+      <c r="T40" t="n">
+        <v>76.909575</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -3196,8 +3320,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/11%25C2%25B018%2728.0%2522N%2B76%25C2%25B045%2729.1%2522E/%4011.3077835,76.7555084,17z/data%3D!3m1!4b1!4m4!3m3!8m2!3d11.3077835!4d76.7580833%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MDYwMi4wIPu8ASoASAFQAw%253D%253D%26skid%3D08b2b7b1-ecda-439c-85b6-2e6e1cb0edca&amp;q=EhAkBQIB4C7guzR74cqdAFF6GP_Ky88GIjBJM35V6NX0LdOXuNLBAaZU1D7kxdDRzi5S5JSytMRF_yR_5O2QTTXkTam3Rtx3FgQyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S41" t="inlineStr"/>
-      <c r="T41" t="inlineStr"/>
+      <c r="S41" t="n">
+        <v>11.3077835</v>
+      </c>
+      <c r="T41" t="n">
+        <v>76.7555084</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -3266,8 +3394,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/Wild%2BEden%2BOrganic%2BFarms/%4011.3915404,76.9197357,1437m/data%3D!3m1!1e3!4m6!3m5!1s0x3ba8e9ce73018fc3:0x8aa4664523899af5!8m2!3d11.39164!4d76.927215!16s%252Fg%252F11j8hlzftq%3Fauthuser%3D0%26entry%3Dtts%26g_ep%3DEgoyMDI1MDcwNi4wIPu8ASoASAFQAw%253D%253D%26skid%3Da2e96334-b0dc-44f8-a6ae-e94d598f5ae2&amp;q=EhAkBQIB4C7guzR74cqdAFF6GIDLy88GIjAp2DBlaIDl5gbum2iG-F7ZOFhLQtJw8KjdWdRizYJ7Upkw_ViSP44s9bABGQf2fXQyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S42" t="inlineStr"/>
-      <c r="T42" t="inlineStr"/>
+      <c r="S42" t="n">
+        <v>11.3915404</v>
+      </c>
+      <c r="T42" t="n">
+        <v>76.9197357</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -3336,8 +3468,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/11%25C2%25B000%2712.3%2522N%2B77%25C2%25B010%2743.5%2522E/%4011.003428,77.178762,739m/data%3D!3m1!1e3!4m4!3m3!8m2!3d11.003428!4d77.178762%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MDcxNS4xIPu8ASoASAFQAw%253D%253D%26skid%3Dd61f3190-2380-4f31-8b37-eae52094236c&amp;q=EhAkBQIB4C7guzR74cqdAFF6GIHLy88GIjCS5q2kmxtY6AeTMUIFb6iG0f4GBx3sSyH8O1zB0IbL67tF5WOunuPtYVsHpc40ER4yAnJSWgFD</t>
         </is>
       </c>
-      <c r="S43" t="inlineStr"/>
-      <c r="T43" t="inlineStr"/>
+      <c r="S43" t="n">
+        <v>11.003428</v>
+      </c>
+      <c r="T43" t="n">
+        <v>77.17876200000001</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -3406,8 +3542,12 @@
           <t>https://www.google.com/sorry/index?continue=https://maps.google.com/%3Fq%3D10.9714453,76.9671702%26hl%3Den-IN%26gl%3Din%26entry%3Dgps%26lucs%3D,47071704%26g_ep%3DCAISBjYuNzYuMxgAIKzfASoJLDQ3MDcxNzA0QgJJTg%253D%253D%26g_st%3Diw&amp;hl=en-IN&amp;q=EhAkBQIB4C7guzR74cqdAFF6GIPLy88GIi3VylbCmlE9XiL0ZLxo48y4fkgiV3rTvfZ2N9O6mYG3Fefg2Wd2qyGOwKKAXAwyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S44" t="inlineStr"/>
-      <c r="T44" t="inlineStr"/>
+      <c r="S44" t="n">
+        <v>10.9714453</v>
+      </c>
+      <c r="T44" t="n">
+        <v>76.9671702</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -3476,8 +3616,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/10%25C2%25B034%2707.1%2522N%2B77%25C2%25B033%2743.1%2522E/%4010.5686511,77.5593948,740m/data%3D!3m2!1e3!4b1!4m4!3m3!8m2!3d10.5686511!4d77.5619697%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MDcxNS4xIPu8ASoASAFQAw%253D%253D%26skid%3D53c3c13a-eb57-491a-97f1-0579ec443a8a&amp;q=EhAkBQIB4C7guzR74cqdAFF6GITLy88GIjB99_dIlJTdGL83IoK780FoRKn_dVrQacPj699vvYqWrSQcSS5xfrdIso3Ba7II_1kyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S45" t="inlineStr"/>
-      <c r="T45" t="inlineStr"/>
+      <c r="S45" t="n">
+        <v>10.5686511</v>
+      </c>
+      <c r="T45" t="n">
+        <v>77.55939480000001</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -3546,8 +3690,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/11%25C2%25B017%2706.0%2522N%2B76%25C2%25B041%2712.4%2522E/%4011.2849867,76.6842011,17z/data%3D!4m4!3m3!8m2!3d11.2849867!4d76.686776%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MDYwMi4wIPu8ASoASAFQAw%253D%253D%26skid%3D2e0e0f46-2ce2-45a7-9f52-f5811ad602bf&amp;q=EhAkBQIB4C7guzR74cqdAFF6GIXLy88GIjAibm9UkYsHXXY2789Cklx07-X3ENlGD4BtzGmY2BMe1nzGRVfYsmkUfGzeBcbpJQ4yAnJSWgFD</t>
         </is>
       </c>
-      <c r="S46" t="inlineStr"/>
-      <c r="T46" t="inlineStr"/>
+      <c r="S46" t="n">
+        <v>11.2849867</v>
+      </c>
+      <c r="T46" t="n">
+        <v>76.6842011</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -3610,8 +3758,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/11%25C2%25B002%2720.5%2522N%2B77%25C2%25B000%2751.2%2522E/%4011.0388606,77.0123806,591m/data%3D!3m1!1e3!4m4!3m3!8m2!3d11.0390268!4d77.0142182%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MDcxMy4wIPu8ASoASAFQAw%253D%253D%26skid%3Dc0adcb42-25a5-4e98-becd-07a1061f4ed8&amp;q=EhAkBQIB4C7guzR74cqdAFF6GIbLy88GIjBCS40g8kUjlVC34c_8wTeZhHM0QLCH2YWlf1mj0sSXN0wLmNudmnvqXNI89VJBJSoyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S47" t="inlineStr"/>
-      <c r="T47" t="inlineStr"/>
+      <c r="S47" t="n">
+        <v>11.0388606</v>
+      </c>
+      <c r="T47" t="n">
+        <v>77.0123806</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -3750,8 +3902,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/10%25C2%25B052%2726.6%2522N%2B76%25C2%25B054%2745.9%2522E/%4010.8743097,76.9114678,4599m/data%3D!3m1!1e3!4m4!3m3!8m2!3d10.8740644!4d76.912735%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MDcxMy4wIPu8ASoASAFQAw%253D%253D%26skid%3D25396959-fe67-4079-b049-7d7b52d930d3&amp;q=EhAkBQIB4C7guzR74cqdAFF6GInLy88GIjAwLBr8er64rVVjpMigI8SyExEtNNGMsA9_vy1qAJv-wKSJY7RbJcnHhqPIpy4o3MYyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S49" t="inlineStr"/>
-      <c r="T49" t="inlineStr"/>
+      <c r="S49" t="n">
+        <v>10.8743097</v>
+      </c>
+      <c r="T49" t="n">
+        <v>76.9114678</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -3820,8 +3976,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/11%25C2%25B018%2713.8%2522N%2B76%25C2%25B038%2750.0%2522E/%4011.3038195,76.6446351,17z/data%3D!3m1!4b1!4m4!3m3!8m2!3d11.3038195!4d76.64721%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MDYwMi4wIPu8ASoASAFQAw%253D%253D%26skid%3D2826b38f-b38a-4046-956e-04550a4ba370&amp;q=EhAkBQIB4C7guzR74cqdAFF6GIrLy88GIjDCWhuSTaq_AwYnPuxNbUD38yihSGUksx0UwREZ6rjd-Kfd7QkWPxhOczbL993tAAgyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S50" t="inlineStr"/>
-      <c r="T50" t="inlineStr"/>
+      <c r="S50" t="n">
+        <v>11.3038195</v>
+      </c>
+      <c r="T50" t="n">
+        <v>76.6446351</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -3892,8 +4052,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/10%25C2%25B053%2743.0%2522N%2B76%25C2%25B056%2743.0%2522E/%4010.895274,76.9426963,715m/data%3D!3m2!1e3!4b1!4m4!3m3!8m2!3d10.895274!4d76.9452712%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MDcxNS4xIPu8ASoASAFQAw%253D%253D%26skid%3D181d52b5-88d8-4695-87fd-07435446f8ec&amp;q=EhAkBQIB4C7guzR74cqdAFF6GIvLy88GIjBVI3pSGc3nIVXpuIf8UNAT5rPOzRyG3Y_HhJMuyxa2DZAOjNzVWAVOHsPkbmtSlLsyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S51" t="inlineStr"/>
-      <c r="T51" t="inlineStr"/>
+      <c r="S51" t="n">
+        <v>10.895274</v>
+      </c>
+      <c r="T51" t="n">
+        <v>76.94269629999999</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -3960,8 +4124,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/10.894962,76.939788/data%3D!4m6!3m5!1s0!7e2!8m2!3d10.8949622!4d76.9397875%3Futm_source%3Dmstt_1%26entry%3Dgps%26coh%3D192189%26g_ep%3DCAESBzI1LjI2LjgYACDl7Q0qkAEsOTQyNTk1NTEsOTQyNzUzMDAsOTQyMjMyOTksOTQyMTY0MTMsOTQyMTI0OTYsOTQyNjAwMzUsOTQyMDczOTQsOTQyMDc1MDYsOTQyMDg1MDYsOTQyMTc1MjMsOTQyMTg2NTMsOTQyMjk4MzksOTQyNzUxNjgsNDcwODQzOTMsOTQyMTMyMDAsOTQyNTgzMjVCAklO%26skid%3D1739996c-0be0-4c3b-ab2e-91e470fa9975%26g_st%3Daw&amp;q=EhAkBQIB4C7guzR74cqdAFF6GI3Ly88GIjDcws0CbZgMbMiQZ4BASo7HofnuLRBjqqxYicAUgyqA7YRxfOnrieHg_ddfzJPSmAQyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S52" t="inlineStr"/>
-      <c r="T52" t="inlineStr"/>
+      <c r="S52" t="n">
+        <v>10.8949622</v>
+      </c>
+      <c r="T52" t="n">
+        <v>76.93978749999999</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -4030,8 +4198,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/10%25C2%25B059%2758.0%2522N%2B77%25C2%25B001%2721.2%2522E/%4010.9991097,77.0230247,3042m/data%3D!3m1!1e3!4m4!3m3!8m2!3d10.999436!4d77.022546%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MDcxMy4wIPu8ASoASAFQAw%253D%253D%26skid%3D9df22802-09b4-4a54-8e52-3b0249740328&amp;q=EhAkBQIB4C7guzR74cqdAFF6GI7Ly88GIjBtb-96JHBHm3TLFr2ytOlMj8b1cCKNAjGH4K05bZENcU1dvZZ7KI_Yb8Fd5CW36j0yAnJSWgFD</t>
         </is>
       </c>
-      <c r="S53" t="inlineStr"/>
-      <c r="T53" t="inlineStr"/>
+      <c r="S53" t="n">
+        <v>10.9991097</v>
+      </c>
+      <c r="T53" t="n">
+        <v>77.02302469999999</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -4100,8 +4272,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/11%25C2%25B009%2705.8%2522N%2B77%25C2%25B011%2748.4%2522E/%4011.1516211,77.1942136,739m/data%3D!3m2!1e3!4b1!4m4!3m3!8m2!3d11.1516211!4d77.1967885%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MDcxNS4xIPu8ASoASAFQAw%253D%253D%26skid%3Dfde599e5-a7a5-4acf-b939-c8a25f98fe64&amp;q=EhAkBQIB4C7guzR74cqdAFF6GI_Ly88GIjBM50jCZy0jZF3HvDzIe0iaj-6dhvsyZsUlcekonrPLzg967mArVECYp8emAG1pMfgyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S54" t="inlineStr"/>
-      <c r="T54" t="inlineStr"/>
+      <c r="S54" t="n">
+        <v>11.1516211</v>
+      </c>
+      <c r="T54" t="n">
+        <v>77.1942136</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -4170,8 +4346,12 @@
           <t>https://www.google.com/sorry/index?continue=https://maps.google.com/%3Fq%3D11.1511815,77.1902660%26entry%3Dgps%26lucs%3D,94224825,94227247,94227248,47071704,47069508,94218641,94203019,47084304,94208458,94208447%26g_ep%3DCAISEjI1LjEzLjUuNzQwMDEyMzg1MBgAINeCAypaLDk0MjI0ODI1LDk0MjI3MjQ3LDk0MjI3MjQ4LDQ3MDcxNzA0LDQ3MDY5NTA4LDk0MjE4NjQxLDk0MjAzMDE5LDQ3MDg0MzA0LDk0MjA4NDU4LDk0MjA4NDQ3QgJJTg%253D%253D%26skid%3D1b6eed1e-28b7-449d-80f5-cbf915772ce6%26g_st%3Diwb&amp;q=EhAkBQIB4C7guzR74cqdAFF6GJHLy88GIi0sNQxRRO4O5m5tlM5oVOz4YS6T7oBpkjKr3PxpEgu5QVIlMmUsGv5SXGtqgGQyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S55" t="inlineStr"/>
-      <c r="T55" t="inlineStr"/>
+      <c r="S55" t="n">
+        <v>11.1511815</v>
+      </c>
+      <c r="T55" t="n">
+        <v>77.19026599999999</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -4240,8 +4420,12 @@
           <t>https://www.google.com/sorry/index?continue=https://maps.google.com/%3Fq%3D10.9912920,77.0111306%26entry%3Dgps%26lucs%3D,94233200,94224825,94227247,94227248,47071704,47069508,94218641,94203019,47084304,94208458,94208447%26g_ep%3DCAISDTYuMTI2LjMuNzY1MDAYACDXggMqYyw5NDIzMzIwMCw5NDIyNDgyNSw5NDIyNzI0Nyw5NDIyNzI0OCw0NzA3MTcwNCw0NzA2OTUwOCw5NDIxODY0MSw5NDIwMzAxOSw0NzA4NDMwNCw5NDIwODQ1OCw5NDIwODQ0N0ICSU4%253D%26g_st%3Diw&amp;q=EhAkBQIB4C7guzR74cqdAFF6GJPLy88GIi26gEZO35HTLJKQhAUhwXSWWp-NV18x5ovfd9TOXtrnPt4Wl4LB0Tt39ZM0TPIyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S56" t="inlineStr"/>
-      <c r="T56" t="inlineStr"/>
+      <c r="S56" t="n">
+        <v>10.991292</v>
+      </c>
+      <c r="T56" t="n">
+        <v>77.0111306</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -4310,8 +4494,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/11%25C2%25B008%2706.7%2522N%2B76%25C2%25B059%2735.2%2522E/%4011.135199,76.9905466,812m/data%3D!3m1!1e3!4m4!3m3!8m2!3d11.135199!4d76.9931215%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MDcxNS4xIPu8ASoASAFQAw%253D%253D%26skid%3D0e4acd03-91ff-4c36-baa5-e7e8b383e828&amp;q=EhAkBQIB4C7guzR74cqdAFF6GJTLy88GIjDWStq_uXIkxd42DOpYBDOy1x9-sAIiz5yyvYku0BcAqaWiNaH1U0L_jA7rJl5y27syAnJSWgFD</t>
         </is>
       </c>
-      <c r="S57" t="inlineStr"/>
-      <c r="T57" t="inlineStr"/>
+      <c r="S57" t="n">
+        <v>11.135199</v>
+      </c>
+      <c r="T57" t="n">
+        <v>76.9905466</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -4371,8 +4559,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/11%25C2%25B004%2706.6%2522N%2B77%25C2%25B002%2724.9%2522E/%4011.0685073,77.0376792,739m/data%3D!3m2!1e3!4b1!4m4!3m3!8m2!3d11.0685073!4d77.0402541%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MDcxNS4xIPu8ASoASAFQAw%253D%253D%26skid%3Dfafc5429-53b0-4940-a9c7-08057b843705&amp;q=EhAkBQIB4C7guzR74cqdAFF6GJXLy88GIjAPFVfJJ88n7VHnKbBBDcw76ng7jXkw7snX7W6EEkEb2doomjz32g_mcnuXn4Dbf6YyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S58" t="inlineStr"/>
-      <c r="T58" t="inlineStr"/>
+      <c r="S58" t="n">
+        <v>11.0685073</v>
+      </c>
+      <c r="T58" t="n">
+        <v>77.0376792</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -4441,8 +4633,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/10.887695,77.035110/data%3D!4m6!3m5!1s0!7e2!8m2!3d10.887695299999999!4d77.03511019999999%3Futm_source%3Dmstt_1%26entry%3Dgps%26coh%3D192189%26g_ep%3DCAESCjExLjE0NC4xMDUYACDXggMqkAEsOTQyMDc0ODIsOTQyMjMyOTksOTQyMTY0MTMsOTQyMTI0OTYsOTQyMTI2NjUsOTQyMDczOTQsOTQyMDc1MDYsOTQyMDg1MDYsOTQyMTc1MjMsOTQyMTg2NTMsOTQyMjk4MzksOTQyMzkxMjEsOTQyMjUwNTMsNDcwODcxMTgsNDcwODQzOTMsOTQyMTMyMDBCAklO&amp;q=EhAkBQIB4C7guzR74cqdAFF6GJbLy88GIjD7btGFFLpuXg9OKSF5GPa5OHbJCrTnQsjNvhSBNw8AAVIP1A13qYrF9r-O3O-oEtQyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S59" t="inlineStr"/>
-      <c r="T59" t="inlineStr"/>
+      <c r="S59" t="n">
+        <v>10.8876953</v>
+      </c>
+      <c r="T59" t="n">
+        <v>77.03511019999999</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -4511,8 +4707,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/10.922502,77.200927/data%3D!4m6!3m5!1s0!7e2!8m2!3d10.9225019!4d77.2009274%3Futm_source%3Dmstt_1%26entry%3Dgps%26coh%3D192189%26g_ep%3DCAESBjI1LjguMRgAIPrsDSpsLDk0MjQyNTgzLDk0MjIzMjk5LDk0MjE2NDEzLDk0MjEyNDk2LDk0MjA3Mzk0LDk0MjA3NTA2LDk0MjA4NTA2LDk0MjE3NTIzLDk0MjE4NjUzLDk0MjI5ODM5LDQ3MDg0MzkzLDk0MjEzMjAwQgJJTg%253D%253D%26g_st%3Daw&amp;q=EhAkBQIB4C7guzR74cqdAFF6GJjLy88GIjAAVoUPcegrm3oJ4Pm1oQHOF1wkjIbMxG3ZeC_K1cRtHit5e4nYgv_mL87bV2jwFy4yAnJSWgFD</t>
         </is>
       </c>
-      <c r="S60" t="inlineStr"/>
-      <c r="T60" t="inlineStr"/>
+      <c r="S60" t="n">
+        <v>10.9225019</v>
+      </c>
+      <c r="T60" t="n">
+        <v>77.2009274</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -4573,8 +4773,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/10%25C2%25B056%2727.3%2522N%2B77%25C2%25B009%2728.3%2522E/%4010.940919,77.157869,670m/data%3D!3m2!1e3!4b1!4m4!3m3!8m2!3d10.940919!4d77.157869%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MDgxOS4wIPu8ASoASAFQAw%253D%253D%26skid%3D87c81d2d-345d-4643-aa40-d7e4a97fa859&amp;q=EhAkBQIB4C7guzR74cqdAFF6GJnLy88GIjC2aw6VXOiaZVfYSgjn4ANhcLUdZJg3KEP3s7xOoYrR46QU1H3R-YkxBtb2ImyLdqcyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S61" t="inlineStr"/>
-      <c r="T61" t="inlineStr"/>
+      <c r="S61" t="n">
+        <v>10.940919</v>
+      </c>
+      <c r="T61" t="n">
+        <v>77.15786900000001</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -4635,8 +4839,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/10%25C2%25B054%2716.7%2522N%2B77%25C2%25B009%2724.6%2522E/%4010.904629,77.156827,855m/data%3D!3m2!1e3!4b1!4m4!3m3!8m2!3d10.904629!4d77.156827%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MDcyMC4wIPu8ASoASAFQAw%253D%253D%26skid%3D26034ab5-5afa-4488-a4d9-4de825589d4c&amp;q=EhAkBQIB4C7guzR74cqdAFF6GJrLy88GIjAyM-pfv661qkISdsWLPw2M2Zfjyxm1P9iNkmA5S-KFOkbkR8QbzmeRoWoSrGXeXCsyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S62" t="inlineStr"/>
-      <c r="T62" t="inlineStr"/>
+      <c r="S62" t="n">
+        <v>10.904629</v>
+      </c>
+      <c r="T62" t="n">
+        <v>77.15682700000001</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -4697,8 +4905,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/10%25C2%25B046%2701.8%2522N%2B77%25C2%25B011%2704.2%2522E/%4010.7671635,77.1819197,856m/data%3D!3m2!1e3!4b1!4m4!3m3!8m2!3d10.7671635!4d77.1844946%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MDcyMC4wIPu8ASoASAFQAw%253D%253D%26skid%3D2c2c7304-fa4f-4de5-881a-227c5def2569&amp;q=EhAkBQIB4C7guzR74cqdAFF6GJvLy88GIjCvvVfs_QchacFQi5dQ9gdmHqxDHcOfFexXfkKdACH3o4iiwEU5h5sjUKuxpcH99xkyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S63" t="inlineStr"/>
-      <c r="T63" t="inlineStr"/>
+      <c r="S63" t="n">
+        <v>10.7671635</v>
+      </c>
+      <c r="T63" t="n">
+        <v>77.18191969999999</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -4759,8 +4971,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/10%25C2%25B045%2746.2%2522N%2B77%25C2%25B011%2727.4%2522E/%4010.76282,77.1883672,856m/data%3D!3m2!1e3!4b1!4m4!3m3!8m2!3d10.76282!4d77.1909421%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MDcyMC4wIPu8ASoASAFQAw%253D%253D%26skid%3Df2800ab5-0a8e-4457-b428-48c68ee51e27&amp;q=EhAkBQIB4C7guzR74cqdAFF6GJ7Ly88GIjA2xnL647NOHBQQO3yuoN2vpa_FD2X5o4dg5uAiT8czycBmCxy3Pr6BfNjyUmXruoIyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S64" t="inlineStr"/>
-      <c r="T64" t="inlineStr"/>
+      <c r="S64" t="n">
+        <v>10.76282</v>
+      </c>
+      <c r="T64" t="n">
+        <v>77.1883672</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -4821,8 +5037,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/10%25C2%25B044%2736.4%2522N%2B77%25C2%25B010%2734.5%2522E/%4010.7434396,77.1736684,856m/data%3D!3m2!1e3!4b1!4m4!3m3!8m2!3d10.7434396!4d77.1762433%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MDcyMC4wIPu8ASoASAFQAw%253D%253D%26skid%3Dede9a2e1-d3e3-4033-a223-a5ac93e0b86e&amp;q=EhAkBQIB4C7guzR74cqdAFF6GJ_Ly88GIjByOgUGJEBVgxzicx8VQVlzkgPA-zJP3IS3r_W1aPvjn3Hjyg8ZyRa1XtP-Tr7D7nsyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S65" t="inlineStr"/>
-      <c r="T65" t="inlineStr"/>
+      <c r="S65" t="n">
+        <v>10.7434396</v>
+      </c>
+      <c r="T65" t="n">
+        <v>77.1736684</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -4883,8 +5103,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/10%25C2%25B044%2728.5%2522N%2B77%25C2%25B010%2743.0%2522E/%4010.7412452,77.1760347,856m/data%3D!3m2!1e3!4b1!4m4!3m3!8m2!3d10.7412452!4d77.1786096%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MDcyMC4wIPu8ASoASAFQAw%253D%253D%26skid%3Df2dfc92c-b0ff-4ef6-9637-0039fdc7e87f&amp;q=EhAkBQIB4C7guzR74cqdAFF6GKDLy88GIjDHZfkyJDtoWk3MQSiWfMlLIyoGIxSlMEb8spoPSSEWvDYgHjshAEdEp0PHD_7dNQUyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S66" t="inlineStr"/>
-      <c r="T66" t="inlineStr"/>
+      <c r="S66" t="n">
+        <v>10.7412452</v>
+      </c>
+      <c r="T66" t="n">
+        <v>77.1760347</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -4945,8 +5169,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/10%25C2%25B042%2717.6%2522N%2B77%25C2%25B011%2736.9%2522E/%4010.7048759,77.191018,856m/data%3D!3m2!1e3!4b1!4m4!3m3!8m2!3d10.7048759!4d77.1935929%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MDcyMC4wIPu8ASoASAFQAw%253D%253D%26skid%3D7c194f7d-aead-4897-a9d7-c5faa7ba260d&amp;q=EhAkBQIB4C7guzR74cqdAFF6GKHLy88GIjCugJS8_-dNcZT3iG8BXeAGRIuwf2XtGNm-TP4C6gjZN-d5NP4RFVsf88Z5VASrZF0yAnJSWgFD</t>
         </is>
       </c>
-      <c r="S67" t="inlineStr"/>
-      <c r="T67" t="inlineStr"/>
+      <c r="S67" t="n">
+        <v>10.7048759</v>
+      </c>
+      <c r="T67" t="n">
+        <v>77.191018</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -5007,8 +5235,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/10%25C2%25B042%2759.5%2522N%2B77%25C2%25B013%2757.2%2522E/%4010.7165182,77.2299775,856m/data%3D!3m2!1e3!4b1!4m4!3m3!8m2!3d10.7165182!4d77.2325524%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MDcyMC4wIPu8ASoASAFQAw%253D%253D%26skid%3Df0f81d91-b02a-40d2-8388-6787189280db&amp;q=EhAkBQIB4C7guzR74cqdAFF6GKLLy88GIjCClWeHhk6Ye69q1ikEZ2Oyu53CCakUGhJfRee-dKGANLntSzTiZty-kcpzBQ2hFiAyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S68" t="inlineStr"/>
-      <c r="T68" t="inlineStr"/>
+      <c r="S68" t="n">
+        <v>10.7165182</v>
+      </c>
+      <c r="T68" t="n">
+        <v>77.2299775</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -5069,8 +5301,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/10%25C2%25B043%2710.2%2522N%2B77%25C2%25B013%2758.4%2522E/%4010.7194914,77.2303238,856m/data%3D!3m2!1e3!4b1!4m4!3m3!8m2!3d10.7194914!4d77.2328987%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MDcyMC4wIPu8ASoASAFQAw%253D%253D%26skid%3D56cda0b6-1af9-4c9a-852b-2b3d9c772281&amp;q=EhAkBQIB4C7guzR74cqdAFF6GKPLy88GIjDQv-CVA4pGRfg1RYTPWz9_kMCZTVO-8h51ZnfGyfk0CdTlMn7_wjbwIjxGB_I1DFgyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S69" t="inlineStr"/>
-      <c r="T69" t="inlineStr"/>
+      <c r="S69" t="n">
+        <v>10.7194914</v>
+      </c>
+      <c r="T69" t="n">
+        <v>77.23032379999999</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -5131,8 +5367,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/10%25C2%25B047%2700.2%2522N%2B77%25C2%25B018%2722.6%2522E/%4010.7833985,77.303689,856m/data%3D!3m2!1e3!4b1!4m4!3m3!8m2!3d10.7833985!4d77.3062639%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MDcyMC4wIPu8ASoASAFQAw%253D%253D%26skid%3D7932b5c3-32aa-4eb3-9d94-e12cc5bb7ee4&amp;q=EhAkBQIB4C7guzR74cqdAFF6GKXLy88GIjDBnYAl6cDkuyDQuYeZDN5oI29K3_iFCCOBjLn_oDU2J91SElyDOnFeFhkM6YTvHsoyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S70" t="inlineStr"/>
-      <c r="T70" t="inlineStr"/>
+      <c r="S70" t="n">
+        <v>10.7833985</v>
+      </c>
+      <c r="T70" t="n">
+        <v>77.30368900000001</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -5191,8 +5431,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/11%25C2%25B000%2714.2%2522N%2B77%25C2%25B000%2753.1%2522E/%4011.0039453,77.0121674,855m/data%3D!3m2!1e3!4b1!4m4!3m3!8m2!3d11.0039453!4d77.0147423%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MDcyMC4wIPu8ASoASAFQAw%253D%253D%26skid%3Dc82bd8ee-4b7a-4113-9f36-33978e7661ba&amp;q=EhAkBQIB4C7guzR74cqdAFF6GKfLy88GIjCZTmN0R2lViqKKBRkeUlFFvZCJXbCpS-FvPFX9tHykFJyTmuYPYdPiPqGBvIr-7oUyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S71" t="inlineStr"/>
-      <c r="T71" t="inlineStr"/>
+      <c r="S71" t="n">
+        <v>11.0039453</v>
+      </c>
+      <c r="T71" t="n">
+        <v>77.0121674</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -5253,8 +5497,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/11%25C2%25B000%2730.0%2522N%2B77%25C2%25B000%2754.6%2522E/%4011.0083212,77.0125808,855m/data%3D!3m2!1e3!4b1!4m4!3m3!8m2!3d11.0083212!4d77.0151557%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MDcyMC4wIPu8ASoASAFQAw%253D%253D%26skid%3D0ba5a1d4-592b-45d9-a33c-ca07e529b5e3&amp;q=EhAkBQIB4C7guzR74cqdAFF6GKjLy88GIjCACTNKlRHCWteg5wzwThulihOxM2yDXgvsF8oaSLWNGPJmedsmaGF4yZyi_DFPET0yAnJSWgFD</t>
         </is>
       </c>
-      <c r="S72" t="inlineStr"/>
-      <c r="T72" t="inlineStr"/>
+      <c r="S72" t="n">
+        <v>11.0083212</v>
+      </c>
+      <c r="T72" t="n">
+        <v>77.01258079999999</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -5313,8 +5561,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/11%25C2%25B000%2738.4%2522N%2B77%25C2%25B001%2701.8%2522E/%4011.0106583,77.0145863,855m/data%3D!3m2!1e3!4b1!4m4!3m3!8m2!3d11.0106583!4d77.0171612%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MDcyMC4wIPu8ASoASAFQAw%253D%253D%26skid%3D449ee85f-8587-47e8-a6e4-5211b9312dc5&amp;q=EhAkBQIB4C7guzR74cqdAFF6GKnLy88GIjCdUxXY4x08EMuK6TXwxtC3LhiWJDEmQIXUMERNsyPyetRXCOz0h8R5Bn3NdIox7kUyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S73" t="inlineStr"/>
-      <c r="T73" t="inlineStr"/>
+      <c r="S73" t="n">
+        <v>11.0106583</v>
+      </c>
+      <c r="T73" t="n">
+        <v>77.0145863</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -5373,8 +5625,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/11%25C2%25B001%2731.9%2522N%2B77%25C2%25B001%2700.6%2522E/%4011.0255219,77.014254,855m/data%3D!3m2!1e3!4b1!4m4!3m3!8m2!3d11.0255219!4d77.0168289%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MDcyMC4wIPu8ASoASAFQAw%253D%253D%26skid%3D928b2496-5db7-473c-9a85-e07b157a975c&amp;q=EhAkBQIB4C7guzR74cqdAFF6GKrLy88GIjBTSA7paoSD1JKfS_oY_uhuT5-CfEKZqH4fpvArAeJ0VZOB3B4FK7bbQT96LN_gFgIyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S74" t="inlineStr"/>
-      <c r="T74" t="inlineStr"/>
+      <c r="S74" t="n">
+        <v>11.0255219</v>
+      </c>
+      <c r="T74" t="n">
+        <v>77.01425399999999</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -5435,8 +5691,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/11%25C2%25B002%2711.3%2522N%2B76%25C2%25B056%2730.9%2522E/%4011.036475,76.9393334,855m/data%3D!3m2!1e3!4b1!4m4!3m3!8m2!3d11.036475!4d76.9419083%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MDcyMC4wIPu8ASoASAFQAw%253D%253D%26skid%3D39cfc89b-0dce-4964-a87c-b2562aab0b30&amp;q=EhAkBQIB4C7guzR74cqdAFF6GKvLy88GIjBiM7lxfCwb13UAojP_Yi2nGtBM0qxWDtUjqsh3Lba5kbq7DWThwkFXjSdz1c-V9ooyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S75" t="inlineStr"/>
-      <c r="T75" t="inlineStr"/>
+      <c r="S75" t="n">
+        <v>11.036475</v>
+      </c>
+      <c r="T75" t="n">
+        <v>76.9393334</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -5497,8 +5757,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/10%25C2%25B058%2758.6%2522N%2B76%25C2%25B055%2717.8%2522E/%4010.9829463,76.9216087,855m/data%3D!3m2!1e3!4b1!4m4!3m3!8m2!3d10.9829463!4d76.9216087%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MDcyMC4wIPu8ASoASAFQAw%253D%253D%26skid%3D843b58c4-d94f-40af-8f87-9beaba311e20&amp;q=EhAkBQIB4C7guzR74cqdAFF6GKzLy88GIjAiJ8Wi0C6d0wjHEu1SU4x718t-dRhcyIWqn_Zd1ChGE1ZOKi57_jzkM1h3My8Mlo0yAnJSWgFD</t>
         </is>
       </c>
-      <c r="S76" t="inlineStr"/>
-      <c r="T76" t="inlineStr"/>
+      <c r="S76" t="n">
+        <v>10.9829463</v>
+      </c>
+      <c r="T76" t="n">
+        <v>76.92160869999999</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -5561,8 +5825,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/Rottigoundanur%2BRoad,%2BTamil%2BNadu%2B641105/%4010.8749621,76.9061662,1504m/data%3D!3m1!1e3!4m6!3m5!1s0x3ba84351318debe9:0xa238b96498d2048b!8m2!3d10.8746211!4d76.9100863!16s%252Fg%252F1tfv3kpt%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MDgxOS4wIPu8ASoASAFQAw%253D%253D%26skid%3Dd396d309-485c-400e-89e0-766157dd82a8&amp;q=EhAkBQIB4C7guzR74cqdAFF6GK7Ly88GIjD_rGucGAaELn3AXiT16Hd8cGDHHg1jeluM0pQWsLK9UhakX20ovPZNjazRP6Nsy2MyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S77" t="inlineStr"/>
-      <c r="T77" t="inlineStr"/>
+      <c r="S77" t="n">
+        <v>10.8749621</v>
+      </c>
+      <c r="T77" t="n">
+        <v>76.9061662</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -5621,8 +5889,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/11%25C2%25B001%2723.7%2522N%2B77%25C2%25B000%2738.5%2522E/%4011.0232593,77.0081249,855m/data%3D!3m2!1e3!4b1!4m4!3m3!8m2!3d11.0232593!4d77.0106998%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MDcyMy4wIPu8ASoASAFQAw%253D%253D%26skid%3Dcc930602-2e71-4ba6-b727-a7ec18ac2dba&amp;q=EhAkBQIB4C7guzR74cqdAFF6GK_Ly88GIjAmOStArI3PcmZpSotn86a2T4_g7hBWDeBbJgYL2lra49KOrAETlWcoL1jG9djeuJQyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S78" t="inlineStr"/>
-      <c r="T78" t="inlineStr"/>
+      <c r="S78" t="n">
+        <v>11.0232593</v>
+      </c>
+      <c r="T78" t="n">
+        <v>77.0081249</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -5683,8 +5955,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/10%25C2%25B047%2726.1%2522N%2B77%25C2%25B006%2757.9%2522E/%4010.7905807,77.1135102,855m/data%3D!3m2!1e3!4b1!4m4!3m3!8m2!3d10.7905807!4d77.1160851%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MDcyMy4wIPu8ASoASAFQAw%253D%253D%26skid%3D0393247f-900f-4c31-94fd-dcc9076320cc&amp;q=EhAkBQIB4C7guzR74cqdAFF6GLDLy88GIjAUG7Nu0wHZKZCp-KnLjZ7a2ObnYkB6THQLY6HG0eD_yp22MRf9Y2Dn0HxRBkOnyAQyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S79" t="inlineStr"/>
-      <c r="T79" t="inlineStr"/>
+      <c r="S79" t="n">
+        <v>10.7905807</v>
+      </c>
+      <c r="T79" t="n">
+        <v>77.11351019999999</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -5807,8 +6083,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/10%25C2%25B044%2757.4%2522N%2B76%25C2%25B055%2744.9%2522E/%4010.7492678,76.9265584,856m/data%3D!3m2!1e3!4b1!4m4!3m3!8m2!3d10.7492678!4d76.9291333%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MDcyMy4wIPu8ASoASAFQAw%253D%253D%26skid%3D2abb6e17-bf51-4a01-830a-db42831bd423&amp;q=EhAkBQIB4C7guzR74cqdAFF6GLLLy88GIjDTn00oxvk51YNmqP9EuE37HsfFsIygtmQ8rqgz0SoOLmc3bH-7qukYIHBqUJlLAgcyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S81" t="inlineStr"/>
-      <c r="T81" t="inlineStr"/>
+      <c r="S81" t="n">
+        <v>10.7492678</v>
+      </c>
+      <c r="T81" t="n">
+        <v>76.9265584</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -5869,8 +6149,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/10%25C2%25B045%2727.1%2522N%2B76%25C2%25B056%2735.8%2522E/%4010.7575362,76.9406887,856m/data%3D!3m2!1e3!4b1!4m4!3m3!8m2!3d10.7575362!4d76.9432636%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MDcyMy4wIPu8ASoASAFQAw%253D%253D%26skid%3D7578cb7e-a470-4850-b8b6-5fd29997b8be&amp;q=EhAkBQIB4C7guzR74cqdAFF6GLTLy88GIjBNhIsYOJQFzSvU3EKF3LKbjI92TpslyX5W1hUbtBWCHR25Wb5Vkqi5cQMyWCXUKDkyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S82" t="inlineStr"/>
-      <c r="T82" t="inlineStr"/>
+      <c r="S82" t="n">
+        <v>10.7575362</v>
+      </c>
+      <c r="T82" t="n">
+        <v>76.9406887</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -5931,8 +6215,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/10%25C2%25B045%2740.0%2522N%2B76%25C2%25B057%2706.4%2522E/%4010.7611135,76.9492015,856m/data%3D!3m2!1e3!4b1!4m4!3m3!8m2!3d10.7611135!4d76.9517764%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MDcyMy4wIPu8ASoASAFQAw%253D%253D%26skid%3Def0637b2-63c1-4783-9078-91fb5cab4ba6&amp;q=EhAkBQIB4C7guzR74cqdAFF6GLXLy88GIjB6GApS5YceTtKj3wb5Onp26u0QlTcKU3BjIXV1drak1mBeC_j5X1R8Za5KxAce21kyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S83" t="inlineStr"/>
-      <c r="T83" t="inlineStr"/>
+      <c r="S83" t="n">
+        <v>10.7611135</v>
+      </c>
+      <c r="T83" t="n">
+        <v>76.9492015</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -5993,8 +6281,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/10%25C2%25B046%2752.9%2522N%2B76%25C2%25B058%2730.2%2522E/%4010.7813473,76.9724898,856m/data%3D!3m2!1e3!4b1!4m4!3m3!8m2!3d10.7813473!4d76.9750647%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MDcyMy4wIPu8ASoASAFQAw%253D%253D%26skid%3Ddf5c0fcd-ffe2-44c8-9bec-46373ec6cae5&amp;q=EhAkBQIB4C7guzR74cqdAFF6GLnLy88GIjDsU_BHymOOobLZLy4HWncYKLVNvjRhCnCc9OAC9yXHrgVmJ4lFzU5TwcCnSbYr0xEyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S84" t="inlineStr"/>
-      <c r="T84" t="inlineStr"/>
+      <c r="S84" t="n">
+        <v>10.7813473</v>
+      </c>
+      <c r="T84" t="n">
+        <v>76.97248980000001</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -6063,8 +6355,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/10%25C2%25B055%2756.0%2522N%2B77%25C2%25B004%2752.5%2522E/%4010.9322117,77.0786769,855m/data%3D!3m2!1e3!4b1!4m4!3m3!8m2!3d10.9322117!4d77.0812518%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MDcyMy4wIPu8ASoASAFQAw%253D%253D%26skid%3D3487e4d3-39d7-44f8-a177-831f239b2516&amp;q=EhAkBQIB4C7guzR74cqdAFF6GLrLy88GIjCX_0ehKTLkrlpDQ_WEEgKuJQstmaOEqo3yeBWpKx_QAhE9jki0oN2wJ2TIQlMi_7AyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S85" t="inlineStr"/>
-      <c r="T85" t="inlineStr"/>
+      <c r="S85" t="n">
+        <v>10.9322117</v>
+      </c>
+      <c r="T85" t="n">
+        <v>77.0786769</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -6129,8 +6425,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/10%25C2%25B057%2706.0%2522N%2B77%25C2%25B007%2757.2%2522E/%4010.9516773,77.1299849,855m/data%3D!3m2!1e3!4b1!4m4!3m3!8m2!3d10.9516773!4d77.1325598%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MDcyMy4wIPu8ASoASAFQAw%253D%253D%26skid%3Dae2738ad-eef6-411b-a35c-85898ce2377e&amp;q=EhAkBQIB4C7guzR74cqdAFF6GLzLy88GIjDYVCjA2AkySFm9vNJBPGwkUELe7yIojlW2bINfPKQagv8J1D5gRsTfzSmtXvXN5ogyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S86" t="inlineStr"/>
-      <c r="T86" t="inlineStr"/>
+      <c r="S86" t="n">
+        <v>10.9516773</v>
+      </c>
+      <c r="T86" t="n">
+        <v>77.1299849</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -6189,8 +6489,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/11%25C2%25B007%2735.1%2522N%2B76%25C2%25B044%2758.8%2522E/%4011.1264268,76.7470868,855m/data%3D!3m2!1e3!4b1!4m4!3m3!8m2!3d11.1264268!4d76.7496617%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MDcyMy4wIPu8ASoASAFQAw%253D%253D%26skid%3D8f4e5b1b-ac10-4a20-93c9-3d62a7c1c229&amp;q=EhAkBQIB4C7guzR74cqdAFF6GL7Ly88GIjAdZ92wYNxRN7Rv4QstGMn0rwRYbZFXgUh5IOinUbGdiGaoN3QLheZgX_tOh7D__AoyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S87" t="inlineStr"/>
-      <c r="T87" t="inlineStr"/>
+      <c r="S87" t="n">
+        <v>11.1264268</v>
+      </c>
+      <c r="T87" t="n">
+        <v>76.74708680000001</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -6249,8 +6553,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/11.001321,77.009231/data%3D!4m6!3m5!1s0!7e2!8m2!3d11.0013206!4d77.0092313%3Futm_source%3Dmstt_1%26entry%3Dgps%26coh%3D192189%26g_ep%3DCAESBzI1LjI2LjgYACDl7Q0qkAEsOTQyNzgzMDYsOTQyNzUzMTIsOTQyMjMyOTksOTQyMTY0MTMsOTQyMTI0OTYsOTQyMDczOTQsOTQyMDc1MDYsOTQyMDg1MDYsOTQyMTc1MjMsOTQyMTg2NTMsOTQyMjk4MzksOTQyNzUxNjgsOTQyNjI3MzksNDcwODQzOTMsOTQyMTMyMDAsOTQyNTgzMjVCAklO%26skid%3D95eb4f96-3562-481c-bc78-a84b4be7c2bf%26g_st%3Dac&amp;q=EhAkBQIB4C7guzR74cqdAFF6GMDLy88GIjBa5ccus-3C0CPERae4Eeqr9QUQUFPjOSvh1SeVTIXaNC48VMkB0hZiFSsJi7z2_lMyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S88" t="inlineStr"/>
-      <c r="T88" t="inlineStr"/>
+      <c r="S88" t="n">
+        <v>11.0013206</v>
+      </c>
+      <c r="T88" t="n">
+        <v>77.0092313</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -6309,8 +6617,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/11%25C2%25B000%2722.4%2522N%2B76%25C2%25B059%2730.5%2522E/%4011.0062304,76.9892311,855m/data%3D!3m2!1e3!4b1!4m4!3m3!8m2!3d11.0062304!4d76.991806%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MDcyOC4wIPu8ASoASAFQAw%253D%253D%26skid%3Df15dded5-de00-4b7c-a7c6-f2c880fcece1&amp;q=EhAkBQIB4C7guzR74cqdAFF6GMbLy88GIjAKAR-xJ8Tnu25008-AJn_pO4YGXRDXk02APyJoDvn-eWMVic2Tkzqypld6exMVvvIyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S89" t="inlineStr"/>
-      <c r="T89" t="inlineStr"/>
+      <c r="S89" t="n">
+        <v>11.0062304</v>
+      </c>
+      <c r="T89" t="n">
+        <v>76.9892311</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -6371,8 +6683,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/%4011.008563,77.0448761,3a,75y,169.75h/data%3D!3m5!1e1!3m3!1sJDGsvK8jC2Cbe7wGvzM0yg!2e0!6shttps:%252F%252Fstreetviewpixels-pa.googleapis.com%252Fv1%252Fthumbnail%253Fpanoid%253DJDGsvK8jC2Cbe7wGvzM0yg%2526w%253D900%2526h%253D600%2526ll%253D0.0,0.0%2526yaw%253D169.0%2526pitch%253D90.0%2526cb_client%253Dgmm.iv.android%3Futm_source%3Dmstt_0%26g_ep%3DCAESBzI1LjI5LjAYACCBgQEqkAEsOTQyNjc3MjcsOTQyNzUzMDYsOTQyMjMyOTksOTQyMTY0MTMsOTQyODA1NzYsOTQyMTI0OTYsOTQyMDczOTQsOTQyMDc1MDYsOTQyMDg1MDYsOTQyMTc1MjMsOTQyMTg2NTMsOTQyMjk4MzksOTQyNzUxNjgsNDcwODQzOTMsOTQyMTMyMDAsOTQyNTgzMjVCAklO%26skid%3D58f775f0-46f6-4e35-bdd2-a9c70418b237&amp;q=EhAkBQIB4C7guzR74cqdAFF6GMfLy88GIi0olWmQvNloJclwCrmb1P4xC_vk_e2agaBT7XfVOYdH_E8ItUT5h7kaWlDvmNEyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S90" t="inlineStr"/>
-      <c r="T90" t="inlineStr"/>
+      <c r="S90" t="n">
+        <v>11.008563</v>
+      </c>
+      <c r="T90" t="n">
+        <v>77.0448761</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -6431,8 +6747,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/11%25C2%25B000%2723.9%2522N%2B76%25C2%25B058%2747.0%2522E/%4011.0066326,76.9771423,855m/data%3D!3m2!1e3!4b1!4m4!3m3!8m2!3d11.0066326!4d76.9797172%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MDcyOC4wIPu8ASoASAFQAw%253D%253D%26skid%3De1930f63-be38-4a53-925f-933b5a621ba9&amp;q=EhAkBQIB4C7guzR74cqdAFF6GMrLy88GIjAH8dNI8ifSPw_7wPibYr2tl4rrxy_REUzTTq0z99yMqXRGEoYJZjeiuwK9Cuu7glsyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S91" t="inlineStr"/>
-      <c r="T91" t="inlineStr"/>
+      <c r="S91" t="n">
+        <v>11.0066326</v>
+      </c>
+      <c r="T91" t="n">
+        <v>76.9771423</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -6493,8 +6813,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/11%25C2%25B005%2723.7%2522N%2B77%25C2%25B005%2704.0%2522E/%4011.0899243,77.08187,855m/data%3D!3m2!1e3!4b1!4m4!3m3!8m2!3d11.0899243!4d77.0844449%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MDczMC4wIPu8ASoASAFQAw%253D%253D%26skid%3Dccc82c18-11d6-4cd7-8bfe-4ad32255e23d&amp;q=EhAkBQIB4C7guzR74cqdAFF6GMzLy88GIjCQO_eZx5XK_y5nMqhoL1VkpOVPYy0_zf9VtrOiEtSeqa4o292CbKhA48x2iNYKhnwyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S92" t="inlineStr"/>
-      <c r="T92" t="inlineStr"/>
+      <c r="S92" t="n">
+        <v>11.0899243</v>
+      </c>
+      <c r="T92" t="n">
+        <v>77.08187</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -6555,8 +6879,12 @@
           <t>https://www.google.com/sorry/index?continue=https://maps.google.com/%3Fq%3D11.0248566,76.9727844%26entry%3Dgps%26lucs%3D,94282333,94224825,94227247,94227248,94231188,47071704,47069508,94218641,94203019,47084304%26g_ep%3DCAISEjI1LjA0LjAuNzE3NjEyNzQyMBgAINeCAypaLDk0MjgyMzMzLDk0MjI0ODI1LDk0MjI3MjQ3LDk0MjI3MjQ4LDk0MjMxMTg4LDQ3MDcxNzA0LDQ3MDY5NTA4LDk0MjE4NjQxLDk0MjAzMDE5LDQ3MDg0MzA0QgJJTg%253D%253D%26skid%3D53ab3da2-41a9-41eb-8eb2-351d0d447e3b%26g_st%3Diw&amp;q=EhAkBQIB4C7guzR74cqdAFF6GM3Ly88GIi3n1X59tBh7qpCvR-P9XQ31RXeqHube5gYQ5E3itPut3Ec1dwY8WZI_oCAmEnMyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S93" t="inlineStr"/>
-      <c r="T93" t="inlineStr"/>
+      <c r="S93" t="n">
+        <v>11.0248566</v>
+      </c>
+      <c r="T93" t="n">
+        <v>76.97278439999999</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -6617,8 +6945,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/11%25C2%25B014%2735.5%2522N%2B77%25C2%25B032%2759.0%2522E/%4011.2432003,77.5471462,854m/data%3D!3m2!1e3!4b1!4m4!3m3!8m2!3d11.2432003!4d77.5497211%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MDgxMy4wIPu8ASoASAFQAw%253D%253D%26skid%3D9353fb18-e0ac-4b04-b668-859838e1bb92&amp;q=EhAkBQIB4C7guzR74cqdAFF6GNDLy88GIjAFfmxw-SACaH7dApWLUudR24H0YCCcWxvIS1ew9Idf-YVD7F2Jvi2f1jd2DQ8ube8yAnJSWgFD</t>
         </is>
       </c>
-      <c r="S94" t="inlineStr"/>
-      <c r="T94" t="inlineStr"/>
+      <c r="S94" t="n">
+        <v>11.2432003</v>
+      </c>
+      <c r="T94" t="n">
+        <v>77.5471462</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -6679,8 +7011,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/11%25C2%25B010%2714.2%2522N%2B77%25C2%25B006%2719.9%2522E/%4011.1705994,77.1029566,854m/data%3D!3m2!1e3!4b1!4m4!3m3!8m2!3d11.1705994!4d77.1055315%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MDgxMy4wIPu8ASoASAFQAw%253D%253D%26skid%3D5c6ec0e3-c52f-4bb7-812a-cd2d35b02847&amp;q=EhAkBQIB4C7guzR74cqdAFF6GNHLy88GIjBtnkAaE2MGRBsUwYbpE5dRSNb2aOVpMrPAGDC-2Tz7IJVfiN81Qqt8QrAgzwSlLAoyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S95" t="inlineStr"/>
-      <c r="T95" t="inlineStr"/>
+      <c r="S95" t="n">
+        <v>11.1705994</v>
+      </c>
+      <c r="T95" t="n">
+        <v>77.1029566</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -6741,8 +7077,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/11%25C2%25B010%2732.3%2522N%2B77%25C2%25B004%2745.3%2522E/%4011.1756429,77.0766784,854m/data%3D!3m2!1e3!4b1!4m4!3m3!8m2!3d11.1756429!4d77.0792533%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MDgxMy4wIPu8ASoASAFQAw%253D%253D%26skid%3Db4a4bf3b-f816-4995-9bdc-00fa9a749dfe&amp;q=EhAkBQIB4C7guzR74cqdAFF6GNLLy88GIjCssdmy2Mmva843qSl8BSBG0txRJpsVZduJeZv2W4tRW8YL54zn6YIbuOcUC7blwaYyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S96" t="inlineStr"/>
-      <c r="T96" t="inlineStr"/>
+      <c r="S96" t="n">
+        <v>11.1756429</v>
+      </c>
+      <c r="T96" t="n">
+        <v>77.07667840000001</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -6803,8 +7143,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/11%25C2%25B009%2753.2%2522N%2B77%25C2%25B001%2750.1%2522E/%4011.1647682,77.0280024,854m/data%3D!3m2!1e3!4b1!4m4!3m3!8m2!3d11.1647682!4d77.0305773%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MDgxMy4wIPu8ASoASAFQAw%253D%253D%26skid%3De2ee411b-f2f8-4e49-becd-65b4b2e0890a&amp;q=EhAkBQIB4C7guzR74cqdAFF6GNPLy88GIjCrZbB9xPLmLZXcLz7XVkQvCaAjc8nY7qx6-pzu1Z5icOpxH-1gRj8TMtzr2BoJhEUyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S97" t="inlineStr"/>
-      <c r="T97" t="inlineStr"/>
+      <c r="S97" t="n">
+        <v>11.1647682</v>
+      </c>
+      <c r="T97" t="n">
+        <v>77.02800240000001</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -6865,8 +7209,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/11%25C2%25B011%2733.7%2522N%2B77%25C2%25B003%2731.6%2522E/%4011.1926839,77.0562141,854m/data%3D!3m2!1e3!4b1!4m4!3m3!8m2!3d11.1926839!4d77.058789%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MDgxMy4wIPu8ASoASAFQAw%253D%253D%26skid%3D0ad4455d-ac4c-4781-b142-39392846463c&amp;q=EhAkBQIB4C7guzR74cqdAFF6GNXLy88GIjDoY2iDuI5mG-jEymqtQRb7zElgckympfykpdrk5azMcxAGxiXJh1XYWwVY3nK_myEyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S98" t="inlineStr"/>
-      <c r="T98" t="inlineStr"/>
+      <c r="S98" t="n">
+        <v>11.1926839</v>
+      </c>
+      <c r="T98" t="n">
+        <v>77.05621410000001</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -6925,8 +7273,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/11%25C2%25B026%2741.0%2522N%2B76%25C2%25B049%2706.1%2522E/%4011.444716,76.8157961,854m/data%3D!3m2!1e3!4b1!4m4!3m3!8m2!3d11.444716!4d76.818371!5m1!1e1%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MDkxNC4wIPu8ASoASAFQAw%253D%253D%26skid%3Db5900f9a-3fe0-4324-8b76-94a966d3c3c9&amp;q=EhAkBQIB4C7guzR74cqdAFF6GNbLy88GIjBYtxidur44G5oaJQFZtDUnDJK17hOxrDNJwlifonnygT9-fHIdOpUPtcrpeUPpxxEyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S99" t="inlineStr"/>
-      <c r="T99" t="inlineStr"/>
+      <c r="S99" t="n">
+        <v>11.444716</v>
+      </c>
+      <c r="T99" t="n">
+        <v>76.8157961</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -6985,8 +7337,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/11%25C2%25B000%2740.4%2522N%2B76%25C2%25B049%2730.6%2522E/%4011.0112302,76.8225902,855m/data%3D!3m2!1e3!4b1!4m4!3m3!8m2!3d11.0112302!4d76.8251651!5m1!1e1%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MDkxNC4wIPu8ASoASAFQAw%253D%253D%26skid%3D8569f125-4f64-45b8-9f57-b7aaccb0f7fb&amp;q=EhAkBQIB4C7guzR74cqdAFF6GNfLy88GIjAC1mlaLWeW46kvaZnlYC0Kj2rNJfVDVw5cn3iNPApBrGymsMhKDmHcaRX98oKMjqkyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S100" t="inlineStr"/>
-      <c r="T100" t="inlineStr"/>
+      <c r="S100" t="n">
+        <v>11.0112302</v>
+      </c>
+      <c r="T100" t="n">
+        <v>76.82259019999999</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -7045,8 +7401,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/11%25C2%25B007%2700.1%2522N%2B77%25C2%25B009%2735.9%2522E/%4011.1167049,77.1574051,855m/data%3D!3m2!1e3!4b1!4m4!3m3!8m2!3d11.1167049!4d77.15998%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MDgyNS4wIPu8ASoASAFQAw%253D%253D%26skid%3D9ec21741-c72a-46fe-82c1-11e89c0f13e6&amp;q=EhAkBQIB4C7guzR74cqdAFF6GNjLy88GIjCd47oViepF7OBg80PspPAEOyw-WhMrj0STRblpJ5w6-uL5ZFNG1uxDpBERDksbk1YyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S101" t="inlineStr"/>
-      <c r="T101" t="inlineStr"/>
+      <c r="S101" t="n">
+        <v>11.1167049</v>
+      </c>
+      <c r="T101" t="n">
+        <v>77.15740510000001</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -7105,8 +7465,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/11%25C2%25B008%2708.8%2522N%2B77%25C2%25B009%2749.1%2522E/%4011.135767,77.161075,854m/data%3D!3m2!1e3!4b1!4m4!3m3!8m2!3d11.135767!4d77.1636499%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MDgyNS4wIPu8ASoASAFQAw%253D%253D%26skid%3Da9044e4c-9d32-4538-9dc0-eefc586bab81&amp;q=EhAkBQIB4C7guzR74cqdAFF6GNnLy88GIjCC3DsjKH3qfzQQvcpI_cjyOK7PBGBGmobtXqkx-GT4FsEQ_9YOvf3ZXw8pxH62kyYyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S102" t="inlineStr"/>
-      <c r="T102" t="inlineStr"/>
+      <c r="S102" t="n">
+        <v>11.135767</v>
+      </c>
+      <c r="T102" t="n">
+        <v>77.161075</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -7165,8 +7529,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/11%25C2%25B005%2721.4%2522N%2B77%25C2%25B008%2759.9%2522E/%4011.0892834,77.1473886,855m/data%3D!3m2!1e3!4b1!4m4!3m3!8m2!3d11.0892834!4d77.1499635%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MDgyNS4wIPu8ASoASAFQAw%253D%253D%26skid%3D8c36fd82-e722-4506-bf83-039ece810612&amp;q=EhAkBQIB4C7guzR74cqdAFF6GNrLy88GIjDc1pjzBLQo8Tz784XvMTnxowI092EiFjjUL1aj4kTrFDg4FnxG61QYV9ghfwEUVRYyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S103" t="inlineStr"/>
-      <c r="T103" t="inlineStr"/>
+      <c r="S103" t="n">
+        <v>11.0892834</v>
+      </c>
+      <c r="T103" t="n">
+        <v>77.1473886</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -7225,8 +7593,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/11%25C2%25B004%2709.8%2522N%2B77%25C2%25B009%2746.5%2522E/%4011.0693768,77.1603267,855m/data%3D!3m2!1e3!4b1!4m4!3m3!8m2!3d11.0693768!4d77.1629016%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MDgyNS4wIPu8ASoASAFQAw%253D%253D%26skid%3D84c803d9-b682-4c88-95ca-6afb37df6bd0&amp;q=EhAkBQIB4C7guzR74cqdAFF6GNzLy88GIjDYCmam0mnCyC0isW869QKjmGAHZK1H3pK9iyyXg1ON3t9cIaPw-1bV1KhQWK1gvw0yAnJSWgFD</t>
         </is>
       </c>
-      <c r="S104" t="inlineStr"/>
-      <c r="T104" t="inlineStr"/>
+      <c r="S104" t="n">
+        <v>11.0693768</v>
+      </c>
+      <c r="T104" t="n">
+        <v>77.1603267</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -7285,8 +7657,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/11%25C2%25B008%2729.5%2522N%2B77%25C2%25B009%2734.1%2522E/%4011.1415191,77.1569052,854m/data%3D!3m2!1e3!4b1!4m4!3m3!8m2!3d11.1415191!4d77.1594801%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MDgyNS4wIPu8ASoASAFQAw%253D%253D%26skid%3D9d886476-bd29-4da4-8b37-f05c5653f833&amp;q=EhAkBQIB4C7guzR74cqdAFF6GN3Ly88GIjBu3GlUbEWREuhb50HJZHs3-OLpAMuDDUycCXRry0yz-DF9-EByyB3TL5dVKDnNiuwyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S105" t="inlineStr"/>
-      <c r="T105" t="inlineStr"/>
+      <c r="S105" t="n">
+        <v>11.1415191</v>
+      </c>
+      <c r="T105" t="n">
+        <v>77.1569052</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -7345,8 +7721,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/11%25C2%25B005%2716.5%2522N%2B77%25C2%25B010%2718.1%2522E/%4011.0879105,77.1691081,855m/data%3D!3m2!1e3!4b1!4m4!3m3!8m2!3d11.0879105!4d77.171683%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MDgyNS4wIPu8ASoASAFQAw%253D%253D%26skid%3Deac3d5f9-ce8c-40c9-b7a7-a52ee253306e&amp;q=EhAkBQIB4C7guzR74cqdAFF6GN_Ly88GIjBXWFhtzlUNy2MJSJO-H-C-zchjZBKJGUPTu_1Drb7PAUmZnoLe0VHxw9IV2b9fWEgyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S106" t="inlineStr"/>
-      <c r="T106" t="inlineStr"/>
+      <c r="S106" t="n">
+        <v>11.0879105</v>
+      </c>
+      <c r="T106" t="n">
+        <v>77.1691081</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -7405,8 +7785,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/11%25C2%25B005%2709.7%2522N%2B77%25C2%25B010%2701.9%2522E/%4011.0860273,77.164615,855m/data%3D!3m2!1e3!4b1!4m4!3m3!8m2!3d11.0860273!4d77.1671899%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MDgyNS4wIPu8ASoASAFQAw%253D%253D%26skid%3D59aabd9c-35c3-46e6-976a-36c737716e45&amp;q=EhAkBQIB4C7guzR74cqdAFF6GODLy88GIjAtWAexoQQ04oPlslMBdPgWoOZLGTGMhhQ8QGzdAyXmZjIPwnHbaNCIFznJCueGCIgyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S107" t="inlineStr"/>
-      <c r="T107" t="inlineStr"/>
+      <c r="S107" t="n">
+        <v>11.0860273</v>
+      </c>
+      <c r="T107" t="n">
+        <v>77.164615</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -7466,8 +7850,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/10%25C2%25B055%2756.3%2522N%2B77%25C2%25B016%2758.5%2522E/%4010.932312,77.282902,855m/data%3D!3m2!1e3!4b1!4m4!3m3!8m2!3d10.932312!4d77.282902%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MDgyNS4wIPu8ASoASAFQAw%253D%253D%26skid%3D9c8803bb-8473-4298-9263-830d4184fee7&amp;q=EhAkBQIB4C7guzR74cqdAFF6GOLLy88GIjCJ_LZGTeF3asDoCQG2wKvbfGmqQg0UTIMEhFHvFl5OAgKStUtQpwUs47gNp9oatncyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S108" t="inlineStr"/>
-      <c r="T108" t="inlineStr"/>
+      <c r="S108" t="n">
+        <v>10.932312</v>
+      </c>
+      <c r="T108" t="n">
+        <v>77.28290200000001</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -7528,8 +7916,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/10%25C2%25B051%2736.4%2522N%2B76%25C2%25B051%2757.6%2522E/%4010.8601069,76.8634172,855m/data%3D!3m2!1e3!4b1!4m4!3m3!8m2!3d10.8601069!4d76.8659921%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MDgyNS4wIPu8ASoASAFQAw%253D%253D%26skid%3D94fd0119-3305-449f-be7f-ffec4812ca50&amp;q=EhAkBQIB4C7guzR74cqdAFF6GOPLy88GIjALApk_3aLdluEdp9M0jdCv2GKV4s3c8BaAGU6tPoWmqhOf5UIWoaIQlnyceNi6r-8yAnJSWgFD</t>
         </is>
       </c>
-      <c r="S109" t="inlineStr"/>
-      <c r="T109" t="inlineStr"/>
+      <c r="S109" t="n">
+        <v>10.8601069</v>
+      </c>
+      <c r="T109" t="n">
+        <v>76.8634172</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -7586,8 +7978,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/11%25C2%25B012%2745.7%2522N%2B77%25C2%25B002%2724.4%2522E/%4011.212681,77.0375433,854m/data%3D!3m2!1e3!4b1!4m4!3m3!8m2!3d11.212681!4d77.0401182%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MDgyNS4wIPu8ASoASAFQAw%253D%253D%26skid%3D5a5bfff2-0bcd-4286-b873-c01d1eb367b6&amp;q=EhAkBQIB4C7guzR74cqdAFF6GOXLy88GIjAa7EXHt6DCWSSMSg0Fac8m9LRH06L5Rcz4L3CE-rg-NlNEHfVzCuvWBRZ1MedL2EgyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S110" t="inlineStr"/>
-      <c r="T110" t="inlineStr"/>
+      <c r="S110" t="n">
+        <v>11.212681</v>
+      </c>
+      <c r="T110" t="n">
+        <v>77.0375433</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -7646,8 +8042,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/11%25C2%25B000%2711.3%2522N%2B77%25C2%25B001%2708.2%2522E/%4011.0031433,77.0163584,855m/data%3D!3m2!1e3!4b1!4m4!3m3!8m2!3d11.0031433!4d77.0189333%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MDgyNS4wIPu8ASoASAFQAw%253D%253D%26skid%3De4db5ee5-3c71-4ebe-84a7-46f31b333b1e&amp;q=EhAkBQIB4C7guzR74cqdAFF6GObLy88GIjD2BxK3viBHJ2L-wCDVq3IWdWOLfnOUhoxg5zOu7e4wEizhdyF1_OXtJW6zzhIIgMUyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S111" t="inlineStr"/>
-      <c r="T111" t="inlineStr"/>
+      <c r="S111" t="n">
+        <v>11.0031433</v>
+      </c>
+      <c r="T111" t="n">
+        <v>77.0163584</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -7706,8 +8106,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/11%25C2%25B003%2745.8%2522N%2B77%25C2%25B004%2721.3%2522E/%4011.0627101,77.0700158,855m/data%3D!3m2!1e3!4b1!4m4!3m3!8m2!3d11.0627101!4d77.0725907%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MDgyNS4wIPu8ASoASAFQAw%253D%253D%26skid%3D276695e8-c44e-4800-afd7-75da7d12c4cd&amp;q=EhAkBQIB4C7guzR74cqdAFF6GOjLy88GIjCXGJF8pUbM0xUz_dSf2COfTTpSdVnb54FsiY1g5Ekg-jivB2_w-s67YBsF0aelzJAyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S112" t="inlineStr"/>
-      <c r="T112" t="inlineStr"/>
+      <c r="S112" t="n">
+        <v>11.0627101</v>
+      </c>
+      <c r="T112" t="n">
+        <v>77.07001579999999</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -7766,8 +8170,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/11%25C2%25B001%2726.4%2522N%2B77%25C2%25B010%2725.7%2522E/%4011.0239895,77.1712419,855m/data%3D!3m2!1e3!4b1!4m4!3m3!8m2!3d11.0239895!4d77.1738168%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MDgyNS4wIPu8ASoASAFQAw%253D%253D%26skid%3D0989b371-d9df-4e94-a3c7-84c8dd3b4e44&amp;q=EhAkBQIB4C7guzR74cqdAFF6GOnLy88GIjAnCuxd8rsbjIAlqp6GijRgzk5L7C0dYsQ0TK8HxDrDSYKmw8VLV7kExePdiHp9VcUyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S113" t="inlineStr"/>
-      <c r="T113" t="inlineStr"/>
+      <c r="S113" t="n">
+        <v>11.0239895</v>
+      </c>
+      <c r="T113" t="n">
+        <v>77.1712419</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -7824,8 +8232,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/11%25C2%25B006%2708.6%2522N%2B77%25C2%25B002%2714.8%2522E/%4011.1024001,77.0348761,794m/data%3D!3m2!1e3!4b1!4m4!3m3!8m2!3d11.1024001!4d77.037451!5m1!1e1%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MDgyNS4wIPu8ASoASAFQAw%253D%253D%26skid%3De1e5f8c6-7667-4a46-8a0c-efc26f8c95af&amp;q=EhAkBQIB4C7guzR74cqdAFF6GOrLy88GIjBo2ZXtCdtgqBFvMB4vYuPGkAho6PW0YmM2tBOLA-wInEAvk6fRMpik67mMYpjbos4yAnJSWgFD</t>
         </is>
       </c>
-      <c r="S114" t="inlineStr"/>
-      <c r="T114" t="inlineStr"/>
+      <c r="S114" t="n">
+        <v>11.1024001</v>
+      </c>
+      <c r="T114" t="n">
+        <v>77.03487610000001</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -7881,8 +8293,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/11%25C2%25B003%2710.8%2522N%2B76%25C2%25B056%2730.2%2522E/%4011.053,76.9391473,794m/data%3D!3m2!1e3!4b1!4m4!3m3!8m2!3d11.053!4d76.9417222!5m1!1e1%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MDgyNS4wIPu8ASoASAFQAw%253D%253D%26skid%3Dd4fdd889-dd89-44f6-a16f-4158ad8e63f8&amp;q=EhAkBQIB4C7guzR74cqdAFF6GOvLy88GIjB9tz5msczqkLMEgqM7yYKr_TihukRNPXx_WHvVBDqL2_aaHY3chfAOYWbqPU0bCpAyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S115" t="inlineStr"/>
-      <c r="T115" t="inlineStr"/>
+      <c r="S115" t="n">
+        <v>11.053</v>
+      </c>
+      <c r="T115" t="n">
+        <v>76.9391473</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -7937,8 +8353,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/11%25C2%25B003%2760.0%2522N%2B77%25C2%25B006%2714.6%2522E/%4011.0666637,77.1014771,794m/data%3D!3m2!1e3!4b1!4m4!3m3!8m2!3d11.0666637!4d77.104052!5m1!1e1%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MDgyNS4wIPu8ASoASAFQAw%253D%253D%26skid%3D3d8bee52-ef4b-4002-b63f-69a6e60010c5&amp;q=EhAkBQIB4C7guzR74cqdAFF6GOzLy88GIjAOtPxcw7qSKwJUmtkwFeEh0prMlMrg_imIkJYrWrGFra4PQBvU3e5oEMCivhATTZAyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S116" t="inlineStr"/>
-      <c r="T116" t="inlineStr"/>
+      <c r="S116" t="n">
+        <v>11.0666637</v>
+      </c>
+      <c r="T116" t="n">
+        <v>77.1014771</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -7994,8 +8414,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/11%25C2%25B000%2729.6%2522N%2B76%25C2%25B057%2722.4%2522E/%4011.0082197,76.9536412,794m/data%3D!3m2!1e3!4b1!4m4!3m3!8m2!3d11.0082197!4d76.9562161!5m1!1e1%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MDgyNS4wIPu8ASoASAFQAw%253D%253D%26skid%3Dd6e5d6b8-6e48-45cd-adac-44bfc1c45c41&amp;q=EhAkBQIB4C7guzR74cqdAFF6GO3Ly88GIjCYj_LCpl001FToqP4usx5qxehlWrKDuN33FWm8Z7GqIOT5P7ZjZDqOHQDti46b3D0yAnJSWgFD</t>
         </is>
       </c>
-      <c r="S117" t="inlineStr"/>
-      <c r="T117" t="inlineStr"/>
+      <c r="S117" t="n">
+        <v>11.0082197</v>
+      </c>
+      <c r="T117" t="n">
+        <v>76.95364120000001</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -8055,8 +8479,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/11%25C2%25B002%2706.6%2522N%2B77%25C2%25B009%2713.5%2522E/%4011.035162,77.1511812,794m/data%3D!3m2!1e3!4b1!4m4!3m3!8m2!3d11.035162!4d77.1537561!5m1!1e1%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MDgyNS4wIPu8ASoASAFQAw%253D%253D%26skid%3D680cf35b-b56f-4adf-9142-f71b7fb8706a&amp;q=EhAkBQIB4C7guzR74cqdAFF6GO7Ly88GIjAsVgvcPQ_elCKPhaNutt8H68Dnwq_FsuhvPjy0rl-5FDySYQfgu-VfVC5YXZzdzqoyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S118" t="inlineStr"/>
-      <c r="T118" t="inlineStr"/>
+      <c r="S118" t="n">
+        <v>11.035162</v>
+      </c>
+      <c r="T118" t="n">
+        <v>77.1511812</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -8115,8 +8543,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/10%25C2%25B058%2729.6%2522N%2B76%25C2%25B050%2707.7%2522E/%4010.974894,76.8328971,794m/data%3D!3m2!1e3!4b1!4m4!3m3!8m2!3d10.974894!4d76.835472!5m1!1e1%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MDgyNS4wIPu8ASoASAFQAw%253D%253D%26skid%3Db59d92e7-92d3-4d2e-881e-b367233ca221&amp;q=EhAkBQIB4C7guzR74cqdAFF6GO_Ly88GIjDiccKeeEmC7pgILY-9So-VnwrOyWdVYnxVY-7OHUuhzFqBOs0qHLGkqwBb17TZSRgyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S119" t="inlineStr"/>
-      <c r="T119" t="inlineStr"/>
+      <c r="S119" t="n">
+        <v>10.974894</v>
+      </c>
+      <c r="T119" t="n">
+        <v>76.8328971</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -8175,8 +8607,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/10%25C2%25B045%2721.7%2522N%2B77%25C2%25B001%2713.7%2522E/%4010.75603,77.020478,795m/data%3D!3m2!1e3!4b1!4m4!3m3!8m2!3d10.75603!4d77.020478!5m1!1e1%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MDgyNS4wIPu8ASoASAFQAw%253D%253D%26skid%3Db10ffe67-e16f-4099-89d8-62ab92c2297d&amp;q=EhAkBQIB4C7guzR74cqdAFF6GPDLy88GIjDISwXoG6vM3qqdxUwxlj6a2zgmcGTDHYM1Yvu0dqsRAfwLqx7XvyJOwE8OUc_r8hUyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S120" t="inlineStr"/>
-      <c r="T120" t="inlineStr"/>
+      <c r="S120" t="n">
+        <v>10.75603</v>
+      </c>
+      <c r="T120" t="n">
+        <v>77.020478</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -8238,8 +8674,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/Forest%2BTransit%2BHotel%2B%2526%2BService%2BApartment/%4011.0237693,76.9783071,794m/data%3D!3m2!1e3!4b1!4m9!3m8!1s0x3ba859a5779d3809:0x8412b930f3ac7445!5m2!4m1!1i2!8m2!3d11.0237693!4d76.9783071!16s%252Fg%252F11w96tt2gp!5m1!1e1%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MDgyNS4wIPu8ASoASAFQAw%253D%253D%26skid%3Dc0acf08e-2eb0-498f-9b13-c44406577e1d&amp;q=EhAkBQIB4C7guzR74cqdAFF6GPHLy88GIjCsxkLp0Ds9XsOMfESgylx2BNSr11XLtvronbIzgAB0DxWqFUvzJz6KNuqG1myL7dUyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S121" t="inlineStr"/>
-      <c r="T121" t="inlineStr"/>
+      <c r="S121" t="n">
+        <v>11.0237693</v>
+      </c>
+      <c r="T121" t="n">
+        <v>76.97830709999999</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -8300,8 +8740,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/11%25C2%25B001%2718.5%2522N%2B76%25C2%25B057%2751.0%2522E/%4011.021807,76.964163,794m/data%3D!3m2!1e3!4b1!4m4!3m3!8m2!3d11.021807!4d76.964163!5m1!1e1%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MDgyNS4wIPu8ASoASAFQAw%253D%253D%26skid%3D338c7918-6276-4302-b681-bf68ad804b55&amp;q=EhAkBQIB4C7guzR74cqdAFF6GPLLy88GIjDV0vgHSXFlw4K6MP1c2iwFllu7PFNSMUQ98lc-HOhD6d5M2i8ByErPIvKOszVlN1MyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S122" t="inlineStr"/>
-      <c r="T122" t="inlineStr"/>
+      <c r="S122" t="n">
+        <v>11.021807</v>
+      </c>
+      <c r="T122" t="n">
+        <v>76.964163</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -8406,8 +8850,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/11%25C2%25B021%2710.1%2522N%2B76%25C2%25B048%2733.0%2522E/%4011.3528056,76.8091667,854m/data%3D!3m2!1e3!4b1!4m4!3m3!8m2!3d11.3528056!4d76.8091667!5m1!1e1%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MDkzMC4wIPu8ASoASAFQAw%253D%253D%26skid%3Da3414e0e-88ee-4cac-841d-13bcf386a3de&amp;q=EhAkBQIB4C7guzR74cqdAFF6GPPLy88GIjCe8is0Z4IljTxdiP1k1eh0QhQPSHxy83ycHxyu1usjJittpvNWawtQj-gl1-wWcQEyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S124" t="inlineStr"/>
-      <c r="T124" t="inlineStr"/>
+      <c r="S124" t="n">
+        <v>11.3528056</v>
+      </c>
+      <c r="T124" t="n">
+        <v>76.80916670000001</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -8469,8 +8917,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/10%25C2%25B043%2716.3%2522N%2B76%25C2%25B059%2737.4%2522E/%4010.7212048,76.9911537,856m/data%3D!3m2!1e3!4b1!4m4!3m3!8m2!3d10.7212048!4d76.9937286!5m1!1e1%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MDkzMC4wIPu8ASoASAFQAw%253D%253D%26skid%3Ddba902cd-0c48-4fba-8eed-6ae6ae562044&amp;q=EhAkBQIB4C7guzR74cqdAFF6GPXLy88GIjDaEhvhKXhv_zg-1oVAjW-nBNAWGFSg1fYf7oP-herouuD2bk_n4mgp-5OLVWp0iiEyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S125" t="inlineStr"/>
-      <c r="T125" t="inlineStr"/>
+      <c r="S125" t="n">
+        <v>10.7212048</v>
+      </c>
+      <c r="T125" t="n">
+        <v>76.9911537</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -8531,8 +8983,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/11%25C2%25B004%2753.4%2522N%2B77%25C2%25B008%2707.5%2522E/%4011.081499,77.135404,855m/data%3D!3m2!1e3!4b1!4m4!3m3!8m2!3d11.081499!4d77.135404!5m1!1e1%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MDkzMC4wIPu8ASoASAFQAw%253D%253D%26skid%3Df58a6575-6470-4676-8df6-230e669781b6&amp;q=EhAkBQIB4C7guzR74cqdAFF6GPjLy88GIjDk8Oy-uR5MH-7yK2sKN1QhMe6melCf06H5pO4saiSKVsabDxqrsFtiWvBYNNkKM1wyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S126" t="inlineStr"/>
-      <c r="T126" t="inlineStr"/>
+      <c r="S126" t="n">
+        <v>11.081499</v>
+      </c>
+      <c r="T126" t="n">
+        <v>77.13540399999999</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -8594,8 +9050,12 @@
           <t>https://www.google.com/sorry/index?continue=https://maps.google.com/%3Fq%3D11.101858,77.128649%26entry%3Dgps%26g_ep%3DCAESCjExLjU0LjM0MDMYAEICSU4%253D%26shorturl%3D1&amp;q=EhAkBQIB4C7guzR74cqdAFF6GPnLy88GIi3uVLCb6H92fE_CWDcfZSvnxifgR1SKlywU9a4HzMPI9iycNCnxlCPb7DPaO9QyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S127" t="inlineStr"/>
-      <c r="T127" t="inlineStr"/>
+      <c r="S127" t="n">
+        <v>11.101858</v>
+      </c>
+      <c r="T127" t="n">
+        <v>77.128649</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -8708,8 +9168,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/Bogampatti%2B-%2BSithanaickenpalayam%2B-%2BLN%2BPalayam%2BRd,%2BLakshminaickenpalayam,%2BTamil%2BNadu%2B641658/%4010.9242335,77.1424181,855m/data%3D!3m2!1e3!4b1!4m6!3m5!1s0x3ba85250d6eedc91:0x54a9e6af32b10df2!8m2!3d10.9242335!4d77.1424181!16s%252Fg%252F11jn0nkwy7!5m1!1e1%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MTAwMS4wIPu8ASoASAFQAw%253D%253D%26skid%3D3b26ca50-65cb-419b-879c-8235821cab49&amp;q=EhAkBQIB4C7guzR74cqdAFF6GPvLy88GIjDH39yy0CQN7EECoiqQKX7TB0DCbCUZ-ZcF-tQ1wm2P0lSs5f_vxrxbjzEz6982NNYyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S129" t="inlineStr"/>
-      <c r="T129" t="inlineStr"/>
+      <c r="S129" t="n">
+        <v>10.9242335</v>
+      </c>
+      <c r="T129" t="n">
+        <v>77.1424181</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -8768,8 +9232,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/11%25C2%25B011%2702.2%2522N%2B77%25C2%25B000%2722.5%2522E/%4011.1846475,77.0032322,2487m/data%3D!3m1!1e3!4m4!3m3!8m2!3d11.183935!4d77.006244!5m1!1e1%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MTAwMS4wIPu8ASoASAFQAw%253D%253D%26skid%3D6cf225ff-2271-4be8-9402-1884f9e40e1d&amp;q=EhAkBQIB4C7guzR74cqdAFF6GP7Ly88GIjC7V_MH_Ks5GtO6jP2deD2mK879HSC5jqamd4-5FzC6lPASb54hWuggh0GFsDuDrLAyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S130" t="inlineStr"/>
-      <c r="T130" t="inlineStr"/>
+      <c r="S130" t="n">
+        <v>11.1846475</v>
+      </c>
+      <c r="T130" t="n">
+        <v>77.0032322</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -8826,8 +9294,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/11%25C2%25B011%2739.2%2522N%2B77%25C2%25B000%2705.5%2522E/%4011.1942343,76.99895,854m/data%3D!3m2!1e3!4b1!4m4!3m3!8m2!3d11.1942343!4d77.0015249!5m1!1e1%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MTAwMS4wIPu8ASoASAFQAw%253D%253D%26skid%3D21fcd586-338b-4b36-b12b-7a546ab922f9&amp;q=EhAkBQIB4C7guzR74cqdAFF6GIDMy88GIjB0InBWPTn3VfIDdv_q9rjI76luYG_xQEt-ib4efvij-7HNEpgn2WXu8Me4_Kgz8rMyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S131" t="inlineStr"/>
-      <c r="T131" t="inlineStr"/>
+      <c r="S131" t="n">
+        <v>11.1942343</v>
+      </c>
+      <c r="T131" t="n">
+        <v>76.99894999999999</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -8884,8 +9356,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/11%25C2%25B010%2746.2%2522N%2B77%25C2%25B003%2746.8%2522E/%4011.181958,77.0591033,1437m/data%3D!3m1!1e3!4m4!3m3!8m2!3d11.179487!4d77.062985!5m1!1e1%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MTAwMS4wIPu8ASoASAFQAw%253D%253D%26skid%3D2e4e52b7-4353-4f21-a2f9-c0d277771516&amp;q=EhAkBQIB4C7guzR74cqdAFF6GIPMy88GIjCMvzxO_t4oBCrbPL8t_z2hNWQ3sIS9-RPN9sjgh8bOILNTq4sdOHiqtSU-dUJCvbEyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S132" t="inlineStr"/>
-      <c r="T132" t="inlineStr"/>
+      <c r="S132" t="n">
+        <v>11.181958</v>
+      </c>
+      <c r="T132" t="n">
+        <v>77.0591033</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -8940,8 +9416,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/10%25C2%25B055%2706.6%2522N%2B77%25C2%25B009%2738.2%2522E/%4010.919099,77.1569282,1710m/data%3D!3m1!1e3!4m4!3m3!8m2!3d10.91851!4d77.160603!5m1!1e1%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MTAwMS4wIPu8ASoASAFQAw%253D%253D%26skid%3Dcbf1da37-3549-411b-9ef3-209be9cdbf91&amp;q=EhAkBQIB4C7guzR74cqdAFF6GIXMy88GIjAYB7-AUz80GFMmnd6_2Bled4HkrGsPCepQnar6OAAoUMYJ0NLfOTcOBmgJet21zioyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S133" t="inlineStr"/>
-      <c r="T133" t="inlineStr"/>
+      <c r="S133" t="n">
+        <v>10.919099</v>
+      </c>
+      <c r="T133" t="n">
+        <v>77.1569282</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -9002,8 +9482,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/10%25C2%25B055%2724.1%2522N%2B76%25C2%25B059%2707.1%2522E/%4010.9233484,76.9827294,17z/data%3D!3m1!4b1!4m4!3m3!8m2!3d10.9233484!4d76.9853043%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MTAwNy4wIPu8ASoASAFQAw%253D%253D%26skid%3Db5104fe0-04a9-490a-a218-950ac5898f5d&amp;q=EhAkBQIB4C7guzR74cqdAFF6GIbMy88GIjCfi1zeLWQbXIxdJR4ZRw7MYQtgpF6DPnw1IkH5tpRahu2CoiRjWD9PMqrdE4tupQUyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S134" t="inlineStr"/>
-      <c r="T134" t="inlineStr"/>
+      <c r="S134" t="n">
+        <v>10.9233484</v>
+      </c>
+      <c r="T134" t="n">
+        <v>76.9827294</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -9064,8 +9548,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/10%25C2%25B055%2746.8%2522N%2B77%25C2%25B000%2754.5%2522E/%4010.9296576,77.0125606,17z/data%3D!3m1!4b1!4m4!3m3!8m2!3d10.9296576!4d77.0151355%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MTAwNy4wIPu8ASoASAFQAw%253D%253D%26skid%3D837f216c-8eaa-4851-bd8e-ed1c3825b79a&amp;q=EhAkBQIB4C7guzR74cqdAFF6GIjMy88GIjA7atiaS2X0yfC7JQ0FJ5DdKLGmtFitMQXMg3jcIumqh-sll4ZnwWv1390D6ge2f68yAnJSWgFD</t>
         </is>
       </c>
-      <c r="S135" t="inlineStr"/>
-      <c r="T135" t="inlineStr"/>
+      <c r="S135" t="n">
+        <v>10.9296576</v>
+      </c>
+      <c r="T135" t="n">
+        <v>77.0125606</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -9126,8 +9614,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/10%25C2%25B056%2752.0%2522N%2B77%25C2%25B000%2742.3%2522E/%4010.9482521,77.0109632,18.71z/data%3D!4m4!3m3!8m2!3d10.9477658!4d77.0117512%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MTAwNy4wIPu8ASoASAFQAw%253D%253D%26skid%3D4a4641a9-3171-49f4-82d6-f2e7c06b82f1&amp;q=EhAkBQIB4C7guzR74cqdAFF6GIrMy88GIjAt8gBRTe3eg8WObqoFzxPMDu5fbfZOguyDE0WmBvifF0PAN3sZ0veBdmDBEezvklAyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S136" t="inlineStr"/>
-      <c r="T136" t="inlineStr"/>
+      <c r="S136" t="n">
+        <v>10.9482521</v>
+      </c>
+      <c r="T136" t="n">
+        <v>77.01096320000001</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -9257,8 +9749,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/10%25C2%25B057%2706.0%2522N%2B77%25C2%25B007%2757.2%2522E/%4010.9516773,77.1299849,855m/data%3D!3m2!1e3!4b1!4m4!3m3!8m2!3d10.9516773!4d77.1325598!5m1!1e1%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MTEwMi4wIPu8ASoASAFQAw%253D%253D%26skid%3D95cf5f98-018b-4e09-9387-730453e29953&amp;q=EhAkBQIB4C7guzR74cqdAFF6GI3My88GIjBB0MsKgW0Z430erc1hBPJLXgfdjRkio4-wAs4A7war09xnrBH2RWFAnjVOB0-ZqwgyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S138" t="inlineStr"/>
-      <c r="T138" t="inlineStr"/>
+      <c r="S138" t="n">
+        <v>10.9516773</v>
+      </c>
+      <c r="T138" t="n">
+        <v>77.1299849</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -9319,8 +9815,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/11%25C2%25B019%2709.1%2522N%2B77%25C2%25B009%2708.3%2522E/%4011.3191801,77.1497232,854m/data%3D!3m2!1e3!4b1!4m4!3m3!8m2!3d11.3191801!4d77.1522981!5m1!1e1%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MTAwOC4wIPu8ASoASAFQAw%253D%253D%26skid%3Dc2eccdaf-7865-45eb-bda2-b9baa8d48d71&amp;q=EhAkBQIB4C7guzR74cqdAFF6GI7My88GIjBSioRkFcqJLe4D6ImAgJc5_DSBoFYL0LF5CfZkyE3WPjymAq22K3b7TqghKqKIcBIyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S139" t="inlineStr"/>
-      <c r="T139" t="inlineStr"/>
+      <c r="S139" t="n">
+        <v>11.3191801</v>
+      </c>
+      <c r="T139" t="n">
+        <v>77.1497232</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -9381,8 +9881,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/11%25C2%25B004%2758.2%2522N%2B77%25C2%25B001%2738.7%2522E/%4011.0828371,77.0248375,855m/data%3D!3m2!1e3!4b1!4m4!3m3!8m2!3d11.0828371!4d77.0274124!5m1!1e1%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MTAwOC4wIPu8ASoASAFQAw%253D%253D%26skid%3D36b9e301-28ce-4b21-b8b3-4f82aaf7b7db&amp;q=EhAkBQIB4C7guzR74cqdAFF6GJHMy88GIjCy4OEsNny0TJl6rWMsKIOJLCZpv9SzlbRDcKjb0sMJNnztuuPyz493gpTHfREhsGkyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S140" t="inlineStr"/>
-      <c r="T140" t="inlineStr"/>
+      <c r="S140" t="n">
+        <v>11.0828371</v>
+      </c>
+      <c r="T140" t="n">
+        <v>77.0248375</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -9443,8 +9947,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/10%25C2%25B045%2740.0%2522N%2B76%25C2%25B057%2706.4%2522E/%4010.7611135,76.9492015,856m/data%3D!3m2!1e3!4b1!4m4!3m3!8m2!3d10.7611135!4d76.9517764!5m1!1e1%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MTAwOC4wIPu8ASoASAFQAw%253D%253D%26skid%3Dcea05a36-75d3-41f8-a088-9815f344c5b6&amp;q=EhAkBQIB4C7guzR74cqdAFF6GJLMy88GIjA2KXuCx3RRnTQRkipl2MZoro30yjAllubwbG1HRGFrNG92Qs_NCn2iJWu-3NZ_omwyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S141" t="inlineStr"/>
-      <c r="T141" t="inlineStr"/>
+      <c r="S141" t="n">
+        <v>10.7611135</v>
+      </c>
+      <c r="T141" t="n">
+        <v>76.9492015</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -9499,8 +10007,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/11%25C2%25B004%2701.2%2522N%2B77%25C2%25B001%2741.3%2522E/%4011.0670013,77.0255736,807m/data%3D!3m2!1e3!4b1!4m4!3m3!8m2!3d11.0670013!4d77.0281485!5m1!1e1%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MTAwOC4wIPu8ASoASAFQAw%253D%253D%26skid%3D2374e8a7-b480-4264-8219-735f8efd46bc&amp;q=EhAkBQIB4C7guzR74cqdAFF6GJTMy88GIjDTI9j--ssEHfudQTOvKZJF9zjLdXCgTkiYEYF0QDAG4O9Fqz0a2wRMt4voQHNxccMyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S142" t="inlineStr"/>
-      <c r="T142" t="inlineStr"/>
+      <c r="S142" t="n">
+        <v>11.0670013</v>
+      </c>
+      <c r="T142" t="n">
+        <v>77.0255736</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -9559,8 +10071,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/10%25C2%25B057%2746.3%2522N%2B77%25C2%25B010%2755.4%2522E/%4010.9628563,77.179493,855m/data%3D!3m2!1e3!4b1!4m4!3m3!8m2!3d10.9628563!4d77.1820679!5m1!1e1%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MTAxMy4wIPu8ASoASAFQAw%253D%253D%26skid%3D67bf3a89-8763-4274-a67b-7910f57385e1&amp;q=EhAkBQIB4C7guzR74cqdAFF6GJfMy88GIjA7ae66YuqmojPkZuY96pw1EASmBToDreUagyPQVFVA8_lfoEheBTdBThXzrYvqtSkyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S143" t="inlineStr"/>
-      <c r="T143" t="inlineStr"/>
+      <c r="S143" t="n">
+        <v>10.9628563</v>
+      </c>
+      <c r="T143" t="n">
+        <v>77.17949299999999</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -9611,8 +10127,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/10%25C2%25B051%2742.0%2522N%2B76%25C2%25B052%2714.7%2522E/%4010.8616667,76.8681751,855m/data%3D!3m2!1e3!4b1!4m4!3m3!8m2!3d10.8616667!4d76.87075!5m1!1e1%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MTAxMy4wIPu8ASoASAFQAw%253D%253D%26skid%3D7a90e69b-542d-47f5-910c-d86a41fc988b&amp;q=EhAkBQIB4C7guzR74cqdAFF6GJnMy88GIjDASx6zuuW0rnSqmzDQAvXxz0b_Recd0FvVUGJav4eBsfaqt-z2F2wJKAbbPBpqvUoyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S144" t="inlineStr"/>
-      <c r="T144" t="inlineStr"/>
+      <c r="S144" t="n">
+        <v>10.8616667</v>
+      </c>
+      <c r="T144" t="n">
+        <v>76.8681751</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -9671,8 +10191,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/11%25C2%25B005%2714.1%2522N%2B77%25C2%25B002%2744.5%2522E/%4011.087253,77.0431051,855m/data%3D!3m2!1e3!4b1!4m4!3m3!8m2!3d11.087253!4d77.04568!5m1!1e1%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MTAyMi4wIPu8ASoASAFQAw%253D%253D%26skid%3D4985b3fe-84a5-4c42-9275-9df76ffbf922&amp;q=EhAkBQIB4C7guzR74cqdAFF6GJrMy88GIjBAa9sh9u7Z4H1KFgATUOuJlswf95EyVGn9agJQKhYagasPduo8_1KiVXOkDrMBMI4yAnJSWgFD</t>
         </is>
       </c>
-      <c r="S145" t="inlineStr"/>
-      <c r="T145" t="inlineStr"/>
+      <c r="S145" t="n">
+        <v>11.087253</v>
+      </c>
+      <c r="T145" t="n">
+        <v>77.04310510000001</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -10005,8 +10529,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/10%25C2%25B053%2733.4%2522N%2B76%25C2%25B055%2736.0%2522E/%4010.892613,76.9240892,855m/data%3D!3m2!1e3!4b1!4m4!3m3!8m2!3d10.892613!4d76.9266641!5m1!1e1%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MTAyOS4yIPu8ASoASAFQAw%253D%253D%26skid%3Dc8f78b1a-3d3c-418d-9695-6b0d90f1f87a&amp;q=EhAkBQIB4C7guzR74cqdAFF6GKHMy88GIjDrJBttT1FpRKXsXZXY15FR2YnGEZIPUSy3MM2VlfnS4l2zEJGzt0k0XzaUO_olMqoyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S150" t="inlineStr"/>
-      <c r="T150" t="inlineStr"/>
+      <c r="S150" t="n">
+        <v>10.892613</v>
+      </c>
+      <c r="T150" t="n">
+        <v>76.9240892</v>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -10069,8 +10597,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/10%25C2%25B053%2741.9%2522N%2B76%25C2%25B056%2723.2%2522E/%4010.894962,76.939788,855m/data%3D!3m2!1e3!4b1!4m4!3m3!8m2!3d10.894962!4d76.939788!5m1!1e1%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MTAyOS4yIPu8ASoASAFQAw%253D%253D%26skid%3Ddbdca245-75a8-40f5-a050-f6e6eda64db4&amp;q=EhAkBQIB4C7guzR74cqdAFF6GKTMy88GIjDAqpevk7yfnJ42OQw_CK9D8H6jiZoWauok-koW81dnLG7zc0KSgoJ-ReObG4oFxqkyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S151" t="inlineStr"/>
-      <c r="T151" t="inlineStr"/>
+      <c r="S151" t="n">
+        <v>10.894962</v>
+      </c>
+      <c r="T151" t="n">
+        <v>76.93978799999999</v>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -10129,8 +10661,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/11%25C2%25B002%2740.7%2522N%2B77%25C2%25B000%2726.0%2522E/%4011.044647,77.00721,855m/data%3D!3m2!1e3!4b1!4m4!3m3!8m2!3d11.044647!4d77.00721!5m1!1e1%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MTEwMi4wIPu8ASoASAFQAw%253D%253D%26skid%3Dd426cc7a-25cd-4e67-bd21-719145d0feee&amp;q=EhAkBQIB4C7guzR74cqdAFF6GKXMy88GIjDgcFEDTOQBTBQQgcrj_XqMs2MD4J9zEa02kp0bSb4RQ1Ziu2f-RLDjKKSf_msNUrMyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S152" t="inlineStr"/>
-      <c r="T152" t="inlineStr"/>
+      <c r="S152" t="n">
+        <v>11.044647</v>
+      </c>
+      <c r="T152" t="n">
+        <v>77.00721</v>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -10191,8 +10727,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/10%25C2%25B049%2728.9%2522N%2B77%25C2%25B003%2711.6%2522E/%4010.8246944,77.0532222,670m/data%3D!3m2!1e3!4b1!4m4!3m3!8m2!3d10.8246944!4d77.0532222!5m1!1e1%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MTEyMy4xIPu8ASoASAFQAw%253D%253D%26skid%3D8d96ac7b-a26e-45c6-9824-65a561df0af9&amp;q=EhAkBQIB4C7guzR74cqdAFF6GKfMy88GIjBgO9Ugf_mtnnVw9A8Hh8_3DK0Pcj5NDIz4Dj278Uu6SnYUS_ojiVmnPIx4j_uG9H8yAnJSWgFD</t>
         </is>
       </c>
-      <c r="S153" t="inlineStr"/>
-      <c r="T153" t="inlineStr"/>
+      <c r="S153" t="n">
+        <v>10.8246944</v>
+      </c>
+      <c r="T153" t="n">
+        <v>77.05322219999999</v>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -10253,8 +10793,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/11%25C2%25B013%2718.3%2522N%2B77%25C2%25B009%2710.7%2522E/%4011.22175,77.1529722,669m/data%3D!3m2!1e3!4b1!4m4!3m3!8m2!3d11.22175!4d77.1529722!5m1!1e1%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MTEyMy4xIPu8ASoASAFQAw%253D%253D%26skid%3Daffd0fda-8ce2-400d-9f70-2706976917bf&amp;q=EhAkBQIB4C7guzR74cqdAFF6GKjMy88GIjCTY4ZfiVmAWYN4NCpTAYXWH3Gncwkq55oxxikDTL4xNs9EGeqOW32VFn2Ywk_5L1syAnJSWgFD</t>
         </is>
       </c>
-      <c r="S154" t="inlineStr"/>
-      <c r="T154" t="inlineStr"/>
+      <c r="S154" t="n">
+        <v>11.22175</v>
+      </c>
+      <c r="T154" t="n">
+        <v>77.15297219999999</v>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -10315,8 +10859,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/11%25C2%25B007%2723.0%2522N%2B77%25C2%25B011%2759.5%2522E/%4011.1230556,77.1998611,670m/data%3D!3m2!1e3!4b1!4m4!3m3!8m2!3d11.1230556!4d77.1998611!5m1!1e1%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MTEyMy4xIPu8ASoASAFQAw%253D%253D%26skid%3De2462dd5-8319-4fc4-8cb7-3794bf35f9db&amp;q=EhAkBQIB4C7guzR74cqdAFF6GKrMy88GIjDxi3wBpzS_fGhjk7d86ojPTyEghPFQgijS0EcvOAJ8WIbqRlzbMjMRJWvoif4aoi4yAnJSWgFD</t>
         </is>
       </c>
-      <c r="S155" t="inlineStr"/>
-      <c r="T155" t="inlineStr"/>
+      <c r="S155" t="n">
+        <v>11.1230556</v>
+      </c>
+      <c r="T155" t="n">
+        <v>77.19986110000001</v>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -10377,8 +10925,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/11%25C2%25B009%2757.5%2522N%2B77%25C2%25B007%2713.2%2522E/%4011.1670981,77.1234483,5785m/data%3D!3m1!1e3!4m4!3m3!8m2!3d11.1659722!4d77.1203333!5m1!1e1%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MTEyMy4xIPu8ASoASAFQAw%253D%253D%26skid%3Deb0cd7e9-bcbe-4557-b03b-a4988767e51d&amp;q=EhAkBQIB4C7guzR74cqdAFF6GKvMy88GIjATmnk59-YnJeZx1_PkBkdPLAdPupLK4LZzkAeOwDu50EaQvECoicmyOuqaKk1V84AyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S156" t="inlineStr"/>
-      <c r="T156" t="inlineStr"/>
+      <c r="S156" t="n">
+        <v>11.1670981</v>
+      </c>
+      <c r="T156" t="n">
+        <v>77.12344830000001</v>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -10439,8 +10991,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/11%25C2%25B010%2728.8%2522N%2B77%25C2%25B007%2709.9%2522E/%4011.1746667,77.1194167,669m/data%3D!3m2!1e3!4b1!4m4!3m3!8m2!3d11.1746667!4d77.1194167!5m1!1e1%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MTEyMy4xIPu8ASoASAFQAw%253D%253D%26skid%3D5b846a9b-20e5-46db-bbd6-35daea5e68c9&amp;q=EhAkBQIB4C7guzR74cqdAFF6GKzMy88GIjCRgBKkOq6wNFAqWNShntNLqYoxwkSdB4ci9WxRcPO992-T9NYnyZRXh3wGDf351xUyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S157" t="inlineStr"/>
-      <c r="T157" t="inlineStr"/>
+      <c r="S157" t="n">
+        <v>11.1746667</v>
+      </c>
+      <c r="T157" t="n">
+        <v>77.1194167</v>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -10501,8 +11057,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/11%25C2%25B007%2702.4%2522N%2B77%25C2%25B009%2711.8%2522E/%4011.1173333,77.1532778,670m/data%3D!3m2!1e3!4b1!4m4!3m3!8m2!3d11.1173333!4d77.1532778!5m1!1e1%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MTEyMy4xIPu8ASoASAFQAw%253D%253D%26skid%3D766c3d44-c8e7-4f48-8344-b138d254725c&amp;q=EhAkBQIB4C7guzR74cqdAFF6GK7My88GIjBFdUvuRKCnCxfAgyRY-Y_tXPJTV8DuuG8ap-n1Ps_7yeTQVg5SBuYDSgEgUTWUuyQyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S158" t="inlineStr"/>
-      <c r="T158" t="inlineStr"/>
+      <c r="S158" t="n">
+        <v>11.1173333</v>
+      </c>
+      <c r="T158" t="n">
+        <v>77.1532778</v>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -10563,8 +11123,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/11%25C2%25B007%2719.8%2522N%2B77%25C2%25B013%2718.1%2522E/%4011.1221667,77.2216944,670m/data%3D!3m2!1e3!4b1!4m4!3m3!8m2!3d11.1221667!4d77.2216944!5m1!1e1%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MTEyMy4xIPu8ASoASAFQAw%253D%253D%26skid%3Df0ecc832-5eab-438c-a86e-ca076d7d10f1&amp;q=EhAkBQIB4C7guzR74cqdAFF6GK_My88GIjDALJsAcIbD1_GRBLjebMXLIDKot3ias7tUYzUSih5f6tR4xxR88yfk3i4UMULnyNcyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S159" t="inlineStr"/>
-      <c r="T159" t="inlineStr"/>
+      <c r="S159" t="n">
+        <v>11.1221667</v>
+      </c>
+      <c r="T159" t="n">
+        <v>77.2216944</v>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -10625,8 +11189,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/11%25C2%25B007%2710.4%2522N%2B77%25C2%25B012%2744.4%2522E/%4011.1195556,77.2123333,670m/data%3D!3m2!1e3!4b1!4m4!3m3!8m2!3d11.1195556!4d77.2123333!5m1!1e1%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MTEyMy4xIPu8ASoASAFQAw%253D%253D%26skid%3D1fe8ab2d-d11d-416d-b476-fbc5a0d3c78c&amp;q=EhAkBQIB4C7guzR74cqdAFF6GLDMy88GIjANjABk01VKJsFOJWSOlCEkXA33Ah9BQfCWov7pvALuBrBQ8GnDfXWkcwv7Vc1bU-EyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S160" t="inlineStr"/>
-      <c r="T160" t="inlineStr"/>
+      <c r="S160" t="n">
+        <v>11.1195556</v>
+      </c>
+      <c r="T160" t="n">
+        <v>77.2123333</v>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -10687,8 +11255,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/11%25C2%25B012%2722.3%2522N%2B77%25C2%25B008%2719.9%2522E/%4011.2096709,77.1290698,4417m/data%3D!3m1!1e3!4m4!3m3!8m2!3d11.2061944!4d77.1388611!5m1!1e1%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MTEyMy4xIPu8ASoASAFQAw%253D%253D%26skid%3D02485574-9932-4d48-8c75-c81a13e97bc5&amp;q=EhAkBQIB4C7guzR74cqdAFF6GLHMy88GIjDXAlUjEYk0U-IIaq477gub-1aGBsy2UWzgoOe7NfgtbNb7I1Kxu-Vc-Xlvcx0Gl1UyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S161" t="inlineStr"/>
-      <c r="T161" t="inlineStr"/>
+      <c r="S161" t="n">
+        <v>11.2096709</v>
+      </c>
+      <c r="T161" t="n">
+        <v>77.1290698</v>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -10749,8 +11321,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/11%25C2%25B011%2708.4%2522N%2B77%25C2%25B009%2752.1%2522E/%4011.2031368,77.1597938,9916m/data%3D!3m1!1e3!4m4!3m3!8m2!3d11.1856667!4d77.1644722!5m1!1e1%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MTEyMy4xIPu8ASoASAFQAw%253D%253D%26skid%3D75025e65-d4f0-4e22-9526-2a45452f6b67&amp;q=EhAkBQIB4C7guzR74cqdAFF6GLPMy88GIjBoFgu72lJHU6uy6_9EJkS9wtvNsCm5g014R-YWMDbFmJ65Xx1dRyXcpgiGVGp1qzwyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S162" t="inlineStr"/>
-      <c r="T162" t="inlineStr"/>
+      <c r="S162" t="n">
+        <v>11.2031368</v>
+      </c>
+      <c r="T162" t="n">
+        <v>77.1597938</v>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -10869,8 +11445,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/Madukkarai,%2BTamil%2BNadu%2B641032/%4010.8864555,76.9555055,1970m/data%3D!3m1!1e3!4m6!3m5!1s0x3ba85ad5e552bc75:0x774f97acfd4f98db!8m2!3d10.8857202!4d76.9646553!16s%252Fg%252F11jgg1n04x!5m1!1e1%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MTEyMy4xIPu8ASoASAFQAw%253D%253D%26skid%3D530d9766-abce-469c-884b-b93fac05380e&amp;q=EhAkBQIB4C7guzR74cqdAFF6GJjOy88GIjB5zfSumQ8I2v5nZ0jyKLSGXvztLTPCRF7165mx17NGGK-qx9PLVu4f64dSUXuizeUyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S164" t="inlineStr"/>
-      <c r="T164" t="inlineStr"/>
+      <c r="S164" t="n">
+        <v>10.8864555</v>
+      </c>
+      <c r="T164" t="n">
+        <v>76.9555055</v>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -10931,8 +11511,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/11%25C2%25B013%2718.9%2522N%2B77%25C2%25B011%2705.1%2522E/%4011.2179349,77.1445546,9916m/data%3D!3m1!1e3!4m4!3m3!8m2!3d11.2219167!4d77.18475!5m1!1e1%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MTEyMy4xIPu8ASoASAFQAw%253D%253D%26skid%3Db108b1f3-5566-467a-bbc9-d49a4ac536ab&amp;q=EhAkBQIB4C7guzR74cqdAFF6GJrOy88GIjDIq6XhN0iaBmaW8F7_Z12lQz3Tt-rpETTTpd33vQjsyHCUtPD4TM-ccLGA_uHbFWQyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S165" t="inlineStr"/>
-      <c r="T165" t="inlineStr"/>
+      <c r="S165" t="n">
+        <v>11.2179349</v>
+      </c>
+      <c r="T165" t="n">
+        <v>77.14455460000001</v>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -10993,8 +11577,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/10%25C2%25B045%2700.3%2522N%2B77%25C2%25B002%2724.5%2522E/%4010.7538606,77.022827,5793m/data%3D!3m1!1e3!4m4!3m3!8m2!3d10.7500833!4d77.0401389!5m1!1e1%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MTEyMy4xIPu8ASoASAFQAw%253D%253D%26skid%3D5b374024-2ac8-4573-93b5-920cc1181b4d&amp;q=EhAkBQIB4C7guzR74cqdAFF6GJvOy88GIjCXeVY-J1foReufIaX2LtjUaRfYu662lPi87wRO4csMc-j8_wn6UHaUfwP7is-dWc4yAnJSWgFD</t>
         </is>
       </c>
-      <c r="S166" t="inlineStr"/>
-      <c r="T166" t="inlineStr"/>
+      <c r="S166" t="n">
+        <v>10.7538606</v>
+      </c>
+      <c r="T166" t="n">
+        <v>77.02282700000001</v>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -11055,8 +11643,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/10%25C2%25B044%2734.0%2522N%2B77%25C2%25B003%2710.1%2522E/%4010.7448434,77.0451705,7585m/data%3D!3m1!1e3!4m4!3m3!8m2!3d10.7427778!4d77.0528056!5m1!1e1%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MTEyMy4xIPu8ASoASAFQAw%253D%253D%26skid%3Dea70d2c1-a354-457b-9dc8-1b97505bcb16&amp;q=EhAkBQIB4C7guzR74cqdAFF6GJ3Oy88GIjDwnALATyvPoXdB5xOX8KvfJDxjKmDVVZ7l-Fc6nU_zQrj0KTt9oyTTVJfa6pBxIogyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S167" t="inlineStr"/>
-      <c r="T167" t="inlineStr"/>
+      <c r="S167" t="n">
+        <v>10.7448434</v>
+      </c>
+      <c r="T167" t="n">
+        <v>77.0451705</v>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
@@ -11117,8 +11709,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/10%25C2%25B049%2747.8%2522N%2B77%25C2%25B002%2743.1%2522E/%4010.8513835,77.0342346,17022m/data%3D!3m1!1e3!4m4!3m3!8m2!3d10.8299444!4d77.0453056!5m1!1e1%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MTEyMy4xIPu8ASoASAFQAw%253D%253D%26skid%3D5df067d1-2b37-488e-b526-5ecdca45621c&amp;q=EhAkBQIB4C7guzR74cqdAFF6GJ_Oy88GIjBcr8S31komVtQFzBv3Z3-axAhj6av5lk03BNmeBpQpRv3N8C_drwfRDcq7mvNzYE8yAnJSWgFD</t>
         </is>
       </c>
-      <c r="S168" t="inlineStr"/>
-      <c r="T168" t="inlineStr"/>
+      <c r="S168" t="n">
+        <v>10.8513835</v>
+      </c>
+      <c r="T168" t="n">
+        <v>77.0342346</v>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
@@ -11179,8 +11775,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/10%25C2%25B050%2707.8%2522N%2B77%25C2%25B002%2729.7%2522E/%4010.8354524,77.0413733,878m/data%3D!3m1!1e3!4m4!3m3!8m2!3d10.8355!4d77.0415833!5m1!1e1%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MTEyMy4xIPu8ASoASAFQAw%253D%253D%26skid%3D686d8ee5-8555-4274-8125-f46dc1e1d8c3&amp;q=EhAkBQIB4C7guzR74cqdAFF6GKHOy88GIjB7GVaSpO13E1vcm-Troi2Myq5PGwXb1vwahRHFNGMdIOWebDtbjCIyKVSZ5zEP4dkyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S169" t="inlineStr"/>
-      <c r="T169" t="inlineStr"/>
+      <c r="S169" t="n">
+        <v>10.8354524</v>
+      </c>
+      <c r="T169" t="n">
+        <v>77.0413733</v>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
@@ -11241,8 +11841,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/10%25C2%25B050%2756.5%2522N%2B77%25C2%25B005%2704.2%2522E/%4010.8503796,77.0699689,5791m/data%3D!3m1!1e3!4m4!3m3!8m2!3d10.8490278!4d77.0845!5m1!1e1%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MTEyMy4xIPu8ASoASAFQAw%253D%253D%26skid%3D6af6c84a-4f97-4a28-8fcd-ad2c05c6f4fe&amp;q=EhAkBQIB4C7guzR74cqdAFF6GKPOy88GIjAJrJzoixNlmsYpbrJkFDzTL5fY9BUhyKHq-rFCmdByR-gBuYpJlmTsI1L2s4wcIDsyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S170" t="inlineStr"/>
-      <c r="T170" t="inlineStr"/>
+      <c r="S170" t="n">
+        <v>10.8503796</v>
+      </c>
+      <c r="T170" t="n">
+        <v>77.06996890000001</v>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
@@ -11303,8 +11907,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/11%25C2%25B004%2718.3%2522N%2B77%25C2%25B007%2757.1%2522E/%4011.0743745,77.1192799,2578m/data%3D!3m1!1e3!4m4!3m3!8m2!3d11.07175!4d77.1325278!5m1!1e1%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MTEyMy4xIPu8ASoASAFQAw%253D%253D%26skid%3D3e2a92f0-6b57-4a24-ae76-073f165c3d96&amp;q=EhAkBQIB4C7guzR74cqdAFF6GKTOy88GIjAtnWWbOelSFK66YkujYL6lx1cS6kCDH1pbYpcYxB9Wbmoi2IKKlHg2xNPSjlsKxI8yAnJSWgFD</t>
         </is>
       </c>
-      <c r="S171" t="inlineStr"/>
-      <c r="T171" t="inlineStr"/>
+      <c r="S171" t="n">
+        <v>11.0743745</v>
+      </c>
+      <c r="T171" t="n">
+        <v>77.1192799</v>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
@@ -11365,8 +11973,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/10%25C2%25B048%2707.2%2522N%2B77%25C2%25B001%2749.6%2522E/%4010.807382,77.015357,5792m/data%3D!3m1!1e3!4m4!3m3!8m2!3d10.802!4d77.0304444!5m1!1e1%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MTEyMy4xIPu8ASoASAFQAw%253D%253D%26skid%3Dfb2af716-07bf-4e82-ac80-0707ad1acc6a&amp;q=EhAkBQIB4C7guzR74cqdAFF6GKbOy88GIjCKpW7gR9bf8OIQOcD7Jam1IHJbiWy__Dnonmhaozljo2g34dMxzW47poAvhgV7vMUyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S172" t="inlineStr"/>
-      <c r="T172" t="inlineStr"/>
+      <c r="S172" t="n">
+        <v>10.807382</v>
+      </c>
+      <c r="T172" t="n">
+        <v>77.01535699999999</v>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
@@ -11427,8 +12039,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/11%25C2%25B013%2718.3%2522N%2B77%25C2%25B009%2710.7%2522E/%4011.2378649,77.1347022,21418m/data%3D!3m1!1e3!4m4!3m3!8m2!3d11.22175!4d77.1529722!5m1!1e1%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MTEyMy4xIPu8ASoASAFQAw%253D%253D%26skid%3De98b0c33-93d8-42d9-bac3-0b5d41e2e644&amp;q=EhAkBQIB4C7guzR74cqdAFF6GKfOy88GIjCx-EQtB88Dke0GHGfAJIOF9E9hS6MgQFurSvALhDM4AfqIV1N4DFERsxFRRpFiouoyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S173" t="inlineStr"/>
-      <c r="T173" t="inlineStr"/>
+      <c r="S173" t="n">
+        <v>11.2378649</v>
+      </c>
+      <c r="T173" t="n">
+        <v>77.13470220000001</v>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
@@ -11489,8 +12105,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/10%25C2%25B053%2726.2%2522N%2B77%25C2%25B002%2704.8%2522E/%4010.8961831,77.0320806,7581m/data%3D!3m1!1e3!4m4!3m3!8m2!3d10.8906111!4d77.0346667!5m1!1e1%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MTEyMy4xIPu8ASoASAFQAw%253D%253D%26skid%3D2269ed86-261c-4fb2-a97b-1259de819704&amp;q=EhAkBQIB4C7guzR74cqdAFF6GKrOy88GIjCYza5WxrTe20N8gJOKaWYZjOZOUeez2vjOBTxU_6mDx2i2nuN6G9LFrWFsj96bRI0yAnJSWgFD</t>
         </is>
       </c>
-      <c r="S174" t="inlineStr"/>
-      <c r="T174" t="inlineStr"/>
+      <c r="S174" t="n">
+        <v>10.8961831</v>
+      </c>
+      <c r="T174" t="n">
+        <v>77.0320806</v>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
@@ -11551,8 +12171,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/11%25C2%25B016%2709.6%2522N%2B77%25C2%25B015%2707.1%2522E/%4011.2790885,77.2153249,16997m/data%3D!3m1!1e3!4m4!3m3!8m2!3d11.2693333!4d77.2519722!5m1!1e1%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MTEyMy4xIPu8ASoASAFQAw%253D%253D%26skid%3Dc2ca6f84-e79e-463a-a4fc-4299964763b7&amp;q=EhAkBQIB4C7guzR74cqdAFF6GKvOy88GIjCdnjCgZE3Em5M8eGI1sYr9DQe6ujmJUx9xx3l1RVzy0qp5x_RrMkiBLjrwKTTdDUIyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S175" t="inlineStr"/>
-      <c r="T175" t="inlineStr"/>
+      <c r="S175" t="n">
+        <v>11.2790885</v>
+      </c>
+      <c r="T175" t="n">
+        <v>77.2153249</v>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
@@ -11613,8 +12237,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/11%25C2%25B017%2743.9%2522N%2B77%25C2%25B010%2720.3%2522E/%4011.3237067,77.1773857,16994m/data%3D!3m1!1e3!4m4!3m3!8m2!3d11.2955278!4d77.1723056!5m1!1e1%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MTEyMy4xIPu8ASoASAFQAw%253D%253D%26skid%3De224a7cf-1e67-4994-9ff0-23845f3155b0&amp;q=EhAkBQIB4C7guzR74cqdAFF6GKzOy88GIjD7IZn73Wfx5YUMippbL559vMNtWVOLRpX79A25G2Cfp8VE3_zc7n9fbvmGVPbNkPEyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S176" t="inlineStr"/>
-      <c r="T176" t="inlineStr"/>
+      <c r="S176" t="n">
+        <v>11.3237067</v>
+      </c>
+      <c r="T176" t="n">
+        <v>77.1773857</v>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
@@ -11675,8 +12303,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/10%25C2%25B054%2710.7%2522N%2B77%25C2%25B001%2738.5%2522E/%4010.9054195,77.0253828,1970m/data%3D!3m1!1e3!4m4!3m3!8m2!3d10.9029722!4d77.0273611!5m1!1e1%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MTEyMy4xIPu8ASoASAFQAw%253D%253D%26skid%3Dda1e74df-8282-4049-86bb-044b492341e7&amp;q=EhAkBQIB4C7guzR74cqdAFF6GK3Oy88GIjDPUPBMIY2Gw6MPGQADTXlc7nNHzbxtqFPf_3I9GgwkEBHsd_WAoUaJVde5lgNDJMwyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S177" t="inlineStr"/>
-      <c r="T177" t="inlineStr"/>
+      <c r="S177" t="n">
+        <v>10.9054195</v>
+      </c>
+      <c r="T177" t="n">
+        <v>77.0253828</v>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
@@ -11737,8 +12369,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/10%25C2%25B051%2740.7%2522N%2B77%25C2%25B004%2727.1%2522E/%4010.864017,77.056041,4422m/data%3D!3m1!1e3!4m4!3m3!8m2!3d10.8613056!4d77.0741944!5m1!1e1%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MTEyMy4xIPu8ASoASAFQAw%253D%253D%26skid%3Db1afce3a-11d0-4d2f-910c-cf815c36b3f4&amp;q=EhAkBQIB4C7guzR74cqdAFF6GLDOy88GIjA6lGnN3oBTLW8FZj4zTkuP8AjcG-onrReE64cOfBjbuV2NVSdtkwcL9UoAjhki9GMyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S178" t="inlineStr"/>
-      <c r="T178" t="inlineStr"/>
+      <c r="S178" t="n">
+        <v>10.864017</v>
+      </c>
+      <c r="T178" t="n">
+        <v>77.05604099999999</v>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
@@ -11799,8 +12435,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/11%25C2%25B015%2709.5%2522N%2B77%25C2%25B010%2716.1%2522E/%4011.1352789,77.0453639,65452m/data%3D!3m1!1e3!4m4!3m3!8m2!3d11.2526389!4d77.1711389!5m1!1e1%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MTEyMy4xIPu8ASoASAFQAw%253D%253D%26skid%3D2108131d-f503-4f0c-8c39-152968b052e7&amp;q=EhAkBQIB4C7guzR74cqdAFF6GLLOy88GIjDcvRCxL3CixNCIdEobKW6jzWt5un7pr7jx-fGYHS44Kn8rhblR6enCsdmQZK-3X5QyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S179" t="inlineStr"/>
-      <c r="T179" t="inlineStr"/>
+      <c r="S179" t="n">
+        <v>11.1352789</v>
+      </c>
+      <c r="T179" t="n">
+        <v>77.0453639</v>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
@@ -11861,8 +12501,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/11%25C2%25B013%2750.6%2522N%2B77%25C2%25B010%2722.0%2522E/%4011.207748,77.1576003,22261m/data%3D!3m1!1e3!4m4!3m3!8m2!3d11.2307222!4d77.1727778!5m1!1e1%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MTEyMy4xIPu8ASoASAFQAw%253D%253D%26skid%3Dd7c1b657-e15b-47bb-ae38-a093d06e1e5e&amp;q=EhAkBQIB4C7guzR74cqdAFF6GLPOy88GIjD_HUKMGGN-MHZTa-6MBp-W7s-7Icc8DcA_s0aUg3pwX5IjUUYvUPVhe0-LTD18KIIyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S180" t="inlineStr"/>
-      <c r="T180" t="inlineStr"/>
+      <c r="S180" t="n">
+        <v>11.207748</v>
+      </c>
+      <c r="T180" t="n">
+        <v>77.1576003</v>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
@@ -11923,8 +12567,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/10%25C2%25B058%2718.9%2522N%2B77%25C2%25B007%2722.3%2522E/%4010.9677862,77.1207288,2578m/data%3D!3m1!1e3!4m4!3m3!8m2!3d10.9719167!4d77.1228611!5m1!1e1%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MTEyMy4xIPu8ASoASAFQAw%253D%253D%26skid%3D838130d7-8e0c-4e68-88b0-e0ebbdc7818e&amp;q=EhAkBQIB4C7guzR74cqdAFF6GLXOy88GIjAuc6a0-HioBgtUI_p9YRN-ygGY3OvlYNgmfe7xnCDY_rpqUmcXCNZMweY_RC81_doyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S181" t="inlineStr"/>
-      <c r="T181" t="inlineStr"/>
+      <c r="S181" t="n">
+        <v>10.9677862</v>
+      </c>
+      <c r="T181" t="n">
+        <v>77.12072879999999</v>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
@@ -11985,8 +12633,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/11%25C2%25B003%2729.3%2522N%2B77%25C2%25B004%2739.6%2522E/%4011.0579276,77.0756808,1148m/data%3D!3m1!1e3!4m4!3m3!8m2!3d11.0581389!4d77.0776667!5m1!1e1%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MTEyMy4xIPu8ASoASAFQAw%253D%253D%26skid%3D14d37026-45c6-4a34-b245-8279899b302a&amp;q=EhAkBQIB4C7guzR74cqdAFF6GLbOy88GIjDmSgdKxOtQNf-z_1mbkdj4rE62uLCOvREGEPFXUY4I6qJOX9H8OYrCfS5dqXE6GkQyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S182" t="inlineStr"/>
-      <c r="T182" t="inlineStr"/>
+      <c r="S182" t="n">
+        <v>11.0579276</v>
+      </c>
+      <c r="T182" t="n">
+        <v>77.0756808</v>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
@@ -12051,8 +12703,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/11%25C2%25B011%2746.2%2522N%2B77%25C2%25B008%2701.8%2522E/%4011.1954161,77.1340109,521m/data%3D!3m1!1e3!4m4!3m3!8m2!3d11.1961667!4d77.1338333!5m1!1e1%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MTEyMy4xIPu8ASoASAFQAw%253D%253D%26skid%3D74bb974e-42d9-4194-a04f-f92baca39780&amp;q=EhAkBQIB4C7guzR74cqdAFF6GLfOy88GIjCkAghopnsTq7NSoQTyRACamLyw50PmYq5K0ChQa8uzyTRoT5ZDjWs4XhnN5rDJc5kyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S183" t="inlineStr"/>
-      <c r="T183" t="inlineStr"/>
+      <c r="S183" t="n">
+        <v>11.1954161</v>
+      </c>
+      <c r="T183" t="n">
+        <v>77.13401090000001</v>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
@@ -12113,8 +12769,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/11%25C2%25B010%2736.3%2522N%2B77%25C2%25B004%2757.4%2522E/%4011.1782755,77.0785459,2577m/data%3D!3m1!1e3!4m4!3m3!8m2!3d11.17675!4d77.0826111!5m1!1e1%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MTEyMy4xIPu8ASoASAFQAw%253D%253D%26skid%3D54e43f27-4c22-401b-88fe-bcff96ce8ed5&amp;q=EhAkBQIB4C7guzR74cqdAFF6GLjOy88GIjA18j_sAbdJ0w5pvLg1rSVQKlH83PGTLkk3Se_fvChKQ3EKjWe5wEhPRVeNqLUO9OAyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S184" t="inlineStr"/>
-      <c r="T184" t="inlineStr"/>
+      <c r="S184" t="n">
+        <v>11.1782755</v>
+      </c>
+      <c r="T184" t="n">
+        <v>77.07854589999999</v>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
@@ -12175,8 +12835,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/11%25C2%25B012%2700.2%2522N%2B77%25C2%25B010%2702.7%2522E/%4011.1934929,77.157592,3374m/data%3D!3m1!1e3!4m4!3m3!8m2!3d11.2000556!4d77.1674167!5m1!1e1%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MTEyMy4xIPu8ASoASAFQAw%253D%253D%26skid%3D5a33e51e-0f7b-41be-b57a-2a52852dfc84&amp;q=EhAkBQIB4C7guzR74cqdAFF6GLnOy88GIjBDCV6hKvfSHThkA_JgWAqALqFUkQymemjYY-N00E7OaeTXZKnkjhUqheToPQdqzMkyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S185" t="inlineStr"/>
-      <c r="T185" t="inlineStr"/>
+      <c r="S185" t="n">
+        <v>11.1934929</v>
+      </c>
+      <c r="T185" t="n">
+        <v>77.15759199999999</v>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
@@ -12237,8 +12901,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/11%25C2%25B013%2745.4%2522N%2B77%25C2%25B013%2706.2%2522E/%4011.2383809,77.217738,9915m/data%3D!3m1!1e3!4m4!3m3!8m2!3d11.2292778!4d77.2183889!5m1!1e1%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MTEyMy4xIPu8ASoASAFQAw%253D%253D%26skid%3D55543dc9-2094-49a9-8b19-2934717dcd38&amp;q=EhAkBQIB4C7guzR74cqdAFF6GLrOy88GIjB96bAuTEMiYC8-sb2hpUmsfMj1skH3Vtaf3UgKgXGizpAzk8K3Ib9_YlfVlFz8sSIyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S186" t="inlineStr"/>
-      <c r="T186" t="inlineStr"/>
+      <c r="S186" t="n">
+        <v>11.2383809</v>
+      </c>
+      <c r="T186" t="n">
+        <v>77.217738</v>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
@@ -12299,8 +12967,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/11%25C2%25B011%2748.8%2522N%2B77%25C2%25B009%2736.4%2522E/%4011.188422,77.1500207,7574m/data%3D!3m1!1e3!4m4!3m3!8m2!3d11.1968889!4d77.1601111!5m1!1e1%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MTEyMy4xIPu8ASoASAFQAw%253D%253D%26skid%3D45603f18-a6e4-45f0-afdd-b9a827cbcfd6&amp;q=EhAkBQIB4C7guzR74cqdAFF6GLzOy88GIjDt9Xcn138Ogm-625hWd4E3tOazfm0gR5Qn5tUWKncRY6o1rATw_sI4H8mAom4wW00yAnJSWgFD</t>
         </is>
       </c>
-      <c r="S187" t="inlineStr"/>
-      <c r="T187" t="inlineStr"/>
+      <c r="S187" t="n">
+        <v>11.188422</v>
+      </c>
+      <c r="T187" t="n">
+        <v>77.1500207</v>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
@@ -12361,8 +13033,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/10%25C2%25B050%2730.0%2522N%2B77%25C2%25B001%2731.1%2522E/%4010.8418123,77.0161167,9929m/data%3D!3m1!1e3!4m4!3m3!8m2!3d10.8416667!4d77.0253056!5m1!1e1%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MTEyMy4xIPu8ASoASAFQAw%253D%253D%26skid%3Df9327613-c0b6-4fe2-b7bb-7abfa1ffeecc&amp;q=EhAkBQIB4C7guzR74cqdAFF6GL3Oy88GIjAygiD4eU3XKNbOxiCjdZCGBlOHF8beORis6h8BGBNwWTi8hUR2S9k0SlawRv2FNoAyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S188" t="inlineStr"/>
-      <c r="T188" t="inlineStr"/>
+      <c r="S188" t="n">
+        <v>10.8418123</v>
+      </c>
+      <c r="T188" t="n">
+        <v>77.0161167</v>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
@@ -12423,8 +13099,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/11%25C2%25B017%2747.7%2522N%2B77%25C2%25B011%2729.4%2522E/%4011.3144293,77.1629941,14996m/data%3D!3m1!1e3!4m4!3m3!8m2!3d11.2965833!4d77.1915!5m1!1e1%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MTEyMy4xIPu8ASoASAFQAw%253D%253D%26skid%3D4ccdc30d-1864-41b2-8977-24874de4a26d&amp;q=EhAkBQIB4C7guzR74cqdAFF6GL_Oy88GIjBR-JBkTwjbt9xJxdHuJSC7PLKW_YN-Yh3VbKPMsKRFGJmzouJ1OZhecugXO8YIMFUyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S189" t="inlineStr"/>
-      <c r="T189" t="inlineStr"/>
+      <c r="S189" t="n">
+        <v>11.3144293</v>
+      </c>
+      <c r="T189" t="n">
+        <v>77.16299410000001</v>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
@@ -12485,8 +13165,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/11%25C2%25B009%2709.2%2522N%2B77%25C2%25B008%2750.6%2522E/%4011.1532784,77.1436744,4418m/data%3D!3m1!1e3!4m4!3m3!8m2!3d11.1525556!4d77.1473889!5m1!1e1%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MTEyMy4xIPu8ASoASAFQAw%253D%253D%26skid%3D2ac5499e-39a0-44d5-bc97-4d7a81028eea&amp;q=EhAkBQIB4C7guzR74cqdAFF6GMDOy88GIjCQ4DDDIY0wTpLufl2rzljoHdltfcT5FV_WiK261vlxT3YfkFtExyfYy9woMQQQbn0yAnJSWgFD</t>
         </is>
       </c>
-      <c r="S190" t="inlineStr"/>
-      <c r="T190" t="inlineStr"/>
+      <c r="S190" t="n">
+        <v>11.1532784</v>
+      </c>
+      <c r="T190" t="n">
+        <v>77.14367439999999</v>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
@@ -12547,8 +13231,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/11%25C2%25B011%2755.8%2522N%2B77%25C2%25B007%2757.5%2522E/%4011.2037764,77.141235,9916m/data%3D!3m1!1e3!4m4!3m3!8m2!3d11.1988333!4d77.1326389!5m1!1e1%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MTEyMy4xIPu8ASoASAFQAw%253D%253D%26skid%3D7ec35428-5382-43a8-92a3-2d2e8e9c9109&amp;q=EhAkBQIB4C7guzR74cqdAFF6GMLOy88GIjB2XPL9mf1rj6IaupFVQJEcKsOb9R8glPEQIdodFWVOt0ASSI6vUydeWpYBpOlCYUAyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S191" t="inlineStr"/>
-      <c r="T191" t="inlineStr"/>
+      <c r="S191" t="n">
+        <v>11.2037764</v>
+      </c>
+      <c r="T191" t="n">
+        <v>77.14123499999999</v>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
@@ -12609,8 +13297,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/10%25C2%25B054%2733.0%2522N%2B77%25C2%25B003%2720.5%2522E/%4010.9080592,77.0459144,1504m/data%3D!3m1!1e3!4m4!3m3!8m2!3d10.9091667!4d77.0556944!5m1!1e1%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MTEyMy4xIPu8ASoASAFQAw%253D%253D%26skid%3D2bf3518d-b47c-4be1-9789-1ad7f67a3970&amp;q=EhAkBQIB4C7guzR74cqdAFF6GMPOy88GIjDdYSfadHj6B6WVzrenUBsCLmlPYyYM1-urYp2B5gYbqVt9iTSBhZTuPW1e4hNohtcyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S192" t="inlineStr"/>
-      <c r="T192" t="inlineStr"/>
+      <c r="S192" t="n">
+        <v>10.9080592</v>
+      </c>
+      <c r="T192" t="n">
+        <v>77.0459144</v>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
@@ -12671,8 +13363,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/10%25C2%25B051%2722.1%2522N%2B77%25C2%25B005%2721.2%2522E/%4010.8669461,77.0884338,12999m/data%3D!3m1!1e3!4m4!3m3!8m2!3d10.8561389!4d77.0892222!5m1!1e1%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MTEyMy4xIPu8ASoASAFQAw%253D%253D%26skid%3Db255657a-9fe8-4315-9bfa-baf856800809&amp;q=EhAkBQIB4C7guzR74cqdAFF6GMTOy88GIjDxcb7QhxTcRtYZl5ZdRYFnrMwc5NjVKgpJwVDlrFF4t9dCDpUG1XP5Z5I-5TtlQFwyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S193" t="inlineStr"/>
-      <c r="T193" t="inlineStr"/>
+      <c r="S193" t="n">
+        <v>10.8669461</v>
+      </c>
+      <c r="T193" t="n">
+        <v>77.0884338</v>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
@@ -12733,8 +13429,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/11%25C2%25B016%2734.2%2522N%2B77%25C2%25B015%2702.5%2522E/%4011.3169839,77.2401032,29137m/data%3D!3m1!1e3!4m4!3m3!8m2!3d11.2761667!4d77.2506944!5m1!1e1%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MTEyMy4xIPu8ASoASAFQAw%253D%253D%26skid%3Dc57877d3-2905-4b36-93f9-86a03088b334&amp;q=EhAkBQIB4C7guzR74cqdAFF6GMXOy88GIjCrJ3xtX_KERE6xnFrtiTKkVrBgVYKr2F7Dik3G26bPl4VcKe-N6di9qeZ9Kp10qH8yAnJSWgFD</t>
         </is>
       </c>
-      <c r="S194" t="inlineStr"/>
-      <c r="T194" t="inlineStr"/>
+      <c r="S194" t="n">
+        <v>11.3169839</v>
+      </c>
+      <c r="T194" t="n">
+        <v>77.24010319999999</v>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
@@ -12795,8 +13495,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/11%25C2%25B013%2702.6%2522N%2B77%25C2%25B007%2742.9%2522E/%4011.2190013,77.1264817,1968m/data%3D!3m1!1e3!4m4!3m3!8m2!3d11.2173889!4d77.1285833!5m1!1e1%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MTEyMy4xIPu8ASoASAFQAw%253D%253D%26skid%3D5b1f0e7b-aef5-4ea3-bff8-ae8a826b1c85&amp;q=EhAkBQIB4C7guzR74cqdAFF6GMfOy88GIjDiHOi3sP8lCFFIuxCw1m7-BBR7TEDQS9H83HpsZYpQ1wndveq5nPBMPWePUx_knaIyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S195" t="inlineStr"/>
-      <c r="T195" t="inlineStr"/>
+      <c r="S195" t="n">
+        <v>11.2190013</v>
+      </c>
+      <c r="T195" t="n">
+        <v>77.1264817</v>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
@@ -12857,8 +13561,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/10%25C2%25B052%2749.1%2522N%2B77%25C2%25B008%2715.9%2522E/%4010.8799114,77.1021111,5790m/data%3D!3m1!1e3!4m4!3m3!8m2!3d10.8803056!4d77.13775!5m1!1e1%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MTEyMy4xIPu8ASoASAFQAw%253D%253D%26skid%3Dc6d74c89-6365-427a-8580-bcef06030e2b&amp;q=EhAkBQIB4C7guzR74cqdAFF6GMnOy88GIjBfjHgyjhFgA8H9GQNyLpG1673TtjtepCGxBeq66lqF37V-UBG3gBzVmTJgyau_hzAyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S196" t="inlineStr"/>
-      <c r="T196" t="inlineStr"/>
+      <c r="S196" t="n">
+        <v>10.8799114</v>
+      </c>
+      <c r="T196" t="n">
+        <v>77.1021111</v>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
@@ -12919,8 +13627,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/11%25C2%25B016%2724.9%2522N%2B77%25C2%25B010%2749.7%2522E/%4011.2736618,77.1885764,12981m/data%3D!3m1!1e3!4m4!3m3!8m2!3d11.2735833!4d77.1804722!5m1!1e1%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MTEyMy4xIPu8ASoASAFQAw%253D%253D%26skid%3D7d32a745-2299-480d-a2e0-27697c82cdb7&amp;q=EhAkBQIB4C7guzR74cqdAFF6GMrOy88GIjCllDbDbWuXG1oNOEWmR0F2NR4c32EfVYwh0uxr47Qt2s5mSUkTGo6I1ZQHUydzT90yAnJSWgFD</t>
         </is>
       </c>
-      <c r="S197" t="inlineStr"/>
-      <c r="T197" t="inlineStr"/>
+      <c r="S197" t="n">
+        <v>11.2736618</v>
+      </c>
+      <c r="T197" t="n">
+        <v>77.1885764</v>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
@@ -12981,8 +13693,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/11%25C2%25B009%2750.2%2522N%2B77%25C2%25B008%2712.8%2522E/%4011.1573438,77.1135819,4418m/data%3D!3m1!1e3!4m4!3m3!8m2!3d11.1639444!4d77.1368889!5m1!1e1%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MTEyMy4xIPu8ASoASAFQAw%253D%253D%26skid%3D242a5692-f3bc-4c6e-94f9-93c7a7fba7b5&amp;q=EhAkBQIB4C7guzR74cqdAFF6GMvOy88GIjBRpoZ0LiQZI--Zodyv-EvZzuuuIZj2N7y3kHaBRFiScdeQ1CuprO7Hked55KIy_3wyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S198" t="inlineStr"/>
-      <c r="T198" t="inlineStr"/>
+      <c r="S198" t="n">
+        <v>11.1573438</v>
+      </c>
+      <c r="T198" t="n">
+        <v>77.1135819</v>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
@@ -13043,8 +13759,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/10%25C2%25B056%2705.3%2522N%2B77%25C2%25B005%2745.2%2522E/%4010.9299165,77.0990489,9926m/data%3D!3m1!1e3!4m4!3m3!8m2!3d10.9348056!4d77.0958889!5m1!1e1%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MTEyMy4xIPu8ASoASAFQAw%253D%253D%26skid%3D91985563-4fb5-4d54-93a4-62b71d32b79f&amp;q=EhAkBQIB4C7guzR74cqdAFF6GMzOy88GIjAqeBISJhCacJzenAJvHVpDf1cNn4890Z5z4EcNnlp1FzN-MWq_1_-9EYGy4122qSwyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S199" t="inlineStr"/>
-      <c r="T199" t="inlineStr"/>
+      <c r="S199" t="n">
+        <v>10.9299165</v>
+      </c>
+      <c r="T199" t="n">
+        <v>77.0990489</v>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
@@ -13105,8 +13825,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/11%25C2%25B010%2729.3%2522N%2B77%25C2%25B014%2720.7%2522E/%4011.1772182,77.2251478,5784m/data%3D!3m1!1e3!4m4!3m3!8m2!3d11.1748056!4d77.2390833!5m1!1e1%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MTEyMy4xIPu8ASoASAFQAw%253D%253D%26skid%3D87287b3d-0004-43fb-b5b1-2b25a2a374c7&amp;q=EhAkBQIB4C7guzR74cqdAFF6GM3Oy88GIjBVBeTa62-TZ-WM4foXhmRescRE2qa6jAZYOhSFTRJ9mIv9DAZuQZQ9c56FmSUQoT0yAnJSWgFD</t>
         </is>
       </c>
-      <c r="S200" t="inlineStr"/>
-      <c r="T200" t="inlineStr"/>
+      <c r="S200" t="n">
+        <v>11.1772182</v>
+      </c>
+      <c r="T200" t="n">
+        <v>77.2251478</v>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
@@ -13167,8 +13891,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/10%25C2%25B049%2729.0%2522N%2B77%25C2%25B002%2746.5%2522E/%4010.8287775,77.0409242,17023m/data%3D!3m1!1e3!4m4!3m3!8m2!3d10.8247222!4d77.04625!5m1!1e1%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MTEyMy4xIPu8ASoASAFQAw%253D%253D%26skid%3D215fdbfc-0f90-4449-9689-5198d6c42a3b&amp;q=EhAkBQIB4C7guzR74cqdAFF6GM7Oy88GIjAxdNoEeOKT3amUdQDwuXm2t4sH0yQEXgBA8gy2bP7m1g-UMAHfopHOF1jw1ra61x4yAnJSWgFD</t>
         </is>
       </c>
-      <c r="S201" t="inlineStr"/>
-      <c r="T201" t="inlineStr"/>
+      <c r="S201" t="n">
+        <v>10.8287775</v>
+      </c>
+      <c r="T201" t="n">
+        <v>77.04092420000001</v>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
@@ -13229,8 +13957,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/10%25C2%25B047%2737.6%2522N%2B76%25C2%25B059%2753.2%2522E/%4010.7934451,76.9526974,13002m/data%3D!3m1!1e3!4m4!3m3!8m2!3d10.7937778!4d76.9981111!5m1!1e1%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MTEyMy4xIPu8ASoASAFQAw%253D%253D%26skid%3D8249e460-95b4-47f1-877c-24a524736e27&amp;q=EhAkBQIB4C7guzR74cqdAFF6GM_Oy88GIjCQRSDYsHA-VMUdsL5t3OTQsxlT0fA2-k9IR2DUW3o17RNFQNjEVBo_vupS-0m4BZUyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S202" t="inlineStr"/>
-      <c r="T202" t="inlineStr"/>
+      <c r="S202" t="n">
+        <v>10.7934451</v>
+      </c>
+      <c r="T202" t="n">
+        <v>76.95269740000001</v>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="n">
@@ -13291,8 +14023,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/11%25C2%25B011%2748.8%2522N%2B77%25C2%25B009%2736.4%2522E/%4011.1610649,77.1486996,29153m/data%3D!3m1!1e3!4m4!3m3!8m2!3d11.1968889!4d77.1601111!5m1!1e1%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MTEyMy4xIPu8ASoASAFQAw%253D%253D%26skid%3D8592f63b-3335-4f66-bea4-f024db8de49a&amp;q=EhAkBQIB4C7guzR74cqdAFF6GNHOy88GIjC4D4EtpgHfpIvzrDEZ0uPYY9ncY4AmqngGqFk0cIs7wC5NfrIARRSpTQC9KL8a5vEyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S203" t="inlineStr"/>
-      <c r="T203" t="inlineStr"/>
+      <c r="S203" t="n">
+        <v>11.1610649</v>
+      </c>
+      <c r="T203" t="n">
+        <v>77.1486996</v>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
@@ -13353,8 +14089,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/10%25C2%25B053%2722.4%2522N%2B76%25C2%25B055%2722.2%2522E/%4010.8885157,76.9149267,3009m/data%3D!3m1!1e3!4m4!3m3!8m2!3d10.8895556!4d76.9228333!5m1!1e1%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MTEyMy4xIPu8ASoASAFQAw%253D%253D%26skid%3Db03ad69f-dd52-43b8-bbdf-9fe68d3ece07&amp;q=EhAkBQIB4C7guzR74cqdAFF6GNLOy88GIjAxQ1xsNz06tA--VWQsUJzQpGMrpacB8gRT22FMG4R-uoeI825gmF9m7xfxW9XazBkyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S204" t="inlineStr"/>
-      <c r="T204" t="inlineStr"/>
+      <c r="S204" t="n">
+        <v>10.8885157</v>
+      </c>
+      <c r="T204" t="n">
+        <v>76.9149267</v>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
@@ -13415,8 +14155,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/10%25C2%25B058%2754.7%2522N%2B77%25C2%25B008%2700.3%2522E/%4010.981707,77.1265656,13504m/data%3D!3m1!1e3!4m4!3m3!8m2!3d10.9818611!4d77.1334167!5m1!1e1%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MTEyMy4xIPu8ASoASAFQAw%253D%253D%26skid%3D3ba71d4b-1f9b-46ff-b081-4f94547833db&amp;q=EhAkBQIB4C7guzR74cqdAFF6GNPOy88GIjDsFSxZ23EIATP7ALEEhZMdVUhFAoWm0PcjBodDrK1o3ddosNqaOJBNi7W4TksDzSUyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S205" t="inlineStr"/>
-      <c r="T205" t="inlineStr"/>
+      <c r="S205" t="n">
+        <v>10.981707</v>
+      </c>
+      <c r="T205" t="n">
+        <v>77.12656560000001</v>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
@@ -13477,8 +14221,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/11%25C2%25B005%2710.0%2522N%2B77%25C2%25B007%2739.0%2522E/%4011.0853525,77.1392084,9920m/data%3D!3m1!1e3!4m4!3m3!8m2!3d11.0861111!4d77.1275!5m1!1e1%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MTEyMy4xIPu8ASoASAFQAw%253D%253D%26skid%3D6d0637f5-0097-43d5-a4f1-2ab278241d40&amp;q=EhAkBQIB4C7guzR74cqdAFF6GNXOy88GIjBgdTlWBJVrDSqH5DzzhRPphCGNBKppw_Ol-9odAQ8hboKs9TC0MYURlByaCwhcubIyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S206" t="inlineStr"/>
-      <c r="T206" t="inlineStr"/>
+      <c r="S206" t="n">
+        <v>11.0853525</v>
+      </c>
+      <c r="T206" t="n">
+        <v>77.1392084</v>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
@@ -13539,8 +14287,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/11%25C2%25B012%2747.0%2522N%2B77%25C2%25B010%2746.4%2522E/%4011.2122503,77.1581555,3246m/data%3D!3m1!1e3!4m4!3m3!8m2!3d11.2130556!4d77.1795556!5m1!1e1%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MTEyMy4xIPu8ASoASAFQAw%253D%253D%26skid%3D688967eb-4195-464e-bcd2-80312716b443&amp;q=EhAkBQIB4C7guzR74cqdAFF6GNbOy88GIjDqIPd9kTzHk3GnHhN9v1roXQny_pWKhzKAmec-81CbaYgenrJFDBf60D0ys43R0fMyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S207" t="inlineStr"/>
-      <c r="T207" t="inlineStr"/>
+      <c r="S207" t="n">
+        <v>11.2122503</v>
+      </c>
+      <c r="T207" t="n">
+        <v>77.15815550000001</v>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
@@ -13601,8 +14353,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/11%25C2%25B025%2737.8%2522N%2B77%25C2%25B012%2712.2%2522E/%4011.4341505,77.1665329,30269m/data%3D!3m1!1e3!4m4!3m3!8m2!3d11.4271667!4d77.2033889!5m1!1e1%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MTEyMy4xIPu8ASoASAFQAw%253D%253D%26skid%3D43935793-f6b1-4bbd-b178-c058f8353901&amp;q=EhAkBQIB4C7guzR74cqdAFF6GNfOy88GIjDlHawlLwUXnZlHFT1NKCQ2gJERcl-USPGJSzQlUAUF0lvROgqGFNoB_Ka-ue8UW_syAnJSWgFD</t>
         </is>
       </c>
-      <c r="S208" t="inlineStr"/>
-      <c r="T208" t="inlineStr"/>
+      <c r="S208" t="n">
+        <v>11.4341505</v>
+      </c>
+      <c r="T208" t="n">
+        <v>77.16653290000001</v>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
@@ -13663,8 +14419,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/10%25C2%25B048%2755.0%2522N%2B76%25C2%25B059%2755.5%2522E/%4010.798331,76.9849475,4339m/data%3D!3m1!1e3!4m4!3m3!8m2!3d10.8152778!4d76.99875!5m1!1e1%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MTEyMy4xIPu8ASoASAFQAw%253D%253D%26skid%3De520cb07-255f-462a-ac01-7f8d8ab36876&amp;q=EhAkBQIB4C7guzR74cqdAFF6GNjOy88GIjC0CCknG1wiNg2OsNipBuKoEMPqCyyybdVZDUSV9_v8d3qXA5JJpBEEhNqXzkEDw5EyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S209" t="inlineStr"/>
-      <c r="T209" t="inlineStr"/>
+      <c r="S209" t="n">
+        <v>10.798331</v>
+      </c>
+      <c r="T209" t="n">
+        <v>76.9849475</v>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="n">
@@ -13725,8 +14485,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/10%25C2%25B056%2750.6%2522N%2B77%25C2%25B009%2732.6%2522E/%4010.9461056,77.1529445,3376m/data%3D!3m1!1e3!4m4!3m3!8m2!3d10.9473889!4d77.1590556!5m1!1e1%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MTEyMy4xIPu8ASoASAFQAw%253D%253D%26skid%3D7de86d7b-239d-4659-abbc-c96279fb8339&amp;q=EhAkBQIB4C7guzR74cqdAFF6GNrOy88GIjAbWVSv55pniG8jmUftb2itrCZKH95EOvR_zj0YLHZZ_EZhIZvHWjipmMQ-ozJ_D9kyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S210" t="inlineStr"/>
-      <c r="T210" t="inlineStr"/>
+      <c r="S210" t="n">
+        <v>10.9461056</v>
+      </c>
+      <c r="T210" t="n">
+        <v>77.1529445</v>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="n">
@@ -13787,8 +14551,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/10%25C2%25B054%2728.1%2522N%2B77%25C2%25B001%2750.2%2522E/%4010.9084944,77.0292968,2579m/data%3D!3m1!1e3!4m4!3m3!8m2!3d10.9078056!4d77.0306111!5m1!1e1%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MTEyMy4xIPu8ASoASAFQAw%253D%253D%26skid%3D48f3293d-5e83-41b7-91c4-6c61fc9a5a40&amp;q=EhAkBQIB4C7guzR74cqdAFF6GNzOy88GIjD6vT0dhYnKp5QDxsIzHuLfkdkHjWv2aP_N9FZLiTqFxxi-pj33UTRVdPI0LrqSbFUyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S211" t="inlineStr"/>
-      <c r="T211" t="inlineStr"/>
+      <c r="S211" t="n">
+        <v>10.9084944</v>
+      </c>
+      <c r="T211" t="n">
+        <v>77.0292968</v>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="n">
@@ -13851,8 +14619,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/10%25C2%25B053%2728.6%2522N%2B77%25C2%25B002%2707.6%2522E/%4010.8895369,77.0309513,2579m/data%3D!3m1!1e3!4m4!3m3!8m2!3d10.8912778!4d77.0354444!5m1!1e1%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MTEyMy4xIPu8ASoASAFQAw%253D%253D%26skid%3D0dee3a62-2dc3-4a23-a697-0b6b9805e305&amp;q=EhAkBQIB4C7guzR74cqdAFF6GN7Oy88GIjAMLWFNx1KTGNBFPtwpFkLyx2n1GRwxUPODEq-oNqNLteHqaDAJmXAbszvKxpxsIgAyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S212" t="inlineStr"/>
-      <c r="T212" t="inlineStr"/>
+      <c r="S212" t="n">
+        <v>10.8895369</v>
+      </c>
+      <c r="T212" t="n">
+        <v>77.0309513</v>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="n">
@@ -13911,8 +14683,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/10%25C2%25B052%2736.0%2522N%2B77%25C2%25B001%2732.0%2522E/%4010.8817616,77.0198202,2579m/data%3D!3m1!1e3!4m4!3m3!8m2!3d10.8766667!4d77.0255556!5m1!1e1%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MTEyMy4xIPu8ASoASAFQAw%253D%253D%26skid%3D9dd9eddc-bd24-446c-84d1-c2a1286972bd&amp;q=EhAkBQIB4C7guzR74cqdAFF6GOHOy88GIjAXAwyjNycG9h5zp4emTtrMctMTbi_NCl0L9Mc4u5jUDNTgdZkPtH9jf_n24LSPxFwyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S213" t="inlineStr"/>
-      <c r="T213" t="inlineStr"/>
+      <c r="S213" t="n">
+        <v>10.8817616</v>
+      </c>
+      <c r="T213" t="n">
+        <v>77.0198202</v>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="n">
@@ -14035,8 +14811,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/11%25C2%25B007%2737.4%2522N%2B77%25C2%25B009%2732.6%2522E/%4011.1298785,77.1426924,7575m/data%3D!3m1!1e3!4m4!3m3!8m2!3d11.1270556!4d77.1590556!5m1!1e1%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MTEyMy4xIPu8ASoASAFQAw%253D%253D%26skid%3Dd0e37d0a-6e8d-4cea-9153-83eb44cd1e04&amp;q=EhAkBQIB4C7guzR74cqdAFF6GOTOy88GIjDEsCkRhWyvcHMDAh8TLzNlabSZTrUqVZZr5eI1FOj5eSJBommeH4x_3kW9lS4b5-QyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S215" t="inlineStr"/>
-      <c r="T215" t="inlineStr"/>
+      <c r="S215" t="n">
+        <v>11.1298785</v>
+      </c>
+      <c r="T215" t="n">
+        <v>77.1426924</v>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="n">
@@ -14097,8 +14877,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/10%25C2%25B054%2728.1%2522N%2B77%25C2%25B001%2750.2%2522E/%4010.9057861,77.026031,1970m/data%3D!3m1!1e3!4m4!3m3!8m2!3d10.9078056!4d77.0306111!5m1!1e1%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MTEyMy4xIPu8ASoASAFQAw%253D%253D%26skid%3D2a958e55-6e5b-4676-99a5-eb1abbff6c31&amp;q=EhAkBQIB4C7guzR74cqdAFF6GOXOy88GIjDVx8D15obbOVXU8J5Vn3BFCslyHP4io2l7HsdcsI1nt3hfl48TZ8mBwMIY3ebJDK4yAnJSWgFD</t>
         </is>
       </c>
-      <c r="S216" t="inlineStr"/>
-      <c r="T216" t="inlineStr"/>
+      <c r="S216" t="n">
+        <v>10.9057861</v>
+      </c>
+      <c r="T216" t="n">
+        <v>77.026031</v>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="n">
@@ -14159,8 +14943,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/10%25C2%25B056%2702.6%2522N%2B77%25C2%25B003%2746.8%2522E/%4010.9334279,77.0642064,2579m/data%3D!3m1!1e3!4m4!3m3!8m2!3d10.9340556!4d77.063!5m1!1e1%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MTEyMy4xIPu8ASoASAFQAw%253D%253D%26skid%3D3c5cb350-800f-4261-bf34-7708aff67e55&amp;q=EhAkBQIB4C7guzR74cqdAFF6GObOy88GIjDvBfpBRDvonJ71GdVVMxgcsezIf4F6U5zqXZD8gGGXYWhs8IsT4MnXgIYlfRx27gYyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S217" t="inlineStr"/>
-      <c r="T217" t="inlineStr"/>
+      <c r="S217" t="n">
+        <v>10.9334279</v>
+      </c>
+      <c r="T217" t="n">
+        <v>77.0642064</v>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="n">
@@ -14221,8 +15009,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/10%25C2%25B055%2756.6%2522N%2B77%25C2%25B005%2721.9%2522E/%4010.9408632,77.0800111,7580m/data%3D!3m1!1e3!4m4!3m3!8m2!3d10.9323889!4d77.0894167!5m1!1e1%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MTEyMy4xIPu8ASoASAFQAw%253D%253D%26skid%3Dc339a321-91a0-4bf4-8c0c-9e0f701636b1&amp;q=EhAkBQIB4C7guzR74cqdAFF6GOjOy88GIjC37h3lQr7icPtoa7c7UEdi42SuIfH_ctPq36Eb3IVjuIfyvY4OGiE4Jw6ySo478iUyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S218" t="inlineStr"/>
-      <c r="T218" t="inlineStr"/>
+      <c r="S218" t="n">
+        <v>10.9408632</v>
+      </c>
+      <c r="T218" t="n">
+        <v>77.08001109999999</v>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="n">
@@ -14283,8 +15075,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/10%25C2%25B055%2756.6%2522N%2B77%25C2%25B005%2721.9%2522E/%4010.9375808,77.0783503,5789m/data%3D!3m1!1e3!4m4!3m3!8m2!3d10.9323889!4d77.0894167!5m1!1e1%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MTEyMy4xIPu8ASoASAFQAw%253D%253D%26skid%3D10459ad7-1a7d-4f78-bb47-25f5b85b982c&amp;q=EhAkBQIB4C7guzR74cqdAFF6GOnOy88GIjASYbedtiFcIhVxlz63ekPd6iXOHsPOOg3fHFfCsBNkqrUzLKx_WkwmJolDvF5kzHAyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S219" t="inlineStr"/>
-      <c r="T219" t="inlineStr"/>
+      <c r="S219" t="n">
+        <v>10.9375808</v>
+      </c>
+      <c r="T219" t="n">
+        <v>77.0783503</v>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="n">
@@ -14345,8 +15141,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/10%25C2%25B057%2707.5%2522N%2B77%25C2%25B001%2709.7%2522E/%4010.9520833,77.0193611,670m/data%3D!3m2!1e3!4b1!4m4!3m3!8m2!3d10.9520833!4d77.0193611!5m1!1e1%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MTEyMy4xIPu8ASoASAFQAw%253D%253D%26skid%3D809fd061-46fb-452d-ac8d-ce32c4f52c38&amp;q=EhAkBQIB4C7guzR74cqdAFF6GOvOy88GIjCqpZ_tIDVdI9S4_EL1gTywFm2KFTSS905YDvmDXrr4WULvrux06UPeTi21Trs_tvUyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S220" t="inlineStr"/>
-      <c r="T220" t="inlineStr"/>
+      <c r="S220" t="n">
+        <v>10.9520833</v>
+      </c>
+      <c r="T220" t="n">
+        <v>77.0193611</v>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="n">
@@ -14407,8 +15207,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/10%25C2%25B053%2720.5%2522N%2B77%25C2%25B001%2716.9%2522E/%4010.8914183,76.9987877,7581m/data%3D!3m1!1e3!4m4!3m3!8m2!3d10.8890278!4d77.0213611!5m1!1e1%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MTEyMy4xIPu8ASoASAFQAw%253D%253D%26skid%3D391708b2-3ffc-41a8-aad0-425063d27a78&amp;q=EhAkBQIB4C7guzR74cqdAFF6GOzOy88GIjAAMmfBL-liTZ4HZChItp5qC-LbTntk9t9t8YZLLf0ng2nrAf1SPF05w2vpFMG4YBMyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S221" t="inlineStr"/>
-      <c r="T221" t="inlineStr"/>
+      <c r="S221" t="n">
+        <v>10.8914183</v>
+      </c>
+      <c r="T221" t="n">
+        <v>76.99878769999999</v>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="n">
@@ -14469,8 +15273,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/11%25C2%25B005%2758.0%2522N%2B77%25C2%25B009%2734.5%2522E/%4011.1081862,77.1291365,6749m/data%3D!3m1!1e3!4m4!3m3!8m2!3d11.0994444!4d77.1595833!5m1!1e1%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MTEyMy4xIPu8ASoASAFQAw%253D%253D%26skid%3De636f231-44c0-4961-810f-5316cce61eb8&amp;q=EhAkBQIB4C7guzR74cqdAFF6GO7Oy88GIjB65QFYgru-mlUDPkX_iPhVVA3w32YemuwOrxUTv7mMV2Yk_VOJjIfnDQ4OVNnzGWQyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S222" t="inlineStr"/>
-      <c r="T222" t="inlineStr"/>
+      <c r="S222" t="n">
+        <v>11.1081862</v>
+      </c>
+      <c r="T222" t="n">
+        <v>77.1291365</v>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="n">
@@ -14531,8 +15339,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/11%25C2%25B005%2718.9%2522N%2B77%25C2%25B004%2750.5%2522E/%4011.0824407,77.0666597,6013m/data%3D!3m1!1e3!4m4!3m3!8m2!3d11.0885833!4d77.0806944!5m1!1e1%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MTEyMy4xIPu8ASoASAFQAw%253D%253D%26skid%3D4af7967b-1e64-4ac5-be69-b0f2c2fd7939&amp;q=EhAkBQIB4C7guzR74cqdAFF6GPDOy88GIjBTcB52Npe278JJ2hiKi87fodrxQOOjgzGBK74ExqmDIlXhY4OLam2gIb0lveIFo8QyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S223" t="inlineStr"/>
-      <c r="T223" t="inlineStr"/>
+      <c r="S223" t="n">
+        <v>11.0824407</v>
+      </c>
+      <c r="T223" t="n">
+        <v>77.0666597</v>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="n">
@@ -14593,8 +15405,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/11%25C2%25B005%2738.0%2522N%2B77%25C2%25B003%2735.3%2522E/%4011.0948008,77.0551144,1148m/data%3D!3m1!1e3!4m4!3m3!8m2!3d11.0938889!4d77.0598056!5m1!1e1%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MTEyMy4xIPu8ASoASAFQAw%253D%253D%26skid%3De99dbb87-f87a-4682-bd71-6cf202f6fccd&amp;q=EhAkBQIB4C7guzR74cqdAFF6GPLOy88GIjDrN3dnurRyIRBloxD3ypmOKJwDeaKtRiJGxz7yHijBogPR7Bae8BRJKk6Ohhy2mVYyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S224" t="inlineStr"/>
-      <c r="T224" t="inlineStr"/>
+      <c r="S224" t="n">
+        <v>11.0948008</v>
+      </c>
+      <c r="T224" t="n">
+        <v>77.05511439999999</v>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="n">
@@ -14655,8 +15471,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/10%25C2%25B057%2751.7%2522N%2B77%25C2%25B008%2700.0%2522E/%4010.9634601,77.1130393,10719m/data%3D!3m1!1e3!4m4!3m3!8m2!3d10.9643611!4d77.1333333!5m1!1e1%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MTEyMy4xIPu8ASoASAFQAw%253D%253D%26skid%3Dd1d9013c-40e5-4022-93d9-27b0c5f240a0&amp;q=EhAkBQIB4C7guzR74cqdAFF6GPTOy88GIjDQ4V9wdKoQuC-yfBgYxFxTrYdnUi-lQak6PvExjch5QFqWosdxynaEZNRBYyUBmqQyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S225" t="inlineStr"/>
-      <c r="T225" t="inlineStr"/>
+      <c r="S225" t="n">
+        <v>10.9634601</v>
+      </c>
+      <c r="T225" t="n">
+        <v>77.1130393</v>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="n">
@@ -14717,8 +15537,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/10%25C2%25B059%2719.4%2522N%2B77%25C2%25B009%2742.3%2522E/%4010.9913976,77.1503613,7579m/data%3D!3m1!1e3!4m4!3m3!8m2!3d10.9887222!4d77.16175!5m1!1e1%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MTEyMy4xIPu8ASoASAFQAw%253D%253D%26skid%3D47d19bd5-59a6-417d-9b3b-b7b39c8381cd&amp;q=EhAkBQIB4C7guzR74cqdAFF6GPbOy88GIjCnxeh3Yp1ny0deCTr2qSmeaEhVjPUhpMnOmqUNiRdTxg1yofrdU6-0RCeczUb1QzEyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S226" t="inlineStr"/>
-      <c r="T226" t="inlineStr"/>
+      <c r="S226" t="n">
+        <v>10.9913976</v>
+      </c>
+      <c r="T226" t="n">
+        <v>77.1503613</v>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="n">
@@ -14779,8 +15603,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/10%25C2%25B055%2728.9%2522N%2B77%25C2%25B008%2731.9%2522E/%4010.9235187,77.136397,3939m/data%3D!3m1!1e3!4m4!3m3!8m2!3d10.9246944!4d77.1421944!5m1!1e1%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MTEyMy4xIPu8ASoASAFQAw%253D%253D%26skid%3Df9fe644e-2589-429d-a34b-d0f2262b7bb1&amp;q=EhAkBQIB4C7guzR74cqdAFF6GPjOy88GIjDhhxK7gcd2lrsBBLUH81VzLx7qvxE_GK7r5-6-2YkDfiHygndI2ix-rGW-lTgXeuUyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S227" t="inlineStr"/>
-      <c r="T227" t="inlineStr"/>
+      <c r="S227" t="n">
+        <v>10.9235187</v>
+      </c>
+      <c r="T227" t="n">
+        <v>77.136397</v>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="n">
@@ -14841,8 +15669,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/10%25C2%25B057%2729.7%2522N%2B77%25C2%25B008%2737.3%2522E/%4010.9622679,77.1340913,7580m/data%3D!3m1!1e3!4m4!3m3!8m2!3d10.95825!4d77.1436944!5m1!1e1%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MTEyMy4xIPu8ASoASAFQAw%253D%253D%26skid%3D61453ec4-de05-4750-bda4-39dcfac6ec58&amp;q=EhAkBQIB4C7guzR74cqdAFF6GPnOy88GIjBTzu4SOMjEXV9oR3IjoSGpUB2yoqnZEgqIzwGsPgC4L0BxpIcGr5pzvzUFnJKjat8yAnJSWgFD</t>
         </is>
       </c>
-      <c r="S228" t="inlineStr"/>
-      <c r="T228" t="inlineStr"/>
+      <c r="S228" t="n">
+        <v>10.9622679</v>
+      </c>
+      <c r="T228" t="n">
+        <v>77.13409129999999</v>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="n">
@@ -14903,8 +15735,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/11%25C2%25B005%2735.2%2522N%2B77%25C2%25B008%2748.0%2522E/%4011.096768,77.1360055,4419m/data%3D!3m1!1e3!4m4!3m3!8m2!3d11.0931111!4d77.1466667!5m1!1e1%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MTEyMy4xIPu8ASoASAFQAw%253D%253D%26skid%3D74dd2389-4ced-4a29-9612-9887b766c28e&amp;q=EhAkBQIB4C7guzR74cqdAFF6GPvOy88GIjCdFPrDYAH6XOVviT3lGTbqqlM4TedMHQOWDmxbrfGOJx6fORV7vxBIMewMRMtMcewyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S229" t="inlineStr"/>
-      <c r="T229" t="inlineStr"/>
+      <c r="S229" t="n">
+        <v>11.096768</v>
+      </c>
+      <c r="T229" t="n">
+        <v>77.1360055</v>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="n">
@@ -14965,8 +15801,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/11%25C2%25B004%2722.2%2522N%2B77%25C2%25B006%2724.4%2522E/%4011.0724123,77.1026074,1969m/data%3D!3m1!1e3!4m4!3m3!8m2!3d11.0728333!4d77.1067778!5m1!1e1%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MTEyMy4xIPu8ASoASAFQAw%253D%253D%26skid%3Df7279ae9-e279-4a5f-942a-b9be47710ccb&amp;q=EhAkBQIB4C7guzR74cqdAFF6GP3Oy88GIjC_NhZhVjjIDoZ02g5suinhQmwU8cfluxVTmSbN6st09GWSDy9Comw1Awi7uJRihjYyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S230" t="inlineStr"/>
-      <c r="T230" t="inlineStr"/>
+      <c r="S230" t="n">
+        <v>11.0724123</v>
+      </c>
+      <c r="T230" t="n">
+        <v>77.1026074</v>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="n">
@@ -15027,8 +15867,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/10%25C2%25B055%2754.8%2522N%2B77%25C2%25B019%2721.6%2522E/%4010.9321526,77.317535,4094m/data%3D!3m1!1e3!4m4!3m3!8m2!3d10.9318889!4d77.3226667!5m1!1e1%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MTEyMy4xIPu8ASoASAFQAw%253D%253D%26skid%3D8244fc60-e92a-4c19-9966-a5681bf9ca37&amp;q=EhAkBQIB4C7guzR74cqdAFF6GP7Oy88GIjDjc4ZliH2W5NHmCm20d8kzgNGFGCGHKX6GYgfi8K170I5lRqSQVK_gPDoPceYBP4MyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S231" t="inlineStr"/>
-      <c r="T231" t="inlineStr"/>
+      <c r="S231" t="n">
+        <v>10.9321526</v>
+      </c>
+      <c r="T231" t="n">
+        <v>77.31753500000001</v>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="n">
@@ -15089,8 +15933,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/11%25C2%25B021%2731.7%2522N%2B77%25C2%25B012%2718.6%2522E/%4011.3742035,77.1694525,11561m/data%3D!3m1!1e3!4m4!3m3!8m2!3d11.3588056!4d77.2051667!5m1!1e1%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MTEyMy4xIPu8ASoASAFQAw%253D%253D%26skid%3Dfba8840f-b663-4f43-8a4b-901c0a504344&amp;q=EhAkBQIB4C7guzR74cqdAFF6GIDPy88GIjCdm7_SvHlzJyiZMdeQ5i1irbv0zwrICnmbQcBSy-pJTXHZpjyypIWAW0iTHtKiEjAyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S232" t="inlineStr"/>
-      <c r="T232" t="inlineStr"/>
+      <c r="S232" t="n">
+        <v>11.3742035</v>
+      </c>
+      <c r="T232" t="n">
+        <v>77.16945250000001</v>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="n">
@@ -15151,8 +15999,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/11%25C2%25B021%2725.5%2522N%2B77%25C2%25B012%2745.7%2522E/%4011.3602863,77.1741687,5352m/data%3D!3m1!1e3!4m4!3m3!8m2!3d11.3570833!4d77.2126944!5m1!1e1%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MTEyMy4xIPu8ASoASAFQAw%253D%253D%26skid%3Da0007fa4-d49d-4428-8525-dcafad18d3a5&amp;q=EhAkBQIB4C7guzR74cqdAFF6GILPy88GIjD6VGLD-ePv4bvNaS_AJX1VnQFYTCixLLz-twBtOTIN52e11ZhpkarjvuM0oGnIa_EyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S233" t="inlineStr"/>
-      <c r="T233" t="inlineStr"/>
+      <c r="S233" t="n">
+        <v>11.3602863</v>
+      </c>
+      <c r="T233" t="n">
+        <v>77.1741687</v>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="n">
@@ -15213,8 +16065,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/10%25C2%25B053%2722.7%2522N%2B77%25C2%25B010%2714.6%2522E/%4010.8867746,77.1548271,2579m/data%3D!3m1!1e3!4m4!3m3!8m2!3d10.8896389!4d77.1707222!5m1!1e1%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MTEyMy4xIPu8ASoASAFQAw%253D%253D%26skid%3Da7333830-580a-4bf1-b414-a8181fe0463b&amp;q=EhAkBQIB4C7guzR74cqdAFF6GITPy88GIjCigKTepQzCYZqabxkbwpAwMvJbYPn0IhTv0sNWHvOozRZBJJDnsH-SmqF1wzZjMLoyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S234" t="inlineStr"/>
-      <c r="T234" t="inlineStr"/>
+      <c r="S234" t="n">
+        <v>10.8867746</v>
+      </c>
+      <c r="T234" t="n">
+        <v>77.15482710000001</v>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="n">
@@ -15275,8 +16131,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/10%25C2%25B056%2731.3%2522N%2B77%25C2%25B014%2755.1%2522E/%4010.9385878,77.2225915,7018m/data%3D!3m1!1e3!4m4!3m3!8m2!3d10.9420278!4d77.2486389!5m1!1e1%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MTEyMy4xIPu8ASoASAFQAw%253D%253D%26skid%3Db49ee2ae-bd02-4ed2-98f4-d55b4490c757&amp;q=EhAkBQIB4C7guzR74cqdAFF6GIXPy88GIjCPXNUTGlYzK1UDkeVfJaGB0AIkRF6tbbwRQS0xyQXmfdxn2SFKAgrdoRe_IXvSPH0yAnJSWgFD</t>
         </is>
       </c>
-      <c r="S235" t="inlineStr"/>
-      <c r="T235" t="inlineStr"/>
+      <c r="S235" t="n">
+        <v>10.9385878</v>
+      </c>
+      <c r="T235" t="n">
+        <v>77.22259149999999</v>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="n">
@@ -15337,8 +16197,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/10%25C2%25B048%2749.1%2522N%2B76%25C2%25B058%2708.3%2522E/%4010.8109175,76.9650082,3378m/data%3D!3m1!1e3!4m4!3m3!8m2!3d10.8136389!4d76.9689722!5m1!1e1%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MTEyMy4xIPu8ASoASAFQAw%253D%253D%26skid%3D7e4727ab-6f03-4ad6-b4c1-b631f22b4c5d&amp;q=EhAkBQIB4C7guzR74cqdAFF6GIfPy88GIjBO71vbSxd6tYJ6Xdwce-xO3e1iF-040MhBDiopVmjfPtUccNyXUWBRJ88MGGApcosyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S236" t="inlineStr"/>
-      <c r="T236" t="inlineStr"/>
+      <c r="S236" t="n">
+        <v>10.8109175</v>
+      </c>
+      <c r="T236" t="n">
+        <v>76.9650082</v>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="n">
@@ -15399,8 +16263,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/10%25C2%25B044%2741.0%2522N%2B77%25C2%25B000%2712.3%2522E/%4010.7452823,76.9964874,5793m/data%3D!3m1!1e3!4m4!3m3!8m2!3d10.7447222!4d77.0034167!5m1!1e1%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MTEyMy4xIPu8ASoASAFQAw%253D%253D%26skid%3D6001fa5c-37c0-42b3-b213-034fea143e14&amp;q=EhAkBQIB4C7guzR74cqdAFF6GIjPy88GIjDW_o9WmnmneF4xp7K6PP6dFtKPdcP4bltYG2FGIAnRMrNhTt6Go1uhqQCc0Wd8LQwyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S237" t="inlineStr"/>
-      <c r="T237" t="inlineStr"/>
+      <c r="S237" t="n">
+        <v>10.7452823</v>
+      </c>
+      <c r="T237" t="n">
+        <v>76.99648740000001</v>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="n">
@@ -15461,8 +16329,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/10%25C2%25B048%2757.1%2522N%2B77%25C2%25B002%2743.5%2522E/%4010.8382504,77.0491149,18385m/data%3D!3m1!1e3!4m4!3m3!8m2!3d10.8158611!4d77.0454167!5m1!1e1%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MTEyMy4xIPu8ASoASAFQAw%253D%253D%26skid%3D2982712b-3922-463a-8124-b5f9481e31cb&amp;q=EhAkBQIB4C7guzR74cqdAFF6GInPy88GIjCC0Daa4LqL43dbDJ4XQfem4JrY36xXwiazBOry5MlfeDYiMdXRyXjouH_toepUnsUyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S238" t="inlineStr"/>
-      <c r="T238" t="inlineStr"/>
+      <c r="S238" t="n">
+        <v>10.8382504</v>
+      </c>
+      <c r="T238" t="n">
+        <v>77.04911490000001</v>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="n">
@@ -15523,8 +16395,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/10%25C2%25B040%2738.5%2522N%2B77%25C2%25B011%2750.2%2522E/%4010.6965147,77.1455677,29199m/data%3D!3m1!1e3!4m4!3m3!8m2!3d10.6773611!4d77.1972778!5m1!1e1%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MTEyMy4xIPu8ASoASAFQAw%253D%253D%26skid%3D86aab080-3e68-4753-98fa-04cf3ec1c11c&amp;q=EhAkBQIB4C7guzR74cqdAFF6GIrPy88GIjDHy9VHVQ98UWJMj2BKei2aJUPrlOmgm4-1PeStODaXppbhsWYv45vSMsBDm_GJIPsyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S239" t="inlineStr"/>
-      <c r="T239" t="inlineStr"/>
+      <c r="S239" t="n">
+        <v>10.6965147</v>
+      </c>
+      <c r="T239" t="n">
+        <v>77.1455677</v>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="n">
@@ -15585,8 +16461,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/10%25C2%25B046%2724.1%2522N%2B76%25C2%25B057%2714.2%2522E/%4010.7944369,76.9448152,29189m/data%3D!3m1!1e3!4m4!3m3!8m2!3d10.7733611!4d76.9539444!5m1!1e1%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MTEyMy4xIPu8ASoASAFQAw%253D%253D%26skid%3Df2e5df43-b923-46b2-8dd5-c5df59369dcd&amp;q=EhAkBQIB4C7guzR74cqdAFF6GIzPy88GIjAOgBRKAwbDhRHZwwCDtVCigk4Ls38Jr5ZESZ8Ae7J9JZpIWnArNXHK850ZDZlTCCkyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S240" t="inlineStr"/>
-      <c r="T240" t="inlineStr"/>
+      <c r="S240" t="n">
+        <v>10.7944369</v>
+      </c>
+      <c r="T240" t="n">
+        <v>76.94481519999999</v>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="n">
@@ -15647,8 +16527,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/11%25C2%25B019%2756.6%2522N%2B77%25C2%25B015%2751.1%2522E/%4011.2762135,77.156049,29141m/data%3D!3m1!1e3!4m4!3m3!8m2!3d11.3323889!4d77.2641944!5m1!1e1%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MTEyMy4xIPu8ASoASAFQAw%253D%253D%26skid%3Dae00f746-64bd-4d4b-a7d8-6a67247d8d1b&amp;q=EhAkBQIB4C7guzR74cqdAFF6GI3Py88GIjC_7I80vluLjUoZCnFcJuaXp-5AXpohCDFFX1SxQyky_NtjWbylR6_JAL5KgoxRcOgyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S241" t="inlineStr"/>
-      <c r="T241" t="inlineStr"/>
+      <c r="S241" t="n">
+        <v>11.2762135</v>
+      </c>
+      <c r="T241" t="n">
+        <v>77.156049</v>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="n">
@@ -15709,8 +16593,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/11%25C2%25B003%2720.6%2522N%2B77%25C2%25B003%2759.1%2522E/%4011.0519109,77.0594387,1504m/data%3D!3m1!1e3!4m4!3m3!8m2!3d11.0557222!4d77.0664167!5m1!1e1%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MTEyMy4xIPu8ASoASAFQAw%253D%253D%26skid%3D0d3d0225-3273-43e9-a534-a86403ac4c49&amp;q=EhAkBQIB4C7guzR74cqdAFF6GI_Py88GIjDjAAe0QsyOrN794GtiFF6XqQKG09pLPb8qmAzLy_Bc4LmyDXCBA3Z1Mi4Y8Q1q6dUyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S242" t="inlineStr"/>
-      <c r="T242" t="inlineStr"/>
+      <c r="S242" t="n">
+        <v>11.0519109</v>
+      </c>
+      <c r="T242" t="n">
+        <v>77.0594387</v>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="n">
@@ -15771,8 +16659,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/10%25C2%25B050%2706.0%2522N%2B77%25C2%25B000%2724.4%2522E/%4010.8445732,77.009259,17022m/data%3D!3m1!1e3!4m4!3m3!8m2!3d10.835!4d77.0067778!5m1!1e1%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MTEyMy4xIPu8ASoASAFQAw%253D%253D%26skid%3Db1209e82-2005-4ba5-ba55-5d0973feb57e&amp;q=EhAkBQIB4C7guzR74cqdAFF6GJDPy88GIjAuYK08DNBxxgNp0zedVO_nxkFdQBaMdmYL0SAlecPjKrQuGL1mRe8pcH8x3mIRubgyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S243" t="inlineStr"/>
-      <c r="T243" t="inlineStr"/>
+      <c r="S243" t="n">
+        <v>10.8445732</v>
+      </c>
+      <c r="T243" t="n">
+        <v>77.009259</v>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="n">
@@ -15833,8 +16725,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/11%25C2%25B015%2757.5%2522N%2B77%25C2%25B010%2717.9%2522E/%4011.2910828,77.1943236,51921m/data%3D!3m1!1e3!4m4!3m3!8m2!3d11.2659722!4d77.1716389!5m1!1e1%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MTEyMy4xIPu8ASoASAFQAw%253D%253D%26skid%3Daa1aeb8e-6852-4c62-b285-b9b9f1114860&amp;q=EhAkBQIB4C7guzR74cqdAFF6GJLPy88GIjCr9e8QaPEfL4xtg5JrbKfKZFVPJzimAbXDQZsMHIZ16d4U7aD085CozjbKWRe4dYkyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S244" t="inlineStr"/>
-      <c r="T244" t="inlineStr"/>
+      <c r="S244" t="n">
+        <v>11.2910828</v>
+      </c>
+      <c r="T244" t="n">
+        <v>77.1943236</v>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="n">
@@ -15895,8 +16791,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/10%25C2%25B058%2733.0%2522N%2B77%25C2%25B010%2725.2%2522E/%4010.9979652,77.1646795,14726m/data%3D!3m1!1e3!4m4!3m3!8m2!3d10.9758333!4d77.1736667!5m1!1e1%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MTEyMy4xIPu8ASoASAFQAw%253D%253D%26skid%3D77141bb8-4b56-41c4-9db3-5f416f8b263f&amp;q=EhAkBQIB4C7guzR74cqdAFF6GJTPy88GIjDORLCiYliOIapd-YcLwSG5aMNtuW0yAQ5vWaBZndX3Oqfgun0CrhgaCHkpqU_f5J4yAnJSWgFD</t>
         </is>
       </c>
-      <c r="S245" t="inlineStr"/>
-      <c r="T245" t="inlineStr"/>
+      <c r="S245" t="n">
+        <v>10.9979652</v>
+      </c>
+      <c r="T245" t="n">
+        <v>77.16467950000001</v>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="n">
@@ -15957,8 +16857,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/11%25C2%25B011%2739.1%2522N%2B77%25C2%25B012%2733.4%2522E/%4011.1926584,77.188548,12985m/data%3D!3m1!1e3!4m4!3m3!8m2!3d11.1941944!4d77.2092778!5m1!1e1%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MTEyMy4xIPu8ASoASAFQAw%253D%253D%26skid%3Dfcd57bd2-7417-4aee-958a-5ecd25abfdc4&amp;q=EhAkBQIB4C7guzR74cqdAFF6GJbPy88GIjD3wkB2mdY8sTJ4hL2WCr93pLxZvD9NL0gEroEKX2ZI7tDne-d7e3-CMHN9bhYjWK8yAnJSWgFD</t>
         </is>
       </c>
-      <c r="S246" t="inlineStr"/>
-      <c r="T246" t="inlineStr"/>
+      <c r="S246" t="n">
+        <v>11.1926584</v>
+      </c>
+      <c r="T246" t="n">
+        <v>77.188548</v>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="n">
@@ -16019,8 +16923,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/11%25C2%25B008%2728.4%2522N%2B77%25C2%25B013%2734.5%2522E/%4011.134183,77.213929,5785m/data%3D!3m1!1e3!4m4!3m3!8m2!3d11.1412222!4d77.22625!5m1!1e1%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MTEyMy4xIPu8ASoASAFQAw%253D%253D%26skid%3D1dea2751-834e-4e0e-8fa7-5f034be3a28d&amp;q=EhAkBQIB4C7guzR74cqdAFF6GJjPy88GIjBoVR5E6jZ8nRxtjijwE6UAjBVLdFOY9Bne3DlFbbLtqA038J8HxNd72JJBRagxrCEyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S247" t="inlineStr"/>
-      <c r="T247" t="inlineStr"/>
+      <c r="S247" t="n">
+        <v>11.134183</v>
+      </c>
+      <c r="T247" t="n">
+        <v>77.21392899999999</v>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="n">
@@ -16081,8 +16989,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/11%25C2%25B006%2742.1%2522N%2B76%25C2%25B059%2710.1%2522E/%4011.1147564,76.9817181,3375m/data%3D!3m1!1e3!4m4!3m3!8m2!3d11.1116944!4d76.9861389!5m1!1e1%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MTEyMy4xIPu8ASoASAFQAw%253D%253D%26skid%3D818449e0-0295-4fcb-9085-644ac2498a1c&amp;q=EhAkBQIB4C7guzR74cqdAFF6GJrPy88GIjA2J6wyJAIfnfc2v1fb5VozVYu2D614wASzQEHQzhuXm1owfhJcK-3GZPjcY2dl_ZQyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S248" t="inlineStr"/>
-      <c r="T248" t="inlineStr"/>
+      <c r="S248" t="n">
+        <v>11.1147564</v>
+      </c>
+      <c r="T248" t="n">
+        <v>76.98171809999999</v>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="n">
@@ -16143,8 +17055,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/%4011.1731101,77.2369884,3a,90y,134.46h,90t/data%3D!3m7!1e1!3m5!1sYww-uKt1nKHVP2O1ZKRsyg!2e0!6shttps:%252F%252Fstreetviewpixels-pa.googleapis.com%252Fv1%252Fthumbnail%253Fcb_client%253Dmaps_sv.tactile%2526w%253D900%2526h%253D600%2526pitch%253D0%2526panoid%253DYww-uKt1nKHVP2O1ZKRsyg%2526yaw%253D134.46286713286716!7i13312!8i6656!5m1!1e1%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MTEyMy4xIPu8ASoASAFQAw%253D%253D%26skid%3D4f3061d6-a5e4-492b-b1c4-99b7ca69bd51&amp;q=EhAkBQIB4C7guzR74cqdAFF6GJzPy88GIi2gy5EU8wR7UgjeSLYcjXjpSgq6eCrK-lRUkkcQ7rs_Hy37r4QD8zng9yB_CtkyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S249" t="inlineStr"/>
-      <c r="T249" t="inlineStr"/>
+      <c r="S249" t="n">
+        <v>11.1731101</v>
+      </c>
+      <c r="T249" t="n">
+        <v>77.2369884</v>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="n">
@@ -16205,8 +17121,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/11%25C2%25B011%2719.1%2522N%2B77%25C2%25B010%2729.2%2522E/%4011.1679169,77.1597832,38172m/data%3D!3m1!1e3!4m4!3m3!8m2!3d11.1886389!4d77.1747778!5m1!1e1%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MTEyMy4xIPu8ASoASAFQAw%253D%253D%26skid%3Da1e43d07-82cc-4de3-8261-24b797b1551f&amp;q=EhAkBQIB4C7guzR74cqdAFF6GJ3Py88GIjBcoD239veVBHzZDMpqS9AJrznXZPNSad0nwFfuBtZ68--RKf8W3yjm5HoUQ65b8vcyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S250" t="inlineStr"/>
-      <c r="T250" t="inlineStr"/>
+      <c r="S250" t="n">
+        <v>11.1679169</v>
+      </c>
+      <c r="T250" t="n">
+        <v>77.15978320000001</v>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="n">
@@ -16267,8 +17187,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/10%25C2%25B053%2726.2%2522N%2B77%25C2%25B002%2704.8%2522E/%4010.8885481,77.0291914,1970m/data%3D!3m1!1e3!4m4!3m3!8m2!3d10.8906111!4d77.0346667!5m1!1e1%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MTEyMy4xIPu8ASoASAFQAw%253D%253D%26skid%3D1ef587f2-0632-4809-aa88-b0f0376d0ecb&amp;q=EhAkBQIB4C7guzR74cqdAFF6GJ_Py88GIjCh9Ie3bvAACwBUbd5ffyQIeRVwJ-lLHIFfr972JkrYwB51q4fnMAxSRPga5My-9A8yAnJSWgFD</t>
         </is>
       </c>
-      <c r="S251" t="inlineStr"/>
-      <c r="T251" t="inlineStr"/>
+      <c r="S251" t="n">
+        <v>10.8885481</v>
+      </c>
+      <c r="T251" t="n">
+        <v>77.0291914</v>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="n">
@@ -16329,8 +17253,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/11%25C2%25B008%2739.1%2522N%2B76%25C2%25B055%2726.4%2522E/%4011.1488539,76.8991989,9918m/data%3D!3m1!1e3!4m4!3m3!8m2!3d11.1441944!4d76.924!5m1!1e1%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MTEyMy4xIPu8ASoASAFQAw%253D%253D%26skid%3D0f8c92c4-bb78-4911-86d5-98e7f1cfdba1&amp;q=EhAkBQIB4C7guzR74cqdAFF6GKDPy88GIjAZxfFbNzEqnrsGcmf6taSIqlDoHgjA4QBn80UcBmx-iVD7HWHaHQfkluj1e24YRLkyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S252" t="inlineStr"/>
-      <c r="T252" t="inlineStr"/>
+      <c r="S252" t="n">
+        <v>11.1488539</v>
+      </c>
+      <c r="T252" t="n">
+        <v>76.8991989</v>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="n">
@@ -16391,8 +17319,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/10%25C2%25B052%2746.1%2522N%2B76%25C2%25B056%2710.2%2522E/%4010.8789497,76.9338447,1970m/data%3D!3m1!1e3!4m4!3m3!8m2!3d10.8794722!4d76.9361667!5m1!1e1%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MTEyMy4xIPu8ASoASAFQAw%253D%253D%26skid%3D0c5755eb-f4c4-43c1-9943-2fc1f4b9a396&amp;q=EhAkBQIB4C7guzR74cqdAFF6GKHPy88GIjD-ppxUqg4aBW6alFSABWD7tTXh7rW9zItq1z3Y-b5jXuKm2uz-w2Vkm3GlURDn-aAyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S253" t="inlineStr"/>
-      <c r="T253" t="inlineStr"/>
+      <c r="S253" t="n">
+        <v>10.8789497</v>
+      </c>
+      <c r="T253" t="n">
+        <v>76.93384469999999</v>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="n">
@@ -16503,8 +17435,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/11%25C2%25B002%2703.5%2522N%2B77%25C2%25B005%2731.2%2522E/%4011.0356617,77.086834,4420m/data%3D!3m1!1e3!4m4!3m3!8m2!3d11.0343056!4d77.092!5m1!1e1%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MTEyMy4xIPu8ASoASAFQAw%253D%253D%26skid%3Db4f61a1d-b9e7-4d9e-8614-e9cad36b5371&amp;q=EhAkBQIB4C7guzR74cqdAFF6GKLPy88GIjCyVzve5GRjMYe22fTxIDMQcaJYOkiAfgHqfZUcCeoD5YgT32Csttfn-ji3hTjCMqYyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S255" t="inlineStr"/>
-      <c r="T255" t="inlineStr"/>
+      <c r="S255" t="n">
+        <v>11.0356617</v>
+      </c>
+      <c r="T255" t="n">
+        <v>77.086834</v>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="n">
@@ -16565,8 +17501,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/10%25C2%25B054%2724.5%2522N%2B77%25C2%25B003%2735.0%2522E/%4010.9029419,77.0519347,5790m/data%3D!3m1!1e3!4m4!3m3!8m2!3d10.9068056!4d77.0597222!5m1!1e1%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MTEyMy4xIPu8ASoASAFQAw%253D%253D%26skid%3D9a2f6418-b235-4f25-b865-0d8bdc7f57c8&amp;q=EhAkBQIB4C7guzR74cqdAFF6GKPPy88GIjDcnLY8RJaW4ialpLhxonJoL9_1O6sjaD7i-aFBui_rFfKc2qWlr7BmnJrvBNfZRrIyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S256" t="inlineStr"/>
-      <c r="T256" t="inlineStr"/>
+      <c r="S256" t="n">
+        <v>10.9029419</v>
+      </c>
+      <c r="T256" t="n">
+        <v>77.0519347</v>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="n">
@@ -16627,8 +17567,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/11%25C2%25B003%2743.9%2522N%2B77%25C2%25B007%2701.8%2522E/%4011.0626234,77.1176162,9921m/data%3D!3m1!1e3!4m4!3m3!8m2!3d11.0621944!4d77.1171667!5m1!1e1%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MTEyMy4xIPu8ASoASAFQAw%253D%253D%26skid%3Df91254cf-0e33-4c2a-842a-00294111f34a&amp;q=EhAkBQIB4C7guzR74cqdAFF6GKTPy88GIjAiL-MaH5oCEZV0VpapJp3RbKkUFE3WbFvdSZ-6iL3Ri5smkKN2I3DWspISFygr0_UyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S257" t="inlineStr"/>
-      <c r="T257" t="inlineStr"/>
+      <c r="S257" t="n">
+        <v>11.0626234</v>
+      </c>
+      <c r="T257" t="n">
+        <v>77.1176162</v>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="n">
@@ -16689,8 +17633,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/11%25C2%25B009%2704.7%2522N%2B77%25C2%25B010%2758.7%2522E/%4011.1488389,77.1605614,17005m/data%3D!3m1!1e3!4m4!3m3!8m2!3d11.1513056!4d77.1829722!5m1!1e1%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MTEyMy4xIPu8ASoASAFQAw%253D%253D%26skid%3Df4d84112-3ca6-466c-b67f-6e919f1959a1&amp;q=EhAkBQIB4C7guzR74cqdAFF6GKXPy88GIjBQ5jC055_CEuimSAQuf1MeUmS0wBAeUISTK0znowP3GkZZsrO1PXy2YSbaqqTTs0IyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S258" t="inlineStr"/>
-      <c r="T258" t="inlineStr"/>
+      <c r="S258" t="n">
+        <v>11.1488389</v>
+      </c>
+      <c r="T258" t="n">
+        <v>77.16056140000001</v>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="n">
@@ -16751,8 +17699,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/11%25C2%25B004%2711.0%2522N%2B77%25C2%25B007%2709.9%2522E/%4011.0738047,77.1194533,1969m/data%3D!3m1!1e3!4m4!3m3!8m2!3d11.0697222!4d77.1194167!5m1!1e1%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MTEyMy4xIPu8ASoASAFQAw%253D%253D%26skid%3D55ecce18-ae76-4820-89b5-d733d9873aca&amp;q=EhAkBQIB4C7guzR74cqdAFF6GKfPy88GIjB-bHAyQ2Jjz1I7OyVlmaQmMOkQlZlKheTAiMsZxihC5_POi0D4yiM0JvPETT7_KYMyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S259" t="inlineStr"/>
-      <c r="T259" t="inlineStr"/>
+      <c r="S259" t="n">
+        <v>11.0738047</v>
+      </c>
+      <c r="T259" t="n">
+        <v>77.1194533</v>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="n">
@@ -16813,8 +17765,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place//%4011.0264779,77.0191636,1148m/data%3D!3m1!1e3!5m1!1e1%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MTEyMy4xIPu8ASoASAFQAw%253D%253D%26skid%3D5ebad539-5991-45f1-a483-e821d7d01467&amp;q=EhAkBQIB4C7guzR74cqdAFF6GKnPy88GIjChIoT4bO4lG9Uo_m_EW7UUZnypJZzmjQdcT77X45BPXzkoz9S4nPP_rbWLyFVv_V0yAnJSWgFD</t>
         </is>
       </c>
-      <c r="S260" t="inlineStr"/>
-      <c r="T260" t="inlineStr"/>
+      <c r="S260" t="n">
+        <v>11.0264779</v>
+      </c>
+      <c r="T260" t="n">
+        <v>77.0191636</v>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="n">
@@ -16875,8 +17831,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/10%25C2%25B052%2744.3%2522N%2B77%25C2%25B001%2737.9%2522E/%4010.8741556,77.0329546,1504m/data%3D!3m1!1e3!4m4!3m3!8m2!3d10.8789722!4d77.0271944!5m1!1e1%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MTEyMy4xIPu8ASoASAFQAw%253D%253D%26skid%3D08bc1c75-a18a-4547-bfa6-fa8d5faff539&amp;q=EhAkBQIB4C7guzR74cqdAFF6GKvPy88GIjDzxWRhMR7xdxajQymHHMLokmChONJdzks4QNM1fsIBEcjruk15XYsWFC_rIiHFnFsyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S261" t="inlineStr"/>
-      <c r="T261" t="inlineStr"/>
+      <c r="S261" t="n">
+        <v>10.8741556</v>
+      </c>
+      <c r="T261" t="n">
+        <v>77.0329546</v>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="n">
@@ -16937,8 +17897,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/10%25C2%25B051%2703.6%2522N%2B77%25C2%25B007%2714.6%2522E/%4010.847282,77.103669,9928m/data%3D!3m1!1e3!4m4!3m3!8m2!3d10.851!4d77.1207222!5m1!1e1%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MTEyMy4xIPu8ASoASAFQAw%253D%253D%26skid%3D72f6700f-6ea4-4bcb-b580-92b91b2960a0&amp;q=EhAkBQIB4C7guzR74cqdAFF6GKzPy88GIjBq3D8Pk9DsaHt2dVy7UKiyPamHntsFNduQVZmkkmnAbQVV88vO_JV5Zlvy63xEXvYyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S262" t="inlineStr"/>
-      <c r="T262" t="inlineStr"/>
+      <c r="S262" t="n">
+        <v>10.847282</v>
+      </c>
+      <c r="T262" t="n">
+        <v>77.103669</v>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="n">
@@ -16999,8 +17963,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/11%25C2%25B009%2739.2%2522N%2B77%25C2%25B009%2708.1%2522E/%4011.1454331,77.1364934,7575m/data%3D!3m1!1e3!4m4!3m3!8m2!3d11.1608889!4d77.15225!5m1!1e1%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MTEyMy4xIPu8ASoASAFQAw%253D%253D%26skid%3D82a8d16c-f812-4b71-88f2-dede9006d65a&amp;q=EhAkBQIB4C7guzR74cqdAFF6GK3Py88GIjDc0zO6HHKRmlV5mD8rerlVYfIj8TvtvlDbaBtrDSvufZ3PgHEKFxjKWZ7DS5LvoeQyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S263" t="inlineStr"/>
-      <c r="T263" t="inlineStr"/>
+      <c r="S263" t="n">
+        <v>11.1454331</v>
+      </c>
+      <c r="T263" t="n">
+        <v>77.13649340000001</v>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="n">
@@ -17061,8 +18029,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/10%25C2%25B058%2715.0%2522N%2B77%25C2%25B010%2717.7%2522E/%4010.975325,77.1521439,9924m/data%3D!3m1!1e3!4m4!3m3!8m2!3d10.9708333!4d77.1715833!5m1!1e1%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MTEyMy4xIPu8ASoASAFQAw%253D%253D%26skid%3D295124b1-db62-4c15-94c7-12e099275fc2&amp;q=EhAkBQIB4C7guzR74cqdAFF6GK_Py88GIjD3PdSRh0_vTA_96WRHPjfPP3vLMGyNR6IzBtlmtxf5OQiUHeejrmxDSYuAmyavgcUyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S264" t="inlineStr"/>
-      <c r="T264" t="inlineStr"/>
+      <c r="S264" t="n">
+        <v>10.975325</v>
+      </c>
+      <c r="T264" t="n">
+        <v>77.1521439</v>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="n">
@@ -17123,8 +18095,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/10%25C2%25B055%2735.1%2522N%2B77%25C2%25B010%2721.8%2522E/%4010.9406958,77.1177264,23156m/data%3D!3m1!1e3!4m4!3m3!8m2!3d10.9264167!4d77.1727222!5m1!1e1%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MTEyMy4xIPu8ASoASAFQAw%253D%253D%26skid%3Dd22aa7e2-f956-4aac-8a53-ca8c79d4506c&amp;q=EhAkBQIB4C7guzR74cqdAFF6GLHPy88GIjBCyuGjG_B6NOyZvLfDNeseHrnLjb9FxYyqeUOVsLUXXVW9Lzmv7B4MaXYYU8b2leQyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S265" t="inlineStr"/>
-      <c r="T265" t="inlineStr"/>
+      <c r="S265" t="n">
+        <v>10.9406958</v>
+      </c>
+      <c r="T265" t="n">
+        <v>77.1177264</v>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="n">
@@ -17185,8 +18161,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/11%25C2%25B008%2712.0%2522N%2B77%25C2%25B009%2708.3%2522E/%4011.1382133,77.1435127,4418m/data%3D!3m1!1e3!4m4!3m3!8m2!3d11.1366667!4d77.1523056!5m1!1e1%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MTEyMy4xIPu8ASoASAFQAw%253D%253D%26skid%3D68c87571-9f23-49f5-b65a-23ed645cd011&amp;q=EhAkBQIB4C7guzR74cqdAFF6GLLPy88GIjD0koB9a--z32-3e04YjE1zzcpIIEc39Owymtv9ZykZhRBV-LtH_QhHkQWQQgsOm_8yAnJSWgFD</t>
         </is>
       </c>
-      <c r="S266" t="inlineStr"/>
-      <c r="T266" t="inlineStr"/>
+      <c r="S266" t="n">
+        <v>11.1382133</v>
+      </c>
+      <c r="T266" t="n">
+        <v>77.1435127</v>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="n">
@@ -17247,8 +18227,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/11%25C2%25B008%2736.4%2522N%2B77%25C2%25B009%2749.4%2522E/%4011.1400915,77.1531115,5785m/data%3D!3m1!1e3!4m4!3m3!8m2!3d11.1434444!4d77.1637222!5m1!1e1%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MTEyMy4xIPu8ASoASAFQAw%253D%253D%26skid%3Dec7e874b-6611-4bac-a98d-9fd0bbfa7bc7&amp;q=EhAkBQIB4C7guzR74cqdAFF6GLPPy88GIjBC8l36K5M3BKvCd90533p-v88z5-dNwQzYXPOKmnITTPvmL_P7nrQpCyrSSIzRVccyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S267" t="inlineStr"/>
-      <c r="T267" t="inlineStr"/>
+      <c r="S267" t="n">
+        <v>11.1400915</v>
+      </c>
+      <c r="T267" t="n">
+        <v>77.15311149999999</v>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="n">
@@ -17309,8 +18293,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/10%25C2%25B054%2747.2%2522N%2B77%25C2%25B001%2749.2%2522E/%4010.9111678,77.0160748,2579m/data%3D!3m1!1e3!4m4!3m3!8m2!3d10.9131111!4d77.0303333!5m1!1e1%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MTEyMy4xIPu8ASoASAFQAw%253D%253D%26skid%3Dfa1388d9-9e98-4e0a-b96a-c07ff9ed0e02&amp;q=EhAkBQIB4C7guzR74cqdAFF6GLXPy88GIjAhBrMmKSK5wRKTuqDujJ74AejHEUcNAtXGLe5gr5jQkfYVyf7j3UaOTEhwwFpxmJ0yAnJSWgFD</t>
         </is>
       </c>
-      <c r="S268" t="inlineStr"/>
-      <c r="T268" t="inlineStr"/>
+      <c r="S268" t="n">
+        <v>10.9111678</v>
+      </c>
+      <c r="T268" t="n">
+        <v>77.0160748</v>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="n">
@@ -17371,8 +18359,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/11%25C2%25B018%2750.8%2522N%2B77%25C2%25B009%2706.3%2522E/%4011.3235666,77.1378842,7570m/data%3D!3m1!1e3!4m4!3m3!8m2!3d11.3141111!4d77.15175!5m1!1e1%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MTEyMy4xIPu8ASoASAFQAw%253D%253D%26skid%3D4f696254-05cc-4bb9-b045-8d2e54f5b694&amp;q=EhAkBQIB4C7guzR74cqdAFF6GLbPy88GIjDPQzHC51WpenCa1PwkGwS-iYeyOmNo9L85go32jBh4R9wWDhEw4vKZHDpVa-utxAoyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S269" t="inlineStr"/>
-      <c r="T269" t="inlineStr"/>
+      <c r="S269" t="n">
+        <v>11.3235666</v>
+      </c>
+      <c r="T269" t="n">
+        <v>77.1378842</v>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="n">
@@ -17433,8 +18425,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/11%25C2%25B006%2734.8%2522N%2B76%25C2%25B059%2732.1%2522E/%4011.1107198,76.9911174,4419m/data%3D!3m1!1e3!4m4!3m3!8m2!3d11.1096667!4d76.99225!5m1!1e1%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MTEyMy4xIPu8ASoASAFQAw%253D%253D%26skid%3Ddeaf279d-9968-4a54-8c76-b01a1888aec4&amp;q=EhAkBQIB4C7guzR74cqdAFF6GLfPy88GIjC6hYw8p0vY-BHgpah1wxFFFoEnqGZvrGFTpJ8GpLr6UjXRZJTT_y-hlFlFvSv5Nt0yAnJSWgFD</t>
         </is>
       </c>
-      <c r="S270" t="inlineStr"/>
-      <c r="T270" t="inlineStr"/>
+      <c r="S270" t="n">
+        <v>11.1107198</v>
+      </c>
+      <c r="T270" t="n">
+        <v>76.99111739999999</v>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="n">
@@ -17495,8 +18491,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/11%25C2%25B004%2751.9%2522N%2B76%25C2%25B059%2729.3%2522E/%4011.0822881,76.9893706,2679m/data%3D!3m1!1e3!4m4!3m3!8m2!3d11.0810833!4d76.9914722!5m1!1e1%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MTEyMy4xIPu8ASoASAFQAw%253D%253D%26skid%3D73531612-8c8a-4f20-83fa-d78f0c39dd18&amp;q=EhAkBQIB4C7guzR74cqdAFF6GLnPy88GIjD_b1mNlXOT4L99UlsZAlk4tmrR0iaoNlHMoJV-FmzWBEw2P54tztIHNqyG0V51b1syAnJSWgFD</t>
         </is>
       </c>
-      <c r="S271" t="inlineStr"/>
-      <c r="T271" t="inlineStr"/>
+      <c r="S271" t="n">
+        <v>11.0822881</v>
+      </c>
+      <c r="T271" t="n">
+        <v>76.9893706</v>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="n">
@@ -17557,8 +18557,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/10%25C2%25B058%2731.9%2522N%2B77%25C2%25B010%2724.9%2522E/%4010.9747008,77.1725427,1149m/data%3D!3m1!1e3!4m4!3m3!8m2!3d10.9755278!4d77.1735833!5m1!1e1%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MTEyMy4xIPu8ASoASAFQAw%253D%253D%26skid%3D0c61635d-ea17-4f3e-bf4f-a497b3438ebf&amp;q=EhAkBQIB4C7guzR74cqdAFF6GLrPy88GIjD7enUEh_RmciarlXf_rev5gursUce-qFndTHnZGB9B_Ekx2xbSF5N2hchIUkYzVwwyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S272" t="inlineStr"/>
-      <c r="T272" t="inlineStr"/>
+      <c r="S272" t="n">
+        <v>10.9747008</v>
+      </c>
+      <c r="T272" t="n">
+        <v>77.17254269999999</v>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="n">
@@ -17619,8 +18623,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/10%25C2%25B055%2753.1%2522N%2B77%25C2%25B005%2750.0%2522E/%4010.9308651,77.0941015,2579m/data%3D!3m1!1e3!4m4!3m3!8m2!3d10.9314167!4d77.0972222!5m1!1e1%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MTEyMy4xIPu8ASoASAFQAw%253D%253D%26skid%3D82c89340-7d5a-486b-b45a-c067e9413729&amp;q=EhAkBQIB4C7guzR74cqdAFF6GLvPy88GIjCmf8Ksx13HkxngNo5L99sqXMgPfGt2D7OeRhL3hW7wMRh5VWUoe8JiXvpbnhakwkUyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S273" t="inlineStr"/>
-      <c r="T273" t="inlineStr"/>
+      <c r="S273" t="n">
+        <v>10.9308651</v>
+      </c>
+      <c r="T273" t="n">
+        <v>77.09410149999999</v>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="n">
@@ -17681,8 +18689,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/10%25C2%25B054%2729.1%2522N%2B77%25C2%25B008%2717.3%2522E/%4010.912253,77.1302121,4422m/data%3D!3m1!1e3!4m4!3m3!8m2!3d10.9080833!4d77.1381389!5m1!1e1%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MTEyMy4xIPu8ASoASAFQAw%253D%253D%26skid%3D1b5d5234-3393-4136-9e90-4f0516ce5420&amp;q=EhAkBQIB4C7guzR74cqdAFF6GL3Py88GIjBM7N4Tu5edAyvtk3iYxh0INX7EB3fKkIE54GlYUVjSNHpzaH3KRzOLHLmlv4TP_mYyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S274" t="inlineStr"/>
-      <c r="T274" t="inlineStr"/>
+      <c r="S274" t="n">
+        <v>10.912253</v>
+      </c>
+      <c r="T274" t="n">
+        <v>77.13021209999999</v>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="n">
@@ -17743,8 +18755,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/10%25C2%25B054%2717.5%2522N%2B77%25C2%25B006%2745.4%2522E/%4010.9074908,77.094171,9926m/data%3D!3m1!1e3!4m4!3m3!8m2!3d10.9048611!4d77.1126111!5m1!1e1%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MTEyMy4xIPu8ASoASAFQAw%253D%253D%26skid%3D6de753bc-4cd4-4578-8ef7-8462caf816c1&amp;q=EhAkBQIB4C7guzR74cqdAFF6GL7Py88GIjAcns869VhjX99HerfibbMk3VaYe0OzikI9xfLOcjRUginaiLWcta0mQYanqzx59TgyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S275" t="inlineStr"/>
-      <c r="T275" t="inlineStr"/>
+      <c r="S275" t="n">
+        <v>10.9074908</v>
+      </c>
+      <c r="T275" t="n">
+        <v>77.094171</v>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="n">
@@ -17805,8 +18821,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/10%25C2%25B049%2714.7%2522N%2B77%25C2%25B009%2725.9%2522E/%4010.8166593,77.1401001,9929m/data%3D!3m1!1e3!4m4!3m3!8m2!3d10.82075!4d77.1571944!5m1!1e1%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MTEyMy4xIPu8ASoASAFQAw%253D%253D%26skid%3D428c397e-0fbb-4196-81c2-6ddb87d000bf&amp;q=EhAkBQIB4C7guzR74cqdAFF6GL_Py88GIjD668ckvMUfepIsJgo57S_-VamPKxEqa_JxwYlqF8TEg_WD0J1VMpXGMeSKNDoFC8gyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S276" t="inlineStr"/>
-      <c r="T276" t="inlineStr"/>
+      <c r="S276" t="n">
+        <v>10.8166593</v>
+      </c>
+      <c r="T276" t="n">
+        <v>77.1401001</v>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="n">
@@ -17867,8 +18887,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/11%25C2%25B003%2758.8%2522N%2B77%25C2%25B002%2714.6%2522E/%4011.0657406,77.0356396,2578m/data%3D!3m1!1e3!4m4!3m3!8m2!3d11.0663333!4d77.0373889!5m1!1e1%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MTEyMy4xIPu8ASoASAFQAw%253D%253D%26skid%3D549c513e-a393-4c89-bd6e-b715e0253b9d&amp;q=EhAkBQIB4C7guzR74cqdAFF6GMDPy88GIjCtY_uio2Nn_kxHKFada_DlFPbn21YUmcYQpW1Jl8j74iBazokRPuR76qit1lzNLJUyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S277" t="inlineStr"/>
-      <c r="T277" t="inlineStr"/>
+      <c r="S277" t="n">
+        <v>11.0657406</v>
+      </c>
+      <c r="T277" t="n">
+        <v>77.0356396</v>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="n">
@@ -17929,8 +18953,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/11%25C2%25B000%2736.2%2522N%2B76%25C2%25B056%2730.6%2522E/%4011.0112484,76.9374469,1504m/data%3D!3m1!1e3!4m4!3m3!8m2!3d11.0100556!4d76.9418333!5m1!1e1%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MTEyMy4xIPu8ASoASAFQAw%253D%253D%26skid%3D5d951324-396a-4db5-b1b7-ef1fa68720b1&amp;q=EhAkBQIB4C7guzR74cqdAFF6GMLPy88GIjAbNmT3uR5L6_DU7CskaJv9YwN_GUIxR2D3PSJbSNUH8a1if6AnyUD0EoudNdl2o4cyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S278" t="inlineStr"/>
-      <c r="T278" t="inlineStr"/>
+      <c r="S278" t="n">
+        <v>11.0112484</v>
+      </c>
+      <c r="T278" t="n">
+        <v>76.9374469</v>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="n">
@@ -17991,8 +19019,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/11%25C2%25B006%2702.1%2522N%2B77%25C2%25B009%2751.0%2522E/%4011.0998506,77.1501356,3375m/data%3D!3m1!1e3!4m4!3m3!8m2!3d11.1005833!4d77.1641667!5m1!1e1%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MTEyMy4xIPu8ASoASAFQAw%253D%253D%26skid%3Dc9027b79-208c-4102-8641-b8b6b91ec6a5&amp;q=EhAkBQIB4C7guzR74cqdAFF6GMTPy88GIjDkgUTJsH78aIFukFTBUuH-trAH9_eBMJ05d0loY1BsiLQVpq80OEbVsMXpcc2cmrIyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S279" t="inlineStr"/>
-      <c r="T279" t="inlineStr"/>
+      <c r="S279" t="n">
+        <v>11.0998506</v>
+      </c>
+      <c r="T279" t="n">
+        <v>77.1501356</v>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="n">
@@ -18053,8 +19085,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/11%25C2%25B006%2713.8%2522N%2B77%25C2%25B009%2734.5%2522E/%4011.1074913,77.1558145,3375m/data%3D!3m1!1e3!4m4!3m3!8m2!3d11.1038333!4d77.1595833!5m1!1e1%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MTEyMy4xIPu8ASoASAFQAw%253D%253D%26skid%3D1d2c647b-dd4a-4230-be30-0f7961fcf85f&amp;q=EhAkBQIB4C7guzR74cqdAFF6GMbPy88GIjA0SDxX-uLgPbB_7BGbxrnI0ZRiD3pAZm9SwZD6I5ol66kiKSTvvEgSPOGPprkVTH4yAnJSWgFD</t>
         </is>
       </c>
-      <c r="S280" t="inlineStr"/>
-      <c r="T280" t="inlineStr"/>
+      <c r="S280" t="n">
+        <v>11.1074913</v>
+      </c>
+      <c r="T280" t="n">
+        <v>77.15581450000001</v>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="n">
@@ -18115,8 +19151,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/11%25C2%25B006%2708.6%2522N%2B77%25C2%25B009%2734.1%2522E/%4011.1036753,77.158952,1968m/data%3D!3m1!1e3!4m4!3m3!8m2!3d11.1023889!4d77.1594722!5m1!1e1%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MTEyMy4xIPu8ASoASAFQAw%253D%253D%26skid%3D76eb0e4d-e254-41e4-9e73-e8c30f9b9424&amp;q=EhAkBQIB4C7guzR74cqdAFF6GMfPy88GIjDH8ZwtA06vxQNS6emRj4HeLwcR0SWDG7_8tJGMd59My4hzzVAm2ONVmZjaxhpUAREyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S281" t="inlineStr"/>
-      <c r="T281" t="inlineStr"/>
+      <c r="S281" t="n">
+        <v>11.1036753</v>
+      </c>
+      <c r="T281" t="n">
+        <v>77.158952</v>
+      </c>
     </row>
     <row r="282">
       <c r="A282" t="n">
@@ -18177,8 +19217,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/11%25C2%25B000%2717.5%2522N%2B77%25C2%25B013%2705.2%2522E/%4011.004127,77.2057256,5788m/data%3D!3m1!1e3!4m4!3m3!8m2!3d11.0048611!4d77.2181111!5m1!1e1%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MTEyMy4xIPu8ASoASAFQAw%253D%253D%26skid%3D9c95c729-2a6c-4077-8044-1f23ae1ed16e&amp;q=EhAkBQIB4C7guzR74cqdAFF6GMjPy88GIjCujUcMsqI8J1HzNIguXrczQBx_WIAL1rnpC5ftqIK_3y3fXMD9yU4gR1T276zUVeUyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S282" t="inlineStr"/>
-      <c r="T282" t="inlineStr"/>
+      <c r="S282" t="n">
+        <v>11.004127</v>
+      </c>
+      <c r="T282" t="n">
+        <v>77.20572559999999</v>
+      </c>
     </row>
     <row r="283">
       <c r="A283" t="n">
@@ -18239,8 +19283,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/11%25C2%25B007%2704.2%2522N%2B77%25C2%25B011%2708.0%2522E/%4011.1168009,77.1755451,3936m/data%3D!3m1!1e3!4m4!3m3!8m2!3d11.1178333!4d77.1855556!5m1!1e1%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MTEyMy4xIPu8ASoASAFQAw%253D%253D%26skid%3Da625b6a8-2833-474f-bac7-d0ed397fa3ee&amp;q=EhAkBQIB4C7guzR74cqdAFF6GMrPy88GIjCKeIffbiIH3J_KOHuv38TPjA49wW7KdgyisKN6IdYSLxbRO2I2f859wmm6dRkxOJ8yAnJSWgFD</t>
         </is>
       </c>
-      <c r="S283" t="inlineStr"/>
-      <c r="T283" t="inlineStr"/>
+      <c r="S283" t="n">
+        <v>11.1168009</v>
+      </c>
+      <c r="T283" t="n">
+        <v>77.17554509999999</v>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="n">
@@ -18301,8 +19349,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/11%25C2%25B006%2702.9%2522N%2B77%25C2%25B006%2700.9%2522E/%4011.1029066,77.0635365,9920m/data%3D!3m1!1e3!4m4!3m3!8m2!3d11.1008056!4d77.10025!5m1!1e1%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MTEyMy4xIPu8ASoASAFQAw%253D%253D%26skid%3D6df0febf-7190-432d-a50e-bd60a875065c&amp;q=EhAkBQIB4C7guzR74cqdAFF6GMzPy88GIjAoYTeHtITy7eMhywddj7mKw_BDtGJswtJJbaSaDLTgTm4gx5CpNfZMz-5pX67r-50yAnJSWgFD</t>
         </is>
       </c>
-      <c r="S284" t="inlineStr"/>
-      <c r="T284" t="inlineStr"/>
+      <c r="S284" t="n">
+        <v>11.1029066</v>
+      </c>
+      <c r="T284" t="n">
+        <v>77.0635365</v>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="n">
@@ -18363,8 +19415,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/11%25C2%25B006%2716.4%2522N%2B77%25C2%25B006%2705.5%2522E/%4011.101318,77.0864169,7576m/data%3D!3m1!1e3!4m4!3m3!8m2!3d11.1045556!4d77.1015278!5m1!1e1%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MTEyMy4xIPu8ASoASAFQAw%253D%253D%26skid%3D10de9a1b-339b-4716-9f57-d19c9f703a99&amp;q=EhAkBQIB4C7guzR74cqdAFF6GM3Py88GIjDQ-goj-x580tIZApJ3vk_CaaB9af4QhJpX2JC1CNkW9lLYBNy4SdCMdyXSpYiSXWAyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S285" t="inlineStr"/>
-      <c r="T285" t="inlineStr"/>
+      <c r="S285" t="n">
+        <v>11.101318</v>
+      </c>
+      <c r="T285" t="n">
+        <v>77.0864169</v>
+      </c>
     </row>
     <row r="286">
       <c r="A286" t="n">
@@ -18425,8 +19481,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/11%25C2%25B006%2716.4%2522N%2B77%25C2%25B006%2705.5%2522E/%4011.1054075,77.1001387,1503m/data%3D!3m1!1e3!4m4!3m3!8m2!3d11.1045556!4d77.1015278!5m1!1e1%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MTEyMy4xIPu8ASoASAFQAw%253D%253D%26skid%3D0b14c644-51a2-4fb7-af71-de1e96a89b0e&amp;q=EhAkBQIB4C7guzR74cqdAFF6GM7Py88GIjDlpWdWoJcwZnVz1JWaaHSoWlnrOmwgWnsAsHLk_kGs1GwCFPpHNoEnRVwC83CKq20yAnJSWgFD</t>
         </is>
       </c>
-      <c r="S286" t="inlineStr"/>
-      <c r="T286" t="inlineStr"/>
+      <c r="S286" t="n">
+        <v>11.1054075</v>
+      </c>
+      <c r="T286" t="n">
+        <v>77.1001387</v>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="n">
@@ -18487,8 +19547,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/11%25C2%25B006%2732.3%2522N%2B77%25C2%25B006%2724.8%2522E/%4011.0983551,77.1007239,5357m/data%3D!3m1!1e3!4m4!3m3!8m2!3d11.1089722!4d77.1068889!5m1!1e1%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MTEyMy4xIPu8ASoASAFQAw%253D%253D%26skid%3D388b761d-35b5-45b0-bb13-fb48ea73d0a0&amp;q=EhAkBQIB4C7guzR74cqdAFF6GM_Py88GIjCd5kEovOHILKWHbAj37A0dFSmnB8Cix4AD5i7yWMS0OLOFFOaZuKUgc5R3eT4ymksyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S287" t="inlineStr"/>
-      <c r="T287" t="inlineStr"/>
+      <c r="S287" t="n">
+        <v>11.0983551</v>
+      </c>
+      <c r="T287" t="n">
+        <v>77.10072390000001</v>
+      </c>
     </row>
     <row r="288">
       <c r="A288" t="n">
@@ -18549,8 +19613,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/11%25C2%25B008%2725.1%2522N%2B77%25C2%25B007%2705.9%2522E/%4011.1492129,77.1097193,7575m/data%3D!3m1!1e3!4m4!3m3!8m2!3d11.1403056!4d77.1183056!5m1!1e1%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MTEyMy4xIPu8ASoASAFQAw%253D%253D%26skid%3Dbb5993c7-9db9-43e4-90b3-7a412944b27e&amp;q=EhAkBQIB4C7guzR74cqdAFF6GNDPy88GIjBC2X27TybonbdSNP3e2-c8uPNP6IBnQpi_KcmXJnjlt_FdrNbo30y9l6EmJMWjydwyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S288" t="inlineStr"/>
-      <c r="T288" t="inlineStr"/>
+      <c r="S288" t="n">
+        <v>11.1492129</v>
+      </c>
+      <c r="T288" t="n">
+        <v>77.10971929999999</v>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="n">
@@ -18611,8 +19679,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/11%25C2%25B006%2758.3%2522N%2B77%25C2%25B008%2717.5%2522E/%4011.1201898,77.1244234,7575m/data%3D!3m1!1e3!4m4!3m3!8m2!3d11.1161944!4d77.1381944!5m1!1e1%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MTEyMy4xIPu8ASoASAFQAw%253D%253D%26skid%3D0e0ad877-6f2c-41bf-94af-214606b3917b&amp;q=EhAkBQIB4C7guzR74cqdAFF6GNLPy88GIjDmOoziCQtw1eoDNHod0L3wvpa6f8P2bymqXo1xIsLh-nUlTnVM9u1LayNCMzlxn6MyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S289" t="inlineStr"/>
-      <c r="T289" t="inlineStr"/>
+      <c r="S289" t="n">
+        <v>11.1201898</v>
+      </c>
+      <c r="T289" t="n">
+        <v>77.1244234</v>
+      </c>
     </row>
     <row r="290">
       <c r="A290" t="n">
@@ -18673,8 +19745,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/10%25C2%25B055%2720.0%2522N%2B76%25C2%25B059%2725.6%2522E/%4010.9214641,76.985277,1970m/data%3D!3m1!1e3!4m4!3m3!8m2!3d10.9222222!4d76.9904444!5m1!1e1%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MTEyMy4xIPu8ASoASAFQAw%253D%253D%26skid%3De8a5b47b-5dc6-4072-b84f-99cbe2e89768&amp;q=EhAkBQIB4C7guzR74cqdAFF6GNPPy88GIjDuod8XO3JR3pSwRwBZdwhdkDF_GwDfubINXhHDvncRy4XFa1h1Gb15ufm58U0fS1QyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S290" t="inlineStr"/>
-      <c r="T290" t="inlineStr"/>
+      <c r="S290" t="n">
+        <v>10.9214641</v>
+      </c>
+      <c r="T290" t="n">
+        <v>76.985277</v>
+      </c>
     </row>
     <row r="291">
       <c r="A291" t="n">
@@ -18735,8 +19811,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/10%25C2%25B049%2746.9%2522N%2B77%25C2%25B002%2744.3%2522E/%4010.8347422,77.0326336,9929m/data%3D!3m1!1e3!4m4!3m3!8m2!3d10.8296944!4d77.0456389!5m1!1e1%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MTEyMy4xIPu8ASoASAFQAw%253D%253D%26skid%3D42e8c494-5df5-43a1-9b37-91c8514003b6&amp;q=EhAkBQIB4C7guzR74cqdAFF6GNXPy88GIjBhyzPgJjzNKr_q3ngOb78cwyYWxe5onNhAt8oiI49Nr7S7O8av3K4ZMraBPaR7b_4yAnJSWgFD</t>
         </is>
       </c>
-      <c r="S291" t="inlineStr"/>
-      <c r="T291" t="inlineStr"/>
+      <c r="S291" t="n">
+        <v>10.8347422</v>
+      </c>
+      <c r="T291" t="n">
+        <v>77.0326336</v>
+      </c>
     </row>
     <row r="292">
       <c r="A292" t="n">
@@ -18797,8 +19877,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/10%25C2%25B055%2735.0%2522N%2B76%25C2%25B059%2740.0%2522E/%4010.9225238,76.9892753,4421m/data%3D!3m1!1e3!4m4!3m3!8m2!3d10.9263889!4d76.9944444!5m1!1e1%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MTEyMy4xIPu8ASoASAFQAw%253D%253D%26skid%3D7da6ee41-5212-4e72-a75b-1320e2c255cd&amp;q=EhAkBQIB4C7guzR74cqdAFF6GNbPy88GIjCoo7yiq262k2tQvzXqH6PyUmC_3HCgASpgLC19Njpl9U8ukJWJe1Lm7bwIPYAg_UwyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S292" t="inlineStr"/>
-      <c r="T292" t="inlineStr"/>
+      <c r="S292" t="n">
+        <v>10.9225238</v>
+      </c>
+      <c r="T292" t="n">
+        <v>76.9892753</v>
+      </c>
     </row>
     <row r="293">
       <c r="A293" t="n">
@@ -18859,8 +19943,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/11%25C2%25B003%2709.2%2522N%2B77%25C2%25B005%2750.9%2522E/%4011.0530397,77.0908767,1969m/data%3D!3m1!1e3!4m4!3m3!8m2!3d11.0525556!4d77.0974722!5m1!1e1%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MTEyMy4xIPu8ASoASAFQAw%253D%253D%26skid%3D94e75131-9bd8-4a93-8b0d-4854c9000530&amp;q=EhAkBQIB4C7guzR74cqdAFF6GNfPy88GIjDsxqWNDt7dEK_g4VqvhN5Nozlx9VyClFGhVIlEMIILWLUtyKnpUVgBmdWejtDOETgyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S293" t="inlineStr"/>
-      <c r="T293" t="inlineStr"/>
+      <c r="S293" t="n">
+        <v>11.0530397</v>
+      </c>
+      <c r="T293" t="n">
+        <v>77.0908767</v>
+      </c>
     </row>
     <row r="294">
       <c r="A294" t="n">
@@ -18921,8 +20009,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/11%25C2%25B002%2748.7%2522N%2B77%25C2%25B004%2747.2%2522E/%4011.0486583,77.0796113,1969m/data%3D!3m1!1e3!4m4!3m3!8m2!3d11.0468611!4d77.0797778!5m1!1e1%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MTEyMy4xIPu8ASoASAFQAw%253D%253D%26skid%3D979be141-afcc-40bb-8b00-1eb599fec21f&amp;q=EhAkBQIB4C7guzR74cqdAFF6GNjPy88GIjCrighcVHgipb-I0F4AEjVQVl7GhcYW0eFXLeQWZdCKvXHjHaJa2XRb0XCSWksXMkkyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S294" t="inlineStr"/>
-      <c r="T294" t="inlineStr"/>
+      <c r="S294" t="n">
+        <v>11.0486583</v>
+      </c>
+      <c r="T294" t="n">
+        <v>77.0796113</v>
+      </c>
     </row>
     <row r="295">
       <c r="A295" t="n">
@@ -18983,8 +20075,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/11%25C2%25B003%2717.7%2522N%2B77%25C2%25B005%2730.4%2522E/%4011.0554276,77.0911815,1894m/data%3D!3m1!1e3!4m4!3m3!8m2!3d11.0549167!4d77.0917778!5m1!1e1%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MTEyMy4xIPu8ASoASAFQAw%253D%253D%26skid%3D370b06ef-7fa7-40c6-9082-d4b0ff504c75&amp;q=EhAkBQIB4C7guzR74cqdAFF6GNnPy88GIjCcMjUU5QOahrI-zwf5eMGpRWA3jQDNF0cQNY9BKpdOgo1kOEwwon78h3RSKIFxvcoyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S295" t="inlineStr"/>
-      <c r="T295" t="inlineStr"/>
+      <c r="S295" t="n">
+        <v>11.0554276</v>
+      </c>
+      <c r="T295" t="n">
+        <v>77.0911815</v>
+      </c>
     </row>
     <row r="296">
       <c r="A296" t="n">
@@ -19045,8 +20141,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/11%25C2%25B002%2753.5%2522N%2B77%25C2%25B004%2742.9%2522E/%4011.0475214,77.0772581,860m/data%3D!3m1!1e3!4m4!3m3!8m2!3d11.0481944!4d77.0785833!5m1!1e1%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MTEyMy4xIPu8ASoASAFQAw%253D%253D%26skid%3Da4191b09-8fa8-4ce0-b950-e034a4e5af74&amp;q=EhAkBQIB4C7guzR74cqdAFF6GNvPy88GIjBJSZHkk53XptEDf65LmNW9TSSRCMtA9t7RXy8kL7RwuzSMzte1nGUeJnI86A8nU8kyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S296" t="inlineStr"/>
-      <c r="T296" t="inlineStr"/>
+      <c r="S296" t="n">
+        <v>11.0475214</v>
+      </c>
+      <c r="T296" t="n">
+        <v>77.07725809999999</v>
+      </c>
     </row>
     <row r="297">
       <c r="A297" t="n">
@@ -19107,8 +20207,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/10%25C2%25B056%2721.5%2522N%2B77%25C2%25B000%2726.3%2522E/%4010.939352,77.0065857,1563m/data%3D!3m1!1e3!4m4!3m3!8m2!3d10.9393056!4d77.0073056!5m1!1e1%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MTEyMy4xIPu8ASoASAFQAw%253D%253D%26skid%3Da84efd3d-6b29-4eb5-b22f-4f9cc06ac1bd&amp;q=EhAkBQIB4C7guzR74cqdAFF6GNzPy88GIjBhnDdh0ngU2pUEACHZ9SLPAObj8QC82uOPOxwVEulml5eKVm1NHQQFA-E9kTfeCTIyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S297" t="inlineStr"/>
-      <c r="T297" t="inlineStr"/>
+      <c r="S297" t="n">
+        <v>10.939352</v>
+      </c>
+      <c r="T297" t="n">
+        <v>77.0065857</v>
+      </c>
     </row>
     <row r="298">
       <c r="A298" t="n">
@@ -19169,8 +20273,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/11%25C2%25B001%2748.0%2522N%2B77%25C2%25B011%2712.5%2522E/%4011.0282808,77.1749775,4420m/data%3D!3m1!1e3!4m4!3m3!8m2!3d11.03!4d77.1868056!5m1!1e1%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MTEyMy4xIPu8ASoASAFQAw%253D%253D%26skid%3D403c21e2-dd16-4329-a325-e0857b4f9bed&amp;q=EhAkBQIB4C7guzR74cqdAFF6GN7Py88GIjD8Vgu1_2Zv3u0RDUJgds3ztqT6H0Q3W3E1kk8y5EkWKKMWkbI89K048czBDZjLosYyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S298" t="inlineStr"/>
-      <c r="T298" t="inlineStr"/>
+      <c r="S298" t="n">
+        <v>11.0282808</v>
+      </c>
+      <c r="T298" t="n">
+        <v>77.1749775</v>
+      </c>
     </row>
     <row r="299">
       <c r="A299" t="n">
@@ -19231,8 +20339,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/11%25C2%25B008%2732.7%2522N%2B77%25C2%25B012%2726.6%2522E/%4011.1601212,77.1810219,12986m/data%3D!3m1!1e3!4m4!3m3!8m2!3d11.1424167!4d77.2073889!5m1!1e1%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MTEyMy4xIPu8ASoASAFQAw%253D%253D%26skid%3D64500bc5-b443-4f13-8466-3296c87c4b6e&amp;q=EhAkBQIB4C7guzR74cqdAFF6GODPy88GIjBANlIbbB8jVr1KZu5Rvk04WH7IccdmDULQTbrugtQdM3iCd3jB1Tu3_WRc9h4s2M8yAnJSWgFD</t>
         </is>
       </c>
-      <c r="S299" t="inlineStr"/>
-      <c r="T299" t="inlineStr"/>
+      <c r="S299" t="n">
+        <v>11.1601212</v>
+      </c>
+      <c r="T299" t="n">
+        <v>77.1810219</v>
+      </c>
     </row>
     <row r="300">
       <c r="A300" t="n">
@@ -19293,8 +20405,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/11%25C2%25B008%2756.1%2522N%2B77%25C2%25B012%2728.8%2522E/%4011.1466207,77.1982101,5785m/data%3D!3m1!1e3!4m4!3m3!8m2!3d11.1489167!4d77.208!5m1!1e1%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MTEyMy4xIPu8ASoASAFQAw%253D%253D%26skid%3Dcf544df7-416e-4fec-88c3-6d5c846df18a&amp;q=EhAkBQIB4C7guzR74cqdAFF6GOHPy88GIjBche0h4GrAsN_MuLL8nAAp8nQeRVW6mSyGwnXhZ1hzlH1Ed4GYYnvqG7Atfdrb1skyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S300" t="inlineStr"/>
-      <c r="T300" t="inlineStr"/>
+      <c r="S300" t="n">
+        <v>11.1466207</v>
+      </c>
+      <c r="T300" t="n">
+        <v>77.1982101</v>
+      </c>
     </row>
     <row r="301">
       <c r="A301" t="n">
@@ -19355,8 +20471,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/11%25C2%25B007%2721.3%2522N%2B77%25C2%25B011%2730.6%2522E/%4011.1317051,77.1841824,9919m/data%3D!3m1!1e3!4m4!3m3!8m2!3d11.1225833!4d77.1918333!5m1!1e1%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MTEyMy4xIPu8ASoASAFQAw%253D%253D%26skid%3De12857ee-e00b-4e9c-a073-918741debc7e&amp;q=EhAkBQIB4C7guzR74cqdAFF6GOLPy88GIjAKFEIC4eBJz_Ny4nXKHyIHTH3fPHxWdsp192JEImhmNJNW0HQouG9_t_8TUqdBt5QyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S301" t="inlineStr"/>
-      <c r="T301" t="inlineStr"/>
+      <c r="S301" t="n">
+        <v>11.1317051</v>
+      </c>
+      <c r="T301" t="n">
+        <v>77.1841824</v>
+      </c>
     </row>
     <row r="302">
       <c r="A302" t="n">
@@ -19417,8 +20537,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/11%25C2%25B008%2745.7%2522N%2B77%25C2%25B012%2705.1%2522E/%4011.1567503,77.1970923,9918m/data%3D!3m1!1e3!4m4!3m3!8m2!3d11.1460278!4d77.2014167!5m1!1e1%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MTEyMy4xIPu8ASoASAFQAw%253D%253D%26skid%3D5eacf561-f7cc-4626-b9cd-1b830ed97866&amp;q=EhAkBQIB4C7guzR74cqdAFF6GOPPy88GIjDCXxn3sAgXTLXT0CwRAbAbOatvNX05va1Kj7GqUUgd0hEZiWiCAh8CZtGtiHr0py8yAnJSWgFD</t>
         </is>
       </c>
-      <c r="S302" t="inlineStr"/>
-      <c r="T302" t="inlineStr"/>
+      <c r="S302" t="n">
+        <v>11.1567503</v>
+      </c>
+      <c r="T302" t="n">
+        <v>77.19709229999999</v>
+      </c>
     </row>
     <row r="303">
       <c r="A303" t="n">
@@ -19479,8 +20603,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/10%25C2%25B056%2752.5%2522N%2B77%25C2%25B011%2709.1%2522E/%4010.9498658,77.1759994,5789m/data%3D!3m1!1e3!4m4!3m3!8m2!3d10.9479167!4d77.1858611!5m1!1e1%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MTEyMy4xIPu8ASoASAFQAw%253D%253D%26skid%3D61c6951f-f9b3-4bc9-b906-0b8d2b9bf10b&amp;q=EhAkBQIB4C7guzR74cqdAFF6GOTPy88GIjCA1gtLkje0zpf8bneL4ubkC0Dxxtr_BqPxVT28salPFNjJrH8Pzb6bRsrtWk4sOggyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S303" t="inlineStr"/>
-      <c r="T303" t="inlineStr"/>
+      <c r="S303" t="n">
+        <v>10.9498658</v>
+      </c>
+      <c r="T303" t="n">
+        <v>77.17599939999999</v>
+      </c>
     </row>
     <row r="304">
       <c r="A304" t="n">
@@ -19541,8 +20669,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/10%25C2%25B058%2707.1%2522N%2B77%25C2%25B009%2735.3%2522E/%4010.9647994,77.1534915,5359m/data%3D!3m1!1e3!4m4!3m3!8m2!3d10.9686389!4d77.1598056!5m1!1e1%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MTEyMy4xIPu8ASoASAFQAw%253D%253D%26skid%3Dab687268-cfd8-4e0a-a302-c556c155973b&amp;q=EhAkBQIB4C7guzR74cqdAFF6GOXPy88GIjAETXLM0MZnJh8Zfh-hToQkdqU_eeb3i0iywsV8lBzeQOqFjx4eDdD_aoCQ9XbZxS4yAnJSWgFD</t>
         </is>
       </c>
-      <c r="S304" t="inlineStr"/>
-      <c r="T304" t="inlineStr"/>
+      <c r="S304" t="n">
+        <v>10.9647994</v>
+      </c>
+      <c r="T304" t="n">
+        <v>77.1534915</v>
+      </c>
     </row>
     <row r="305">
       <c r="A305" t="n">
@@ -19603,8 +20735,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/10%25C2%25B057%2758.9%2522N%2B77%25C2%25B008%2709.1%2522E/%4010.965782,77.1340897,1969m/data%3D!3m1!1e3!4m4!3m3!8m2!3d10.9663611!4d77.1358611!5m1!1e1%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MTEyMy4xIPu8ASoASAFQAw%253D%253D%26skid%3D238df219-3fb7-48ce-8ec9-6251e1a910bd&amp;q=EhAkBQIB4C7guzR74cqdAFF6GObPy88GIjAdxPPEYRwMot2cBUEF0_f9rKPLDo1Rl_aPAaQu1SHvjjSgS_zF62pu54WoNOmYBUgyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S305" t="inlineStr"/>
-      <c r="T305" t="inlineStr"/>
+      <c r="S305" t="n">
+        <v>10.965782</v>
+      </c>
+      <c r="T305" t="n">
+        <v>77.1340897</v>
+      </c>
     </row>
     <row r="306">
       <c r="A306" t="n">
@@ -19665,8 +20801,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/Sulur,%2BTamil%2BNadu%2B641658/%4010.9374662,77.1419044,6253m/data%3D!3m1!1e3!4m6!3m5!1s0x3ba8531edd95f737:0xf9ad124131056ade!8m2!3d10.938263!4d77.1680226!16s%252Fg%252F11k6_3y1hh!5m1!1e1%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MTEyMy4xIPu8ASoASAFQAw%253D%253D%26skid%3D2b1c6f9e-657c-4367-9797-4073ab67526a&amp;q=EhAkBQIB4C7guzR74cqdAFF6GOnPy88GIjD4Tx5F4q2O19sEJ3WylEd1cqIrAk2GafmFoC6WpM5X-gdIGhfas160k6EEQFD4ynwyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S306" t="inlineStr"/>
-      <c r="T306" t="inlineStr"/>
+      <c r="S306" t="n">
+        <v>10.9374662</v>
+      </c>
+      <c r="T306" t="n">
+        <v>77.1419044</v>
+      </c>
     </row>
     <row r="307">
       <c r="A307" t="n">
@@ -19727,8 +20867,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/10%25C2%25B054%2736.2%2522N%2B77%25C2%25B010%2716.8%2522E/%4010.9207949,77.1593754,11579m/data%3D!3m1!1e3!4m4!3m3!8m2!3d10.9100556!4d77.1713333!5m1!1e1%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MTEyMy4xIPu8ASoASAFQAw%253D%253D%26skid%3D178a4216-d82b-4b39-a7a7-e4893162d8ac&amp;q=EhAkBQIB4C7guzR74cqdAFF6GOrPy88GIjBMUdT3lCNefZXWjScVrnzbUJWmwiNMtQrTFzzKzsZHUm1uBFEnISu5LRMsnP8RJQMyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S307" t="inlineStr"/>
-      <c r="T307" t="inlineStr"/>
+      <c r="S307" t="n">
+        <v>10.9207949</v>
+      </c>
+      <c r="T307" t="n">
+        <v>77.1593754</v>
+      </c>
     </row>
     <row r="308">
       <c r="A308" t="n">
@@ -19789,8 +20933,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/10%25C2%25B057%2708.3%2522N%2B77%25C2%25B008%2756.2%2522E/%4010.9566511,77.1305758,7580m/data%3D!3m1!1e3!4m4!3m3!8m2!3d10.9523056!4d77.1489444!5m1!1e1%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MTEyMy4xIPu8ASoASAFQAw%253D%253D%26skid%3D20c1ba35-6b8d-47b8-bee9-b63d2bfc3cf9&amp;q=EhAkBQIB4C7guzR74cqdAFF6GOvPy88GIjABfZUJYiMwR53REjDDBIklnPssuP9UbnIZVMHW6qdcPxWOqj1LwTLk4njgr7LIvsQyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S308" t="inlineStr"/>
-      <c r="T308" t="inlineStr"/>
+      <c r="S308" t="n">
+        <v>10.9566511</v>
+      </c>
+      <c r="T308" t="n">
+        <v>77.1305758</v>
+      </c>
     </row>
     <row r="309">
       <c r="A309" t="n">
@@ -19851,8 +20999,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/10%25C2%25B050%2730.3%2522N%2B77%25C2%25B001%2730.8%2522E/%4010.8437693,77.0110842,8845m/data%3D!3m1!1e3!4m4!3m3!8m2!3d10.84175!4d77.0252222!5m1!1e1%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MTEyMy4xIPu8ASoASAFQAw%253D%253D%26skid%3D2183b330-ad8f-4223-bea8-65e7b5905f4c&amp;q=EhAkBQIB4C7guzR74cqdAFF6GO3Py88GIjDjr9kEGEaumJRMD_U-f8SyfucVOb1P22xxLeJ_D1nFw4s4rvyE07WfsvLhHnDs9h8yAnJSWgFD</t>
         </is>
       </c>
-      <c r="S309" t="inlineStr"/>
-      <c r="T309" t="inlineStr"/>
+      <c r="S309" t="n">
+        <v>10.8437693</v>
+      </c>
+      <c r="T309" t="n">
+        <v>77.0110842</v>
+      </c>
     </row>
     <row r="310">
       <c r="A310" t="n">
@@ -19913,8 +21065,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/10%25C2%25B052%2758.2%2522N%2B77%25C2%25B001%2754.6%2522E/%4010.8813818,77.02372,9927m/data%3D!3m1!1e3!4m4!3m3!8m2!3d10.8828333!4d77.0318333!5m1!1e1%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MTEyMy4xIPu8ASoASAFQAw%253D%253D%26skid%3Db0768510-0879-48dc-bf7f-edb24c8d8f88&amp;q=EhAkBQIB4C7guzR74cqdAFF6GO_Py88GIjB6IyQuB8sG5CRK3rWTc-ANUDeqUDhZi4TGwDIWDQcVb7Io2LeDjPFYe1AR_Yg2JWAyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S310" t="inlineStr"/>
-      <c r="T310" t="inlineStr"/>
+      <c r="S310" t="n">
+        <v>10.8813818</v>
+      </c>
+      <c r="T310" t="n">
+        <v>77.02372</v>
+      </c>
     </row>
     <row r="311">
       <c r="A311" t="n">
@@ -19975,8 +21131,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/10%25C2%25B056%2716.1%2522N%2B77%25C2%25B007%2738.1%2522E/%4010.9368808,77.1102183,4421m/data%3D!3m1!1e3!4m4!3m3!8m2!3d10.9378056!4d77.12725!5m1!1e1%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MTEyMy4xIPu8ASoASAFQAw%253D%253D%26skid%3D7600a9a2-0612-4814-b73c-97cda27d944c&amp;q=EhAkBQIB4C7guzR74cqdAFF6GPDPy88GIjA4x649iXneQFyuDMnXiP1UEnIl2CpDMZTYbh-9nRh3W-XBujsj6aEO1IuDmDeG8IoyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S311" t="inlineStr"/>
-      <c r="T311" t="inlineStr"/>
+      <c r="S311" t="n">
+        <v>10.9368808</v>
+      </c>
+      <c r="T311" t="n">
+        <v>77.1102183</v>
+      </c>
     </row>
     <row r="312">
       <c r="A312" t="n">
@@ -20037,8 +21197,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/10%25C2%25B057%2714.8%2522N%2B77%25C2%25B007%2749.6%2522E/%4010.9546164,77.1279791,1504m/data%3D!3m1!1e3!4m4!3m3!8m2!3d10.9541111!4d77.1304444!5m1!1e1%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MTEyMy4xIPu8ASoASAFQAw%253D%253D%26skid%3De50a3fed-554b-4a6f-b5ca-c4d812e0c1b3&amp;q=EhAkBQIB4C7guzR74cqdAFF6GPHPy88GIjDMqJsDZZj7aqXfZN6804nT9JY15W3V9R0Aq677O-lCevqytrbzx7s1gOD-derZTucyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S312" t="inlineStr"/>
-      <c r="T312" t="inlineStr"/>
+      <c r="S312" t="n">
+        <v>10.9546164</v>
+      </c>
+      <c r="T312" t="n">
+        <v>77.1279791</v>
+      </c>
     </row>
     <row r="313">
       <c r="A313" t="n">
@@ -20099,8 +21263,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/11%25C2%25B009%2747.1%2522N%2B77%25C2%25B013%2704.2%2522E/%4011.1696818,77.2248873,11569m/data%3D!3m1!1e3!4m4!3m3!8m2!3d11.1630833!4d77.2178333!5m1!1e1%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MTEyMy4xIPu8ASoASAFQAw%253D%253D%26skid%3Dba3169e8-97a4-4295-93b0-34085772c6bf&amp;q=EhAkBQIB4C7guzR74cqdAFF6GPLPy88GIjDCtTReejqkEVWbxkmWamN4MnMjcYH_T7SlML12n_nC6fTCW8VBljE5TgVXFHCFcowyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S313" t="inlineStr"/>
-      <c r="T313" t="inlineStr"/>
+      <c r="S313" t="n">
+        <v>11.1696818</v>
+      </c>
+      <c r="T313" t="n">
+        <v>77.22488730000001</v>
+      </c>
     </row>
     <row r="314">
       <c r="A314" t="n">
@@ -20161,8 +21329,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/10%25C2%25B055%2752.5%2522N%2B77%25C2%25B008%2755.2%2522E/%4010.9313425,77.1388851,6498m/data%3D!3m1!1e3!4m4!3m3!8m2!3d10.93125!4d77.1486667!5m1!1e1%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MTEyMy4xIPu8ASoASAFQAw%253D%253D%26skid%3Dfea1b47b-ff04-48be-97fe-56526e4737c4&amp;q=EhAkBQIB4C7guzR74cqdAFF6GPPPy88GIjC5ov3WsxxqeBnMON7S2vayi8i75tTIstqMfFXdYxk9Jq72H1C2WlydXKX_RPE5uzsyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S314" t="inlineStr"/>
-      <c r="T314" t="inlineStr"/>
+      <c r="S314" t="n">
+        <v>10.9313425</v>
+      </c>
+      <c r="T314" t="n">
+        <v>77.1388851</v>
+      </c>
     </row>
     <row r="315">
       <c r="A315" t="n">
@@ -20223,8 +21395,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/11%25C2%25B012%2735.3%2522N%2B77%25C2%25B009%2726.3%2522E/%4011.2093908,77.1467711,4417m/data%3D!3m1!1e3!4m4!3m3!8m2!3d11.2098056!4d77.1573056!5m1!1e1%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MTEyMy4xIPu8ASoASAFQAw%253D%253D%26skid%3Ddfc627e7-38f5-4f38-8b63-f826ab7917c9&amp;q=EhAkBQIB4C7guzR74cqdAFF6GPXPy88GIjCYTftq_NmI5Q6sDbidQaZkHkl-SDgv82DCml4a3ibgPzpv1c1iuiPEqoPQbwF5bpsyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S315" t="inlineStr"/>
-      <c r="T315" t="inlineStr"/>
+      <c r="S315" t="n">
+        <v>11.2093908</v>
+      </c>
+      <c r="T315" t="n">
+        <v>77.1467711</v>
+      </c>
     </row>
     <row r="316">
       <c r="A316" t="n">
@@ -20285,8 +21461,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/10%25C2%25B056%2700.2%2522N%2B77%25C2%25B010%2715.5%2522E/%4010.9296022,77.1481482,9926m/data%3D!3m1!1e3!4m4!3m3!8m2!3d10.9333889!4d77.1709722!5m1!1e1%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MTEyMy4xIPu8ASoASAFQAw%253D%253D%26skid%3D9ac6657c-2702-4484-bb15-24397fbfc468&amp;q=EhAkBQIB4C7guzR74cqdAFF6GPbPy88GIjAjNGScFpEa5QlNcOHDze3NjOiyujACgRtUatx77R2SKevBGICjFH1P7K8bqNX3iD8yAnJSWgFD</t>
         </is>
       </c>
-      <c r="S316" t="inlineStr"/>
-      <c r="T316" t="inlineStr"/>
+      <c r="S316" t="n">
+        <v>10.9296022</v>
+      </c>
+      <c r="T316" t="n">
+        <v>77.14814819999999</v>
+      </c>
     </row>
     <row r="317">
       <c r="A317" t="n">
@@ -20347,8 +21527,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/11%25C2%25B003%2754.6%2522N%2B77%25C2%25B002%2756.9%2522E/%4011.0645581,77.0457561,2296m/data%3D!3m1!1e3!4m4!3m3!8m2!3d11.0651667!4d77.0491389!5m1!1e1%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MTEyMy4xIPu8ASoASAFQAw%253D%253D%26skid%3D969fc520-ad17-41e3-970c-ec8b8fb5dcad&amp;q=EhAkBQIB4C7guzR74cqdAFF6GPjPy88GIjDzdWUi3kOe82AsRFkHGHynraXL_DPi76H8w8p208WgTExe-NStKH1u5qboX01aJQUyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S317" t="inlineStr"/>
-      <c r="T317" t="inlineStr"/>
+      <c r="S317" t="n">
+        <v>11.0645581</v>
+      </c>
+      <c r="T317" t="n">
+        <v>77.04575610000001</v>
+      </c>
     </row>
     <row r="318">
       <c r="A318" t="n">
@@ -20409,8 +21593,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/10%25C2%25B057%2745.8%2522N%2B77%25C2%25B009%2732.0%2522E/%4010.9699501,77.1534069,6752m/data%3D!3m1!1e3!4m4!3m3!8m2!3d10.9627222!4d77.1588889!5m1!1e1%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MTEyMy4xIPu8ASoASAFQAw%253D%253D%26skid%3D6c292247-108d-4eb6-8983-ad2b58c25d59&amp;q=EhAkBQIB4C7guzR74cqdAFF6GPrPy88GIjBeDhEAkSsWV43yg6KV_rAlfKyrw5oaxox6j9Btyr6q1PtcxZ6XHteDJgu_efv8BlAyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S318" t="inlineStr"/>
-      <c r="T318" t="inlineStr"/>
+      <c r="S318" t="n">
+        <v>10.9699501</v>
+      </c>
+      <c r="T318" t="n">
+        <v>77.15340689999999</v>
+      </c>
     </row>
     <row r="319">
       <c r="A319" t="n">
@@ -20473,8 +21661,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/11%25C2%25B004%2724.1%2522N%2B77%25C2%25B003%2705.4%2522E/%4011.0743648,77.0415965,1754m/data%3D!3m1!1e3!4m4!3m3!8m2!3d11.0733611!4d77.0515!5m1!1e1%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MTEyMy4xIPu8ASoASAFQAw%253D%253D%26skid%3Ddeabab1c-c697-460c-934c-54c8ac3fffb5&amp;q=EhAkBQIB4C7guzR74cqdAFF6GPvPy88GIjBfW7Q8ircjRGGMYKt5yjTIUItq-PzP1gVKVB-IX_Zv5R0R7TNFytldiKYCrDOY_zMyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S319" t="inlineStr"/>
-      <c r="T319" t="inlineStr"/>
+      <c r="S319" t="n">
+        <v>11.0743648</v>
+      </c>
+      <c r="T319" t="n">
+        <v>77.0415965</v>
+      </c>
     </row>
     <row r="320">
       <c r="A320" t="n">
@@ -20521,8 +21713,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/11%25C2%25B008%2707.4%2522N%2B77%25C2%25B006%2741.0%2522E/%4011.1181075,77.1218053,9668m/data%3D!3m1!1e3!4m4!3m3!8m2!3d11.1353858!4d77.1113839!5m1!1e1%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MTEwNC4xIPu8ASoASAFQAw%253D%253D%26skid%3D524b28c9-5989-4b7b-bd86-3ed2c57e17bf&amp;q=EhAkBQIB4C7guzR74cqdAFF6GPzPy88GIjDhncScy_e4GvP2PXYJZrbzF_TcyS7EDkKBn2DKXJiCFD5hlsIR5ThxlDsYLpTkJgkyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S320" t="inlineStr"/>
-      <c r="T320" t="inlineStr"/>
+      <c r="S320" t="n">
+        <v>11.1181075</v>
+      </c>
+      <c r="T320" t="n">
+        <v>77.12180530000001</v>
+      </c>
     </row>
     <row r="321">
       <c r="A321" t="n">
@@ -20569,8 +21765,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/11%25C2%25B008%2701.6%2522N%2B77%25C2%25B007%2736.4%2522E/%4011.1237768,77.1273168,6836m/data%3D!3m1!1e3!4m4!3m3!8m2!3d11.133771!4d77.126768!5m1!1e1%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MTEwNC4xIPu8ASoASAFQAw%253D%253D%26skid%3Dfcdaf16a-8cad-4657-bfdf-a3ab130d26ae&amp;q=EhAkBQIB4C7guzR74cqdAFF6GP7Py88GIjD46vthFqecLTMrnWFR9UF0uyXynB_kTkqc3ExbYMfZewBQjWGTUPzzKvxoHxbQeqgyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S321" t="inlineStr"/>
-      <c r="T321" t="inlineStr"/>
+      <c r="S321" t="n">
+        <v>11.1237768</v>
+      </c>
+      <c r="T321" t="n">
+        <v>77.1273168</v>
+      </c>
     </row>
     <row r="322">
       <c r="A322" t="n">
@@ -20617,8 +21817,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/11%25C2%25B025%2729.6%2522N%2B77%25C2%25B011%2743.0%2522E/%4011.4248995,77.1927015,854m/data%3D!3m2!1e3!4b1!4m4!3m3!8m2!3d11.4248995!4d77.1952764!5m1!1e1%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MTExNy4wIPu8ASoASAFQAw%253D%253D%26skid%3D50b7d7fa-7f1a-42c2-a006-76a7198c1945&amp;q=EhAkBQIB4C7guzR74cqdAFF6GP_Py88GIjBc0FINlaoo3QA1DgR6KftboDp--KleHdoYlVLIc0SP0m9dEBKYXHiuxk_w10ogzaQyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S322" t="inlineStr"/>
-      <c r="T322" t="inlineStr"/>
+      <c r="S322" t="n">
+        <v>11.4248995</v>
+      </c>
+      <c r="T322" t="n">
+        <v>77.1927015</v>
+      </c>
     </row>
     <row r="323">
       <c r="A323" t="n">
@@ -20661,8 +21865,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/11%25C2%25B018%2719.8%2522N%2B76%25C2%25B056%2730.4%2522E/%4011.305505,76.941774,854m/data%3D!3m2!1e3!4b1!4m4!3m3!8m2!3d11.305505!4d76.941774!5m1!1e1%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MTExNy4wIPu8ASoASAFQAw%253D%253D%26skid%3Dbc962e21-5fea-446e-9c73-e8f3e14a41de&amp;q=EhAkBQIB4C7guzR74cqdAFF6GIDQy88GIjBaCkgYALyT9vvWKbnMa_sr5ajSABOey44IYNgtc3286uZQVMAdzoz4E_bVcZ4f6cYyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S323" t="inlineStr"/>
-      <c r="T323" t="inlineStr"/>
+      <c r="S323" t="n">
+        <v>11.305505</v>
+      </c>
+      <c r="T323" t="n">
+        <v>76.941774</v>
+      </c>
     </row>
     <row r="324">
       <c r="A324" t="n">
@@ -20709,8 +21917,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/11%25C2%25B002%2747.9%2522N%2B77%25C2%25B008%2747.7%2522E/%4011.0466051,77.1457999,855m/data%3D!3m1!1e3!4m4!3m3!8m2!3d11.0466329!4d77.1465928!5m1!1e1%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MTExNy4wIPu8ASoASAFQAw%253D%253D%26skid%3D49afb32e-c195-41b6-81e4-7cb56157a130&amp;q=EhAkBQIB4C7guzR74cqdAFF6GILQy88GIjDRALZVF3VkSD9dzJLGDHByNurS_vnEGBiPQfdogzTpzw5QMtWQCACHNQAe7aoCAi0yAnJSWgFD</t>
         </is>
       </c>
-      <c r="S324" t="inlineStr"/>
-      <c r="T324" t="inlineStr"/>
+      <c r="S324" t="n">
+        <v>11.0466051</v>
+      </c>
+      <c r="T324" t="n">
+        <v>77.1457999</v>
+      </c>
     </row>
     <row r="325">
       <c r="A325" t="n">
@@ -20761,8 +21973,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/11%25C2%25B007%2731.7%2522N%2B77%25C2%25B004%2707.3%2522E/%4011.1254601,77.0661162,855m/data%3D!3m2!1e3!4b1!4m4!3m3!8m2!3d11.1254601!4d77.0686911!5m1!1e1%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MTExNy4wIPu8ASoASAFQAw%253D%253D%26skid%3Df9ae1c47-f424-445f-bb77-8c29df48ecab&amp;q=EhAkBQIB4C7guzR74cqdAFF6GITQy88GIjDwXUC8okFlSncRwMHQTTSSDQlt4uPFpHjkxGdTu4Y3_GdnkTHwUBRVImr3Re4d4FYyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S325" t="inlineStr"/>
-      <c r="T325" t="inlineStr"/>
+      <c r="S325" t="n">
+        <v>11.1254601</v>
+      </c>
+      <c r="T325" t="n">
+        <v>77.0661162</v>
+      </c>
     </row>
     <row r="326">
       <c r="A326" t="n">
@@ -20813,8 +22029,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/10%25C2%25B059%2722.9%2522N%2B77%25C2%25B007%2740.2%2522E/%4010.9897007,77.1252483,855m/data%3D!3m2!1e3!4b1!4m4!3m3!8m2!3d10.9897007!4d77.1278232!5m1!1e1%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MTExNy4wIPu8ASoASAFQAw%253D%253D%26skid%3Dd6cd8459-7196-45eb-8f6b-b3fbe0767009&amp;q=EhAkBQIB4C7guzR74cqdAFF6GIbQy88GIjAh2rPrDV0Au2lw8icqM_fRgZaoPPzpauQXvoY2bzQ29BgXP-uQ2YdEwqtxUbML1xIyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S326" t="inlineStr"/>
-      <c r="T326" t="inlineStr"/>
+      <c r="S326" t="n">
+        <v>10.9897007</v>
+      </c>
+      <c r="T326" t="n">
+        <v>77.1252483</v>
+      </c>
     </row>
     <row r="327">
       <c r="A327" t="n">
@@ -20893,8 +22113,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/Velliyanthottam%2BRd,%2BSengathurai,%2BTamil%2BNadu%2B641401/%4011.0497368,77.1610665,855m/data%3D!3m2!1e3!4b1!4m6!3m5!1s0x3ba8556e76c2b021:0xc035246373e71b89!8m2!3d11.0497368!4d77.1610665!16s%252Fg%252F1hhvvs674!5m1!1e1%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MTExNy4wIPu8ASoASAFQAw%253D%253D%26skid%3Df1541dd2-4cd3-48a1-bc23-ae7d212bbef9&amp;q=EhAkBQIB4C7guzR74cqdAFF6GIfQy88GIjAMTWSrhJBDrgNk8kll9vGXNHnVKKk-BB-LoBOTOTrs73uM9JbNR_zOa8pxaTVeGXYyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S328" t="inlineStr"/>
-      <c r="T328" t="inlineStr"/>
+      <c r="S328" t="n">
+        <v>11.0497368</v>
+      </c>
+      <c r="T328" t="n">
+        <v>77.1610665</v>
+      </c>
     </row>
     <row r="329">
       <c r="A329" t="n">
@@ -20953,8 +22177,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/10%25C2%25B056%2756.3%2522N%2B76%25C2%25B043%2730.9%2522E/%4010.9489756,76.7226601,855m/data%3D!3m2!1e3!4b1!4m4!3m3!8m2!3d10.9489756!4d76.725235!5m1!1e1%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MTExNy4wIPu8ASoASAFQAw%253D%253D%26skid%3Dcd10c3e5-471f-4ffe-81c5-f98b71835d35&amp;q=EhAkBQIB4C7guzR74cqdAFF6GIjQy88GIjAmGajSrEQ3zy_xcmvZNOMWfRMgklaSEuASZO8N2tzHysYAe9xRrf0BO_DzPnEg9nAyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S329" t="inlineStr"/>
-      <c r="T329" t="inlineStr"/>
+      <c r="S329" t="n">
+        <v>10.9489756</v>
+      </c>
+      <c r="T329" t="n">
+        <v>76.7226601</v>
+      </c>
     </row>
     <row r="330">
       <c r="A330" t="n">
@@ -21005,8 +22233,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/11%25C2%25B016%2723.0%2522N%2B77%25C2%25B001%2701.0%2522E/%4011.2730532,77.0143776,854m/data%3D!3m2!1e3!4b1!4m4!3m3!8m2!3d11.2730532!4d77.0169525!5m1!1e1%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MTExNy4wIPu8ASoASAFQAw%253D%253D%26skid%3D19312202-3817-4a7d-aeb2-4220c9f4c714&amp;q=EhAkBQIB4C7guzR74cqdAFF6GIrQy88GIjBDPBLUNfILMF1-1XtTV7NXInEojVfMgStawFOB0TL7wjxyalUdlBeMibw4_OMlNwMyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S330" t="inlineStr"/>
-      <c r="T330" t="inlineStr"/>
+      <c r="S330" t="n">
+        <v>11.2730532</v>
+      </c>
+      <c r="T330" t="n">
+        <v>77.0143776</v>
+      </c>
     </row>
     <row r="331">
       <c r="A331" t="n">
@@ -21061,8 +22293,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/11%25C2%25B018%2721.0%2522N%2B76%25C2%25B056%2729.0%2522E/%4011.3043157,76.9372349,2031m/data%3D!3m1!1e3!4m4!3m3!8m2!3d11.3058256!4d76.9413774!5m1!1e1%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MTExNy4wIPu8ASoASAFQAw%253D%253D%26skid%3D4e7c8d2c-d05f-4af6-9354-3a98fc675570&amp;q=EhAkBQIB4C7guzR74cqdAFF6GIvQy88GIjAFu76iv5zRoRR0Nmhb7I8pKTWVPm1XZKOVJxZyFor9hN1TKcPF5aDS7vNmD9gGKP8yAnJSWgFD</t>
         </is>
       </c>
-      <c r="S331" t="inlineStr"/>
-      <c r="T331" t="inlineStr"/>
+      <c r="S331" t="n">
+        <v>11.3043157</v>
+      </c>
+      <c r="T331" t="n">
+        <v>76.93723490000001</v>
+      </c>
     </row>
     <row r="332">
       <c r="A332" t="n">
@@ -21117,8 +22353,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/11%25C2%25B012%2759.2%2522N%2B77%25C2%25B001%2713.3%2522E/%4011.2164467,77.0177968,854m/data%3D!3m2!1e3!4b1!4m4!3m3!8m2!3d11.2164467!4d77.0203717!5m1!1e1%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MTExNy4wIPu8ASoASAFQAw%253D%253D%26skid%3Df1b91c64-e91a-46e1-9fbf-951490f89418&amp;q=EhAkBQIB4C7guzR74cqdAFF6GIzQy88GIjCEdrdqYXJxOFXzuklgbE61_rRv9L_CX1BK8APpD0xA6VBYHpSDnAwgH1ZOHVq_orcyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S332" t="inlineStr"/>
-      <c r="T332" t="inlineStr"/>
+      <c r="S332" t="n">
+        <v>11.2164467</v>
+      </c>
+      <c r="T332" t="n">
+        <v>77.0177968</v>
+      </c>
     </row>
     <row r="333">
       <c r="A333" t="n">
@@ -21173,8 +22413,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/SRK%2BMiraj%2Bcinemas/%4011.0031322,77.060043,1438m/data%3D!3m1!1e3!4m6!3m5!1s0x3ba857b203ac51f5:0x84b28d7083bac205!8m2!3d11.002924!4d77.0605624!16s%252Fg%252F11qn0b5_8m!5m1!1e1%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MTEyMy4xIPu8ASoASAFQAw%253D%253D%26skid%3Dd259c827-f226-41ae-887d-51de28feb956&amp;q=EhAkBQIB4C7guzR74cqdAFF6GI3Qy88GIjC9uTurwEwEes0JfZ7gD8mzqn102Dl3JkC44tNmz_lcaCK6XsIMWmeCgG2m7K-00twyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S333" t="inlineStr"/>
-      <c r="T333" t="inlineStr"/>
+      <c r="S333" t="n">
+        <v>11.0031322</v>
+      </c>
+      <c r="T333" t="n">
+        <v>77.06004299999999</v>
+      </c>
     </row>
     <row r="334">
       <c r="A334" t="n">
@@ -21225,8 +22469,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/11%25C2%25B003%2733.0%2522N%2B77%25C2%25B004%2722.8%2522E/%4011.0586467,77.0671002,2417m/data%3D!3m1!1e3!4m4!3m3!8m2!3d11.059155!4d77.072988!5m1!1e1!17m2!4m1!1e3!18m1!1e1%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MTExNy4wIPu8ASoASAFQAw%253D%253D%26skid%3D793ff218-562b-403a-a00f-256b2d926bb2&amp;q=EhAkBQIB4C7guzR74cqdAFF6GI7Qy88GIjAmzzVytvVY_FoKHHlmtpuH7XzMJN-8EGDvP3iuZTvKDLDOBQsrDZ-8q6lRp96oVukyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S334" t="inlineStr"/>
-      <c r="T334" t="inlineStr"/>
+      <c r="S334" t="n">
+        <v>11.0586467</v>
+      </c>
+      <c r="T334" t="n">
+        <v>77.0671002</v>
+      </c>
     </row>
     <row r="335">
       <c r="A335" t="n">
@@ -21273,8 +22521,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/11%25C2%25B002%2749.2%2522N%2B77%25C2%25B003%2718.3%2522E/%4011.0473457,77.0534083,604m/data%3D!3m1!1e3!4m4!3m3!8m2!3d11.046992!4d77.055092!5m1!1e1!17m2!4m1!1e3!18m1!1e1%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MTEyMy4xIPu8ASoASAFQAw%253D%253D%26skid%3D6df0dd4b-b839-4b72-a5f8-9732bc9fa059&amp;q=EhAkBQIB4C7guzR74cqdAFF6GJDQy88GIjAGHnzmIoVIL5RrX1I0S6zNitEwIrqzJp36m-1Xl9V1Qst-d5hgifZSTieZcSFgbTUyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S335" t="inlineStr"/>
-      <c r="T335" t="inlineStr"/>
+      <c r="S335" t="n">
+        <v>11.0473457</v>
+      </c>
+      <c r="T335" t="n">
+        <v>77.0534083</v>
+      </c>
     </row>
     <row r="336">
       <c r="A336" t="n">
@@ -21325,8 +22577,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/11%25C2%25B001%2749.4%2522N%2B77%25C2%25B001%2734.3%2522E/%4011.0310874,77.0201434,3419m/data%3D!3m1!1e3!4m4!3m3!8m2!3d11.0303889!4d77.0261944!5m1!1e1%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MTEyMy4xIPu8ASoASAFQAw%253D%253D%26skid%3D3fecbc3a-0928-48d9-9080-98bc4912f251&amp;q=EhAkBQIB4C7guzR74cqdAFF6GJPQy88GIjD7WPK8uBB4PK0g0oofdjcEh8AElzBDYFbWEmZQjlDnMSTTq3o9sHoZQ2Yl1E8UddUyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S336" t="inlineStr"/>
-      <c r="T336" t="inlineStr"/>
+      <c r="S336" t="n">
+        <v>11.0310874</v>
+      </c>
+      <c r="T336" t="n">
+        <v>77.02014339999999</v>
+      </c>
     </row>
     <row r="337">
       <c r="A337" t="n">
@@ -21377,8 +22633,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/11%25C2%25B000%2722.4%2522N%2B76%25C2%25B053%2753.2%2522E/%4011.0054867,76.8932166,3419m/data%3D!3m1!1e3!4m4!3m3!8m2!3d11.0062222!4d76.8981111!5m1!1e1%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MTEyMy4xIPu8ASoASAFQAw%253D%253D%26skid%3Df1c688e8-ff58-4aaf-82f0-c1b23239bc5f&amp;q=EhAkBQIB4C7guzR74cqdAFF6GJXQy88GIjBBAPFu8YBXcM3-0JWQpPgpr8WZW4_h5VW9GqUGnyU_nZI8IIyOkkVgl1YwoAB8cTwyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S337" t="inlineStr"/>
-      <c r="T337" t="inlineStr"/>
+      <c r="S337" t="n">
+        <v>11.0054867</v>
+      </c>
+      <c r="T337" t="n">
+        <v>76.8932166</v>
+      </c>
     </row>
     <row r="338">
       <c r="A338" t="n">
@@ -21433,8 +22693,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/10%25C2%25B056%2757.7%2522N%2B77%25C2%25B006%2748.9%2522E/%4010.9523747,77.1062734,4186m/data%3D!3m1!1e3!4m4!3m3!8m2!3d10.9493675!4d77.1135864!5m1!1e1%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MTEyMy4xIPu8ASoASAFQAw%253D%253D%26skid%3D0f314206-8f96-4cfa-8c48-966f6b661d3f&amp;q=EhAkBQIB4C7guzR74cqdAFF6GJbQy88GIjDVQUKBTZbPE-MTJ4ijW2oRMz8AhhsSQlMloGFcUBDo-phCm7F4lG86F7LRct1QrrIyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S338" t="inlineStr"/>
-      <c r="T338" t="inlineStr"/>
+      <c r="S338" t="n">
+        <v>10.9523747</v>
+      </c>
+      <c r="T338" t="n">
+        <v>77.10627340000001</v>
+      </c>
     </row>
     <row r="339">
       <c r="A339" t="n">
@@ -21489,8 +22753,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/10%25C2%25B049%2758.9%2522N%2B76%25C2%25B052%2732.4%2522E/%4010.8330322,76.8730819,855m/data%3D!3m2!1e3!4b1!4m4!3m3!8m2!3d10.8330322!4d76.8756568!5m1!1e1%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MTEyMy4xIPu8ASoASAFQAw%253D%253D%26skid%3Dfd089199-d4a6-43f7-9685-b90a35aea8ad&amp;q=EhAkBQIB4C7guzR74cqdAFF6GJnQy88GIjCQ-mv0jp9tA8qRVMbw86vqq5ezXsd_7-jYqh425E3qmLYz5xyt1UmA8FPxuhrC_8syAnJSWgFD</t>
         </is>
       </c>
-      <c r="S339" t="inlineStr"/>
-      <c r="T339" t="inlineStr"/>
+      <c r="S339" t="n">
+        <v>10.8330322</v>
+      </c>
+      <c r="T339" t="n">
+        <v>76.8730819</v>
+      </c>
     </row>
     <row r="340">
       <c r="A340" t="n">
@@ -21549,8 +22817,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/10%25C2%25B053%2728.0%2522N%2B77%25C2%25B002%2706.0%2522E/%4010.891121,77.034988,855m/data%3D!3m2!1e3!4b1!4m4!3m3!8m2!3d10.891121!4d77.034988!5m1!1e1!17m2!4m1!1e3!18m1!1e1%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MTEyMy4xIPu8ASoASAFQAw%253D%253D%26skid%3D7b471d6e-597e-4e85-92c9-1893e1b6d37d&amp;q=EhAkBQIB4C7guzR74cqdAFF6GJrQy88GIjAsnLR8acdEPYh7Mz_HYCfkpohSfd88_LOyZWPGezwBTpOlg2onvqlVDdFzTjETjboyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S340" t="inlineStr"/>
-      <c r="T340" t="inlineStr"/>
+      <c r="S340" t="n">
+        <v>10.891121</v>
+      </c>
+      <c r="T340" t="n">
+        <v>77.034988</v>
+      </c>
     </row>
     <row r="341">
       <c r="A341" t="n">
@@ -21609,8 +22881,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/11%25C2%25B012%2719.6%2522N%2B77%25C2%25B001%2745.5%2522E/%4011.205436,77.02931,854m/data%3D!3m2!1e3!4b1!4m4!3m3!8m2!3d11.205436!4d77.02931!5m1!1e1%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MTEyMy4xIPu8ASoASAFQAw%253D%253D%26skid%3D6b3583d2-433d-4604-a0e5-ddf51180b6f0&amp;q=EhAkBQIB4C7guzR74cqdAFF6GJvQy88GIjCe2NTzaq16j5a9_z0ptqqHlP_IU6dXls1yBOSUX5Erk8CpN-1FalCUf4rMQTFp71MyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S341" t="inlineStr"/>
-      <c r="T341" t="inlineStr"/>
+      <c r="S341" t="n">
+        <v>11.205436</v>
+      </c>
+      <c r="T341" t="n">
+        <v>77.02931</v>
+      </c>
     </row>
     <row r="342">
       <c r="A342" t="n">
@@ -21669,8 +22945,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/10%25C2%25B056%2747.3%2522N%2B77%25C2%25B009%2733.0%2522E/%4010.9473042,77.1585929,2155m/data%3D!3m1!1e3!4m4!3m3!8m2!3d10.946482!4d77.15917!5m1!1e1%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MTEyMy4xIPu8ASoASAFQAw%253D%253D%26skid%3Ddcdd6dd1-85c7-4d7f-b5d2-9ac79bfa0872&amp;q=EhAkBQIB4C7guzR74cqdAFF6GJzQy88GIjDQh23rkqB__mEKqT8sl0l-u-RW_IqF8Gi9Mp7R38nb6gCV7Hw3mhuyFXoeP9g0i8AyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S342" t="inlineStr"/>
-      <c r="T342" t="inlineStr"/>
+      <c r="S342" t="n">
+        <v>10.9473042</v>
+      </c>
+      <c r="T342" t="n">
+        <v>77.1585929</v>
+      </c>
     </row>
     <row r="343">
       <c r="A343" t="n">
@@ -21729,8 +23009,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/Kamarajar%2BRd,%2BESI,%2BCoimbatore,%2BTamil%2BNadu/%4011.0105413,77.0256894,1523m/data%3D!3m1!1e3!4m6!3m5!1s0x3ba857768b2785ed:0x99b3c620d6e0283c!8m2!3d11.0107917!4d77.0245697!16s%252Fg%252F1tfp0x7n!5m1!1e1!17m2!4m1!1e3!18m1!1e1%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MTEzMC4wIPu8ASoASAFQAw%253D%253D%26skid%3D4b2b34be-031a-4948-8a25-3467d4d32e9e&amp;q=EhAkBQIB4C7guzR74cqdAFF6GJ3Qy88GIjD4SxMYKUfgbxIRdBIMgaXY6riMlUXbJgsQ52KcFHybrFNgLFz1UpbjByR9G_w-YNoyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S343" t="inlineStr"/>
-      <c r="T343" t="inlineStr"/>
+      <c r="S343" t="n">
+        <v>11.0105413</v>
+      </c>
+      <c r="T343" t="n">
+        <v>77.0256894</v>
+      </c>
     </row>
     <row r="344">
       <c r="A344" t="n">
@@ -21789,8 +23073,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/10%25C2%25B059%2731.9%2522N%2B77%25C2%25B002%2747.9%2522E/%4010.9920808,77.0441952,1438m/data%3D!3m1!1e3!4m4!3m3!8m2!3d10.992182!4d77.046638!5m1!1e1%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MTEzMC4wIPu8ASoASAFQAw%253D%253D%26skid%3D255ccc9d-c603-4ecc-b774-4b82e078df7c&amp;q=EhAkBQIB4C7guzR74cqdAFF6GJ7Qy88GIjCeC7xD4tlQQSUeMi40bryiKWEHUY6x2wSMigOmnqNCcVtf53m_2Qs1PSVIAf_i1fUyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S344" t="inlineStr"/>
-      <c r="T344" t="inlineStr"/>
+      <c r="S344" t="n">
+        <v>10.9920808</v>
+      </c>
+      <c r="T344" t="n">
+        <v>77.0441952</v>
+      </c>
     </row>
     <row r="345">
       <c r="A345" t="n">
@@ -21849,8 +23137,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/10%25C2%25B051%2742.0%2522N%2B76%25C2%25B052%2714.7%2522E/%4010.861665,76.870758,855m/data%3D!3m2!1e3!4b1!4m4!3m3!8m2!3d10.861665!4d76.870758!5m1!1e1%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MTExNy4wIPu8ASoASAFQAw%253D%253D%26skid%3D7edd11b4-9664-4b66-b707-8482836a8ab5&amp;q=EhAkBQIB4C7guzR74cqdAFF6GKDQy88GIjCSxAiV0HRVcrClr9KpmE6JLI2j_gI1oaZ-f-Ox8DEH-nOCnHcoJLiIG2r3S5s6GFMyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S345" t="inlineStr"/>
-      <c r="T345" t="inlineStr"/>
+      <c r="S345" t="n">
+        <v>10.861665</v>
+      </c>
+      <c r="T345" t="n">
+        <v>76.870758</v>
+      </c>
     </row>
     <row r="346">
       <c r="A346" t="n">
@@ -21909,8 +23201,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/11%25C2%25B005%2721.4%2522N%2B77%25C2%25B008%2759.9%2522E/%4011.0892834,77.1473886,855m/data%3D!3m2!1e3!4b1!4m4!3m3!8m2!3d11.0892834!4d77.1499635!5m1!1e1%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MTExNy4wIPu8ASoASAFQAw%253D%253D%26skid%3D241fb1e9-1284-4347-a55f-b8968fb86f03&amp;q=EhAkBQIB4C7guzR74cqdAFF6GKHQy88GIjCm0XGf77j2quw5jGh47kjvyLhnJphQBwPunw4YLzoNDNKkgHovaKo9_1aNdzqto8IyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S346" t="inlineStr"/>
-      <c r="T346" t="inlineStr"/>
+      <c r="S346" t="n">
+        <v>11.0892834</v>
+      </c>
+      <c r="T346" t="n">
+        <v>77.1473886</v>
+      </c>
     </row>
     <row r="347">
       <c r="A347" t="n">
@@ -21969,8 +23265,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/10%25C2%25B057%2759.1%2522N%2B76%25C2%25B058%2755.2%2522E/%4010.9664116,76.9794308,855m/data%3D!3m2!1e3!4b1!4m4!3m3!8m2!3d10.9664116!4d76.9820057!5m1!1e1%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MTIwMi4wIPu8ASoASAFQAw%253D%253D%26skid%3Dd8c34ce8-c2d6-4385-8be5-657da02865cc&amp;q=EhAkBQIB4C7guzR74cqdAFF6GKLQy88GIjD9zups6w6iJ-JzoN_eiTKRg6AKXUEcR23bjmSNIO88De97oy1w4Zki3Un7vMcU7zAyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S347" t="inlineStr"/>
-      <c r="T347" t="inlineStr"/>
+      <c r="S347" t="n">
+        <v>10.9664116</v>
+      </c>
+      <c r="T347" t="n">
+        <v>76.9794308</v>
+      </c>
     </row>
     <row r="348">
       <c r="A348" t="n">
@@ -22029,8 +23329,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/10%25C2%25B044%2735.8%2522N%2B76%25C2%25B056%2739.0%2522E/%4010.7432881,76.9415782,856m/data%3D!3m2!1e3!4b1!4m4!3m3!8m2!3d10.7432881!4d76.9441531!5m1!1e1%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MTIwMi4wIPu8ASoASAFQAw%253D%253D%26skid%3De466c953-bcff-4835-8b14-4a09ef2e8bd7&amp;q=EhAkBQIB4C7guzR74cqdAFF6GKTQy88GIjBe2029WeSgPv2VPoTcNChOZAIXVJPvKwAWnDW-8EQPBknknkyJq7d7cd9Kyf8y7TgyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S348" t="inlineStr"/>
-      <c r="T348" t="inlineStr"/>
+      <c r="S348" t="n">
+        <v>10.7432881</v>
+      </c>
+      <c r="T348" t="n">
+        <v>76.9415782</v>
+      </c>
     </row>
     <row r="349">
       <c r="A349" t="n">
@@ -22089,8 +23393,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/11%25C2%25B006%2727.2%2522N%2B76%25C2%25B059%2733.7%2522E/%4011.1079418,76.9934748,2033m/data%3D!3m1!1e3!4m4!3m3!8m2!3d11.10755!4d76.992691!5m1!1e1%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MTIwMi4wIPu8ASoASAFQAw%253D%253D%26skid%3D75cd6e58-8cb4-4e9e-9b2f-4a37ae849cf2&amp;q=EhAkBQIB4C7guzR74cqdAFF6GKbQy88GIjDzeiwSUY7qh3pmZ7NdsKxA_o4TS5Xmo3CYlXqTXoZAQrnbQyHcEkgpU5FOzYfRf-oyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S349" t="inlineStr"/>
-      <c r="T349" t="inlineStr"/>
+      <c r="S349" t="n">
+        <v>11.1079418</v>
+      </c>
+      <c r="T349" t="n">
+        <v>76.9934748</v>
+      </c>
     </row>
     <row r="350">
       <c r="A350" t="n">
@@ -22149,8 +23457,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/10%25C2%25B055%2729.5%2522N%2B76%25C2%25B058%2715.7%2522E/%4010.9197272,76.9609017,6841m/data%3D!3m1!1e3!4m4!3m3!8m2!3d10.9248514!4d76.9710262!5m1!1e1%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MTIwMi4wIPu8ASoASAFQAw%253D%253D%26skid%3D821bd937-28df-448f-a748-1f4eb524aacb&amp;q=EhAkBQIB4C7guzR74cqdAFF6GKfQy88GIjCVaGzRoFqNVsD1Rf83p19CS3IuhnStSZZLrvoQdP8cT3L16e38Vg2PN2Ae3G29Tw8yAnJSWgFD</t>
         </is>
       </c>
-      <c r="S350" t="inlineStr"/>
-      <c r="T350" t="inlineStr"/>
+      <c r="S350" t="n">
+        <v>10.9197272</v>
+      </c>
+      <c r="T350" t="n">
+        <v>76.96090169999999</v>
+      </c>
     </row>
     <row r="351">
       <c r="A351" t="n">
@@ -22209,8 +23521,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/11%25C2%25B002%2724.2%2522N%2B76%25C2%25B059%2719.6%2522E/%4011.0364909,76.9880519,3419m/data%3D!3m1!1e3!4m4!3m3!8m2!3d11.0400463!4d76.9887651!5m1!1e1%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MTIwMi4wIPu8ASoASAFQAw%253D%253D%26skid%3D187e24b8-2cc5-46cb-b8fe-e473f05c1ed9&amp;q=EhAkBQIB4C7guzR74cqdAFF6GKjQy88GIjDJUAdDV5iBZ52ZPcnrTqa6PbK6OwjwVtb1py6TSAQyHk5uX2Mcqx_jWceDi0xGfowyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S351" t="inlineStr"/>
-      <c r="T351" t="inlineStr"/>
+      <c r="S351" t="n">
+        <v>11.0364909</v>
+      </c>
+      <c r="T351" t="n">
+        <v>76.9880519</v>
+      </c>
     </row>
     <row r="352">
       <c r="A352" t="n">
@@ -22274,8 +23590,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/11%25C2%25B006%2706.7%2522N%2B77%25C2%25B007%2743.1%2522E/%4011.0898829,77.1161224,6837m/data%3D!3m1!1e3!4m4!3m3!8m2!3d11.101858!4d77.128649!5m1!1e1%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MTEyMy4xIPu8ASoASAFQAw%253D%253D%26skid%3D11c9906a-bcfb-4d26-8f02-43fc55f24be7&amp;q=EhAkBQIB4C7guzR74cqdAFF6GKrQy88GIjDX1vlLWNG7nlpcYFCne499Hzg6SefAFckLgCni4DNpW3PmJzgUV7E3lwOuIDsA6pYyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S352" t="inlineStr"/>
-      <c r="T352" t="inlineStr"/>
+      <c r="S352" t="n">
+        <v>11.0898829</v>
+      </c>
+      <c r="T352" t="n">
+        <v>77.11612239999999</v>
+      </c>
     </row>
     <row r="353">
       <c r="A353" t="n">
@@ -22338,8 +23658,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/11%25C2%25B004%2753.8%2522N%2B77%25C2%25B008%2707.5%2522E/%4011.0815996,77.132836,855m/data%3D!3m2!1e3!4b1!4m4!3m3!8m2!3d11.0815996!4d77.1354109!5m1!1e1%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MTIwMi4wIPu8ASoASAFQAw%253D%253D%26skid%3D2465b663-8142-4d0d-8d1c-2af0137c4f02&amp;q=EhAkBQIB4C7guzR74cqdAFF6GKzQy88GIjBrJi11p8gJ5Jk16YBKB0FfGadYOGMIoHwl9ul5fI_wF8lb2CeICmFV5jSd4gilPo0yAnJSWgFD</t>
         </is>
       </c>
-      <c r="S353" t="inlineStr"/>
-      <c r="T353" t="inlineStr"/>
+      <c r="S353" t="n">
+        <v>11.0815996</v>
+      </c>
+      <c r="T353" t="n">
+        <v>77.132836</v>
+      </c>
     </row>
     <row r="354">
       <c r="A354" t="n">
@@ -22402,8 +23726,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/11%25C2%25B003%2750.3%2522N%2B77%25C2%25B007%2703.1%2522E/%4011.0670515,77.1150126,5750m/data%3D!3m1!1e3!4m4!3m3!8m2!3d11.063961!4d77.117537!5m1!1e1%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MTIwMi4wIPu8ASoASAFQAw%253D%253D%26skid%3Df92630c3-239f-4787-b083-81e59dbf2c22&amp;q=EhAkBQIB4C7guzR74cqdAFF6GK_Qy88GIjAUVryNOEutUVWVa5Av2O-mvjvzOaeu4AfaueX5fhgDwLtqPaJXM5wzwnOMIRv3bugyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S354" t="inlineStr"/>
-      <c r="T354" t="inlineStr"/>
+      <c r="S354" t="n">
+        <v>11.0670515</v>
+      </c>
+      <c r="T354" t="n">
+        <v>77.1150126</v>
+      </c>
     </row>
     <row r="355">
       <c r="A355" t="n">
@@ -22462,8 +23790,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/11%25C2%25B007%2731.3%2522N%2B77%25C2%25B009%2713.5%2522E/%4011.1228955,77.1559999,855m/data%3D!3m1!1e3!4m4!3m3!8m2!3d11.1253596!4d77.1537356!5m1!1e1%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MTIwMi4wIPu8ASoASAFQAw%253D%253D%26skid%3D5b4b8c12-3c47-4700-9315-6fa2092a6e9d&amp;q=EhAkBQIB4C7guzR74cqdAFF6GLDQy88GIjCQqDxObqHGsnvK5dFjHHURZC6zNuNGpU5MxuEOCU5Oex31q89SywvzsZm6urdXgbYyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S355" t="inlineStr"/>
-      <c r="T355" t="inlineStr"/>
+      <c r="S355" t="n">
+        <v>11.1228955</v>
+      </c>
+      <c r="T355" t="n">
+        <v>77.1559999</v>
+      </c>
     </row>
     <row r="356">
       <c r="A356" t="n">
@@ -22522,8 +23854,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/10%25C2%25B057%2715.1%2522N%2B77%25C2%25B007%2750.3%2522E/%4010.9528731,77.1505819,9673m/data%3D!3m1!1e3!4m4!3m3!8m2!3d10.954194!4d77.130639!5m1!1e1%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MTIwMi4wIPu8ASoASAFQAw%253D%253D%26skid%3D4617a08c-78ef-4daa-a099-956aeeebbc00&amp;q=EhAkBQIB4C7guzR74cqdAFF6GLLQy88GIjCY4JuDtbV5FX0sR9-8icowh85MDhhCLL5fMmuuRgd3Dpl3AhYGy9x9q_MPdd-fDRoyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S356" t="inlineStr"/>
-      <c r="T356" t="inlineStr"/>
+      <c r="S356" t="n">
+        <v>10.9528731</v>
+      </c>
+      <c r="T356" t="n">
+        <v>77.15058190000001</v>
+      </c>
     </row>
     <row r="357">
       <c r="A357" t="n">
@@ -22586,8 +23922,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/11%25C2%25B001%2704.2%2522N%2B77%25C2%25B004%2728.8%2522E/%4011.0178306,77.0720881,855m/data%3D!3m2!1e3!4b1!4m4!3m3!8m2!3d11.0178306!4d77.074663%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MTIwOS4wIPu8ASoASAFQAw%253D%253D%26skid%3Dbc075b57-503b-4de2-8b9e-db0134a06379&amp;q=EhAkBQIB4C7guzR74cqdAFF6GLXQy88GIjAns8tolVi7HyXmldxx50sm9nC8wTTTd-AIGdQBNdZIuhJV39Ax5jq19drxebM0k5oyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S357" t="inlineStr"/>
-      <c r="T357" t="inlineStr"/>
+      <c r="S357" t="n">
+        <v>11.0178306</v>
+      </c>
+      <c r="T357" t="n">
+        <v>77.0720881</v>
+      </c>
     </row>
     <row r="358">
       <c r="A358" t="n">
@@ -22650,8 +23990,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/11%25C2%25B000%2721.5%2522N%2B77%25C2%25B004%2712.7%2522E/%4011.002509,77.0665273,2033m/data%3D!3m1!1e3!4m4!3m3!8m2!3d11.0059571!4d77.070182%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MTIwOS4wIPu8ASoASAFQAw%253D%253D%26skid%3Dbcb18772-488d-483e-ac5b-a4ab6a68efa1&amp;q=EhAkBQIB4C7guzR74cqdAFF6GLbQy88GIjA2P5mP92RvpjyZyuSdeE4Ytu3uajnuKxapyXGPvGqQPyzHLQvZZGC360MGOyBV2QsyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S358" t="inlineStr"/>
-      <c r="T358" t="inlineStr"/>
+      <c r="S358" t="n">
+        <v>11.002509</v>
+      </c>
+      <c r="T358" t="n">
+        <v>77.0665273</v>
+      </c>
     </row>
     <row r="359">
       <c r="A359" t="n">
@@ -22771,8 +24115,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/11%25C2%25B008%2739.6%2522N%2B77%25C2%25B003%2716.6%2522E/%4011.1433753,77.0468089,2032m/data%3D!3m1!1e3!4m4!3m3!8m2!3d11.1443404!4d77.0546122%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MTIwOS4wIPu8ASoASAFQAw%253D%253D%26skid%3Df6ecbe25-89fe-4a84-9428-febba256c31c&amp;q=EhAkBQIB4C7guzR74cqdAFF6GLrQy88GIjD6yoJ_v58mTQa2H2YU08_zvKh2fqliz2OXnvJKuXPT_KV8o-lTB3hUH4kQMvivZMAyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S360" t="inlineStr"/>
-      <c r="T360" t="inlineStr"/>
+      <c r="S360" t="n">
+        <v>11.1433753</v>
+      </c>
+      <c r="T360" t="n">
+        <v>77.0468089</v>
+      </c>
     </row>
     <row r="361">
       <c r="A361" t="n">
@@ -22831,8 +24179,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/11%25C2%25B004%2706.7%2522N%2B77%25C2%25B002%2706.2%2522E/%4011.0680233,77.0268412,3419m/data%3D!3m1!1e3!4m4!3m3!8m2!3d11.0685272!4d77.0350571%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MTIwOS4wIPu8ASoASAFQAw%253D%253D%26skid%3D80e52b81-39d3-489d-b0bb-eb0e7d31b384&amp;q=EhAkBQIB4C7guzR74cqdAFF6GLvQy88GIjBxNpTQVzTp3Ui0VRtBj9Fda3qz_Qk_YxObNAcN3AyAmVP8JUL6f-JJUul221hZ0cYyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S361" t="inlineStr"/>
-      <c r="T361" t="inlineStr"/>
+      <c r="S361" t="n">
+        <v>11.0680233</v>
+      </c>
+      <c r="T361" t="n">
+        <v>77.02684120000001</v>
+      </c>
     </row>
     <row r="362">
       <c r="A362" t="n">
@@ -22895,8 +24247,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/11%25C2%25B003%2745.8%2522N%2B77%25C2%25B004%2721.3%2522E/%4011.0627101,77.0700158,855m/data%3D!3m2!1e3!4b1!4m4!3m3!8m2!3d11.0627101!4d77.0725907%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MTIwOS4wIPu8ASoASAFQAw%253D%253D%26skid%3D81c69669-680c-459e-b073-a9147dc98b57&amp;q=EhAkBQIB4C7guzR74cqdAFF6GLzQy88GIjCD8jn_oF-jEiU5jSkGON7lUXa2kfuSplRGSRvVbPBmbzZ0P7Lcwea_xOY785cxt-0yAnJSWgFD</t>
         </is>
       </c>
-      <c r="S362" t="inlineStr"/>
-      <c r="T362" t="inlineStr"/>
+      <c r="S362" t="n">
+        <v>11.0627101</v>
+      </c>
+      <c r="T362" t="n">
+        <v>77.07001579999999</v>
+      </c>
     </row>
     <row r="363">
       <c r="A363" t="n">
@@ -22955,8 +24311,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/11%25C2%25B000%2711.3%2522N%2B77%25C2%25B001%2708.2%2522E/%4011.0009902,77.016779,2033m/data%3D!3m1!1e3!4m4!3m3!8m2!3d11.0031433!4d77.0189333%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MTIwOS4wIPu8ASoASAFQAw%253D%253D%26skid%3Deac21d0f-8afb-4b36-b233-c40f5a159a8c&amp;q=EhAkBQIB4C7guzR74cqdAFF6GL3Qy88GIjDdQ20mLE0Ezy6SRAaqTqhfO6v25_GHzxlOA_pn92Nb1OOTGboRQ7n1ctwA_G0PZCIyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S363" t="inlineStr"/>
-      <c r="T363" t="inlineStr"/>
+      <c r="S363" t="n">
+        <v>11.0009902</v>
+      </c>
+      <c r="T363" t="n">
+        <v>77.016779</v>
+      </c>
     </row>
     <row r="364">
       <c r="A364" t="n">
@@ -23025,8 +24385,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/10%25C2%25B055%2750.5%2522N%2B77%25C2%25B014%2713.5%2522E/%4010.9306904,77.234501,855m/data%3D!3m2!1e3!4b1!4m4!3m3!8m2!3d10.9306904!4d77.2370759%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MTIwOS4wIPu8ASoASAFQAw%253D%253D%26skid%3D5ee74328-1334-4b15-8826-4384039f4fa3&amp;q=EhAkBQIB4C7guzR74cqdAFF6GODQy88GIjC55qOAspvKnb4v58AsihUKP3IvExvppycXRJvrQnQLXpwteNU-RE7WWLvhJ9hmrtYyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S364" t="inlineStr"/>
-      <c r="T364" t="inlineStr"/>
+      <c r="S364" t="n">
+        <v>10.9306904</v>
+      </c>
+      <c r="T364" t="n">
+        <v>77.23450099999999</v>
+      </c>
     </row>
     <row r="365">
       <c r="A365" t="n">
@@ -23095,8 +24459,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/10%25C2%25B040%2743.2%2522N%2B77%25C2%25B013%2709.3%2522E/%4010.6786736,77.2166616,856m/data%3D!3m2!1e3!4b1!4m4!3m3!8m2!3d10.6786736!4d77.2192365%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MTIwOS4wIPu8ASoASAFQAw%253D%253D%26skid%3D60410a9a-e71e-41ef-a289-05726c48a165&amp;q=EhAkBQIB4C7guzR74cqdAFF6GOHQy88GIjCrLa__UqYOdgMUgzThd_3fU6h5goWsLs_Jirh3t-SuytIWtnOBjTaYjehAAb1NnjoyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S365" t="inlineStr"/>
-      <c r="T365" t="inlineStr"/>
+      <c r="S365" t="n">
+        <v>10.6786736</v>
+      </c>
+      <c r="T365" t="n">
+        <v>77.21666159999999</v>
+      </c>
     </row>
     <row r="366">
       <c r="A366" t="n">
@@ -23165,8 +24533,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/10%25C2%25B037%2731.8%2522N%2B77%25C2%25B015%2746.2%2522E/%4010.6255114,77.2602679,815m/data%3D!3m2!1e3!4b1!4m4!3m3!8m2!3d10.6255114!4d77.2628428%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MTIwOS4wIPu8ASoASAFQAw%253D%253D%26skid%3Df0e3f5b4-8757-4eeb-bde5-8990e85bb6cb&amp;q=EhAkBQIB4C7guzR74cqdAFF6GOLQy88GIjAvTjpQLnrL_LqsqNzmhAq9_vxHjGIJJRG-g0D82d8-HvJZkFlh7zthv4z5cTWZbesyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S366" t="inlineStr"/>
-      <c r="T366" t="inlineStr"/>
+      <c r="S366" t="n">
+        <v>10.6255114</v>
+      </c>
+      <c r="T366" t="n">
+        <v>77.2602679</v>
+      </c>
     </row>
     <row r="367">
       <c r="A367" t="n">
@@ -23235,8 +24607,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/10%25C2%25B036%2747.3%2522N%2B77%25C2%25B016%2740.6%2522E/%4010.6108386,77.268227,4610m/data%3D!3m1!1e3!4m4!3m3!8m2!3d10.6131281!4d77.2779296%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MTIwOS4wIPu8ASoASAFQAw%253D%253D%26skid%3Dc7ab3449-997e-4567-b918-9fdb85008379&amp;q=EhAkBQIB4C7guzR74cqdAFF6GOXQy88GIjC99IgQDTpJsd_D6hUmhiaVnkaHbIax3C4iVi8iHWsq3J9kVJxbzE8rBjfZqETZMPkyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S367" t="inlineStr"/>
-      <c r="T367" t="inlineStr"/>
+      <c r="S367" t="n">
+        <v>10.6108386</v>
+      </c>
+      <c r="T367" t="n">
+        <v>77.268227</v>
+      </c>
     </row>
     <row r="368">
       <c r="A368" t="n">
@@ -23295,8 +24671,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/11%25C2%25B012%2722.5%2522N%2B77%25C2%25B007%2746.4%2522E/%4011.2062553,77.1269807,813m/data%3D!3m2!1e3!4b1!4m4!3m3!8m2!3d11.20625!4d77.1295556%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MTIwOS4wIPu8ASoASAFQAw%253D%253D%26skid%3D69876ee7-2328-41a6-8265-108407ca7c77&amp;q=EhAkBQIB4C7guzR74cqdAFF6GObQy88GIjAJZnlfKb4CRdX8N5M1BfQpZyEeracKeU3GWO--Sc7alVlqIUz18hTJw7yLxQ8VAx8yAnJSWgFD</t>
         </is>
       </c>
-      <c r="S368" t="inlineStr"/>
-      <c r="T368" t="inlineStr"/>
+      <c r="S368" t="n">
+        <v>11.2062553</v>
+      </c>
+      <c r="T368" t="n">
+        <v>77.1269807</v>
+      </c>
     </row>
     <row r="369">
       <c r="A369" t="n">
@@ -23355,8 +24735,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/10%25C2%25B059%2738.3%2522N%2B76%25C2%25B057%2705.0%2522E/%4010.9939747,76.9488165,814m/data%3D!3m2!1e3!4b1!4m4!3m3!8m2!3d10.9939747!4d76.9513914%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MTIwOS4wIPu8ASoASAFQAw%253D%253D%26skid%3D66d8c55f-eef8-41fe-8a5e-3dee18ab06e5&amp;q=EhAkBQIB4C7guzR74cqdAFF6GOfQy88GIjB9e1GJ7pwU8om5nZLy_6dKascu9Byx4H770fezJoftNLXtUZyZr8P8WQTRuKkkC9gyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S369" t="inlineStr"/>
-      <c r="T369" t="inlineStr"/>
+      <c r="S369" t="n">
+        <v>10.9939747</v>
+      </c>
+      <c r="T369" t="n">
+        <v>76.94881650000001</v>
+      </c>
     </row>
     <row r="370">
       <c r="A370" t="n">
@@ -23415,8 +24799,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/10%25C2%25B051%2727.5%2522N%2B76%25C2%25B059%2718.2%2522E/%4010.8552605,76.9908003,10956m/data%3D!3m1!1e3!4m4!3m3!8m2!3d10.8576346!4d76.9883897%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MTIwOS4wIPu8ASoASAFQAw%253D%253D%26skid%3D2fdc8cfa-8993-4856-93b2-fb84cb9ed75e&amp;q=EhAkBQIB4C7guzR74cqdAFF6GOnQy88GIjBzrmi6z6EBp2M4b_1IUgqHoVV7g7XxwwQoL1isOVqJeh-PE1E90lGWA3shTwSSYVoyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S370" t="inlineStr"/>
-      <c r="T370" t="inlineStr"/>
+      <c r="S370" t="n">
+        <v>10.8552605</v>
+      </c>
+      <c r="T370" t="n">
+        <v>76.9908003</v>
+      </c>
     </row>
     <row r="371">
       <c r="A371" t="n">
@@ -23475,8 +24863,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/11%25C2%25B001%2754.7%2522N%2B77%25C2%25B000%2741.6%2522E/%4011.031856,77.011543,814m/data%3D!3m2!1e3!4b1!4m4!3m3!8m2!3d11.031856!4d77.011543!17m2!4m1!1e3!18m1!1e1%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MTIwOS4wIPu8ASoASAFQAw%253D%253D%26skid%3D13e7dd19-23b8-48c2-b013-b26ca13e7737&amp;q=EhAkBQIB4C7guzR74cqdAFF6GOvQy88GIjBoOp7XoyG-gWxwFjSTLhGH6Z3wDPZgyAO63Bmhz991ke0eJ3LEzo1JiukOuKcNrDQyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S371" t="inlineStr"/>
-      <c r="T371" t="inlineStr"/>
+      <c r="S371" t="n">
+        <v>11.031856</v>
+      </c>
+      <c r="T371" t="n">
+        <v>77.011543</v>
+      </c>
     </row>
     <row r="372">
       <c r="A372" t="n">
@@ -23535,8 +24927,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/MDR872,%2BTamil%2BNadu/%4011.0858841,76.9792136,814m/data%3D!3m2!1e3!4b1!4m6!3m5!1s0x3ba8586ce4177beb:0x754c1eba09a8ca19!8m2!3d11.0858788!4d76.9817885!16s%252Fg%252F1q5bm6v74%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MTIwOS4wIPu8ASoASAFQAw%253D%253D%26skid%3D942c6f66-3f31-4c5f-8ce6-2028b382b97c&amp;q=EhAkBQIB4C7guzR74cqdAFF6GO3Qy88GIjD_f1Kdt_JoNF9eEw4ipBIJ9sqiO0qLmf9rCbe2jzj5HvKrDQ2wsYN1OJv7Zpsy-JwyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S372" t="inlineStr"/>
-      <c r="T372" t="inlineStr"/>
+      <c r="S372" t="n">
+        <v>11.0858841</v>
+      </c>
+      <c r="T372" t="n">
+        <v>76.97921359999999</v>
+      </c>
     </row>
     <row r="373">
       <c r="A373" t="n">
@@ -23595,8 +24991,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/Selvage%2BNagar,%2BV.N.R.Nagar,%2BCoimbatore,%2BTamil%2BNadu%2B641041/%4011.024145,76.9097267,968m/data%3D!3m1!1e3!4m6!3m5!1s0x3ba85f319a90e4ab:0x170430bcc7388239!8m2!3d11.0246928!4d76.9116106!16s%252Fg%252F11g62s_tks%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MTIwOS4wIPu8ASoASAFQAw%253D%253D%26skid%3D089c2dd0-46f0-449c-a130-dd1c3720639f&amp;q=EhAkBQIB4C7guzR74cqdAFF6GO_Qy88GIjB-bmEnyA_h3P8MNn-HiTbfQafKwShsM0nGpr0wANTQhc4uWGNaAxH77m-l-XJljhkyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S373" t="inlineStr"/>
-      <c r="T373" t="inlineStr"/>
+      <c r="S373" t="n">
+        <v>11.024145</v>
+      </c>
+      <c r="T373" t="n">
+        <v>76.90972669999999</v>
+      </c>
     </row>
     <row r="374">
       <c r="A374" t="n">
@@ -23655,8 +25055,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/10%25C2%25B059%2713.8%2522N%2B77%25C2%25B000%2704.8%2522E/%4010.9918578,77.0033462,3986m/data%3D!3m1!1e3!4m4!3m3!8m2!3d10.987163!4d77.001344%3Fentry%3Dtts%26g_ep%3DEgoyMDI1MTIwOS4wIPu8ASoASAFQAw%253D%253D%26skid%3D716a1a7a-b6c7-4874-9250-845482816967&amp;q=EhAkBQIB4C7guzR74cqdAFF6GPDQy88GIjDLbmYHsjS_ibeUtF3jTmkHrZGGVCzmLjZSB1uEfZiNS-qAObnUWIlH-EjTB6k61gYyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S374" t="inlineStr"/>
-      <c r="T374" t="inlineStr"/>
+      <c r="S374" t="n">
+        <v>10.9918578</v>
+      </c>
+      <c r="T374" t="n">
+        <v>77.0033462</v>
+      </c>
     </row>
     <row r="375">
       <c r="A375" t="n">
@@ -23715,8 +25119,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/10.988170,76.987477/data%3D!4m6!3m5!1s0!7e2!8m2!3d10.988169899999999!4d76.98747689999999!17m2!4m1!1e3!18m1!1e1%3Futm_source%3Dmstt_1%26entry%3Dgps%26coh%3D192189%26g_ep%3DCAESBzI1LjQ5LjYYACDl7Q0qmgEsOTQyNTk1NTEsOTQyNjc3MjcsOTQyNzU0MDcsOTQyOTIxOTUsOTQyOTk1MzIsOTQyODQ0NjAsOTQyODA1NzYsOTQyNjc3ODcsOTQyMDczOTQsOTQyMDc1MDYsOTQyMDg1MDYsOTQyMTg2NTMsOTQyMjk4MzksOTQyNzUxNjgsOTQyNzk2MTksOTQyOTU1MDgsMTAwNzkyNTY4QgJJTg%253D%253D%26skid%3Dff3d0dfa-98b7-4e84-b48e-ffd6f311bac9%26g_st%3Daw&amp;q=EhAkBQIB4C7guzR74cqdAFF6GPHQy88GIjD1igx13fpWtrIXaHcZdbZ3472j5jJ7CGZhRsEqRJnwMjWmdVVNg83Q2_nS888wEwoyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S375" t="inlineStr"/>
-      <c r="T375" t="inlineStr"/>
+      <c r="S375" t="n">
+        <v>10.9881699</v>
+      </c>
+      <c r="T375" t="n">
+        <v>76.98747689999999</v>
+      </c>
     </row>
     <row r="376">
       <c r="A376" t="n">
@@ -23775,8 +25183,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/10.991425,77.004486/data%3D!4m6!3m5!1s0!7e2!8m2!3d10.9914249!4d77.0044858!17m2!4m1!1e3!18m1!1e1%3Futm_source%3Dmstt_1%26entry%3Dgps%26coh%3D192189%26g_ep%3DCAESBzI1LjQ5LjYYACDl7Q0qmgEsOTQyNTk1NTEsOTQyNjc3MjcsOTQyNzU0MDcsOTQyOTIxOTUsOTQyOTk1MzIsOTQyODQ0NjAsOTQyODA1NzYsOTQyNjc3ODcsOTQyMDczOTQsOTQyMDc1MDYsOTQyMDg1MDYsOTQyMTg2NTMsOTQyMjk4MzksOTQyNzUxNjgsOTQyNzk2MTksOTQyOTU1MDgsMTAwNzkyNTY4QgJJTg%253D%253D%26skid%3D33b7d93a-f637-4b29-b68a-2c8c5d9c2498&amp;q=EhAkBQIB4C7guzR74cqdAFF6GPTQy88GIjChNgF-KhaETHtdj7PxxOZMwPKK3elupdN7Uk750SjGHho_ge6tjdM9ft5y5TjI2ykyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S376" t="inlineStr"/>
-      <c r="T376" t="inlineStr"/>
+      <c r="S376" t="n">
+        <v>10.9914249</v>
+      </c>
+      <c r="T376" t="n">
+        <v>77.0044858</v>
+      </c>
     </row>
     <row r="377">
       <c r="A377" t="n">
@@ -23835,8 +25247,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/11.007782,77.036756/data%3D!4m6!3m5!1s0!7e2!8m2!3d11.007781999999999!4d77.0367558!17m2!4m1!1e3!18m1!1e1%3Futm_source%3Dmstt_1%26entry%3Dgps%26coh%3D192189%26g_ep%3DCAESBzI1LjQ5LjYYACD67A0qdSw5NDI2NzcyNyw5NDI3NTQwNyw5NDI5MjE5NSw5NDI5OTUzMiw5NDI4NDQ2Myw5NDI4MDU3Niw5NDIwNzM5NCw5NDIwNzUwNiw5NDIwODUwNiw5NDIxODY1Myw5NDIyOTgzOSw5NDI3NTE2OCw5NDI3OTYxOUICSU4%253D%26skid%3D371f45dd-d5fe-4f85-b9ef-bca9d76e41a5%26g_st%3Daw&amp;q=EhAkBQIB4C7guzR74cqdAFF6GPfQy88GIjDCe3zEFp4j6HG-nN0WonvZQrFkOn2bG5IFQi3BuHWEsJQ81CdopbicNcCaZq5bOBUyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S377" t="inlineStr"/>
-      <c r="T377" t="inlineStr"/>
+      <c r="S377" t="n">
+        <v>11.007782</v>
+      </c>
+      <c r="T377" t="n">
+        <v>77.03675579999999</v>
+      </c>
     </row>
     <row r="378">
       <c r="A378" t="n">
@@ -23895,8 +25311,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/10%25C2%25B058%2725.2%2522N%2B76%25C2%25B047%2727.9%2522E/%4010.973664,76.7885141,814m/data%3D!3m2!1e3!4b1!4m4!3m3!8m2!3d10.973664!4d76.791089!5m1!1e1%3Fentry%3Dtts%26g_ep%3DEgoyMDI2MDEwNC4wIPu8ASoASAFQAw%253D%253D%26skid%3D7c3a3beb-cced-4cce-8067-fb7ca3fe1f78&amp;q=EhAkBQIB4C7guzR74cqdAFF6GPnQy88GIjClRYC52G4RK3cnowc42R8x1TUwMTFDZEAhFoGzTWJaIPqKLKqRdIzub1SlpME5WaAyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S378" t="inlineStr"/>
-      <c r="T378" t="inlineStr"/>
+      <c r="S378" t="n">
+        <v>10.973664</v>
+      </c>
+      <c r="T378" t="n">
+        <v>76.7885141</v>
+      </c>
     </row>
     <row r="379">
       <c r="A379" t="n">
@@ -23955,8 +25375,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/10%25C2%25B059%2706.3%2522N%2B77%25C2%25B003%2704.0%2522E/%4010.9850896,77.0485453,883m/data%3D!3m2!1e3!4b1!4m4!3m3!8m2!3d10.9850896!4d77.0511202!5m1!1e1%3Fentry%3Dtts%26g_ep%3DEgoyMDI2MDExMy4wIPu8ASoASAFQAw%253D%253D%26skid%3D81450f4f-b423-4ebc-a47e-84b8991a494c&amp;q=EhAkBQIB4C7guzR74cqdAFF6GPrQy88GIjCYEekvHdSpfkCHedwBug62YKQAhfIMJFTx085WYNSr39VrqoJWmqJRAFlJmfqbvkYyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S379" t="inlineStr"/>
-      <c r="T379" t="inlineStr"/>
+      <c r="S379" t="n">
+        <v>10.9850896</v>
+      </c>
+      <c r="T379" t="n">
+        <v>77.0485453</v>
+      </c>
     </row>
     <row r="380">
       <c r="A380" t="n">
@@ -24015,8 +25439,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/11%25C2%25B007%2743.0%2522N%2B77%25C2%25B004%2742.7%2522E/%4011.1286009,77.0759554,883m/data%3D!3m2!1e3!4b1!4m4!3m3!8m2!3d11.1286009!4d77.0785303!5m1!1e1%3Fentry%3Dtts%26g_ep%3DEgoyMDI2MDExMy4wIPu8ASoASAFQAw%253D%253D%26skid%3D199a24ab-8938-4f60-ad98-dc64542711f7&amp;q=EhAkBQIB4C7guzR74cqdAFF6GP3Qy88GIjDBaNc2tGocGI4Kv1YesX_VoeE9bSlHnZWcrRIEx3GkANYgih79LjWTGOmOzeDIPgsyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S380" t="inlineStr"/>
-      <c r="T380" t="inlineStr"/>
+      <c r="S380" t="n">
+        <v>11.1286009</v>
+      </c>
+      <c r="T380" t="n">
+        <v>77.0759554</v>
+      </c>
     </row>
     <row r="381">
       <c r="A381" t="n">
@@ -24075,8 +25503,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/11%25C2%25B006%2753.8%2522N%2B77%25C2%25B004%2722.1%2522E/%4011.1149433,77.0702201,883m/data%3D!3m2!1e3!4b1!4m4!3m3!8m2!3d11.1149433!4d77.072795!5m1!1e1%3Fentry%3Dtts%26g_ep%3DEgoyMDI2MDExMy4wIPu8ASoASAFQAw%253D%253D%26skid%3Dce1922e8-55d4-4e7e-b6c1-8d990469f443&amp;q=EhAkBQIB4C7guzR74cqdAFF6GP7Qy88GIjBUQtaAJeQCfmc0d7biDLFbviT31fD0_TFLqe_JvSDPoS3qMq4iHbHkpKJegnEe3BEyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S381" t="inlineStr"/>
-      <c r="T381" t="inlineStr"/>
+      <c r="S381" t="n">
+        <v>11.1149433</v>
+      </c>
+      <c r="T381" t="n">
+        <v>77.0702201</v>
+      </c>
     </row>
     <row r="382">
       <c r="A382" t="n">
@@ -24212,8 +25644,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/Sulur,%2BTamil%2BNadu%2B641016/%4010.976543,77.0556222,1369m/data%3D!3m1!1e3!4m6!3m5!1s0x3ba8572aa2be5b1b:0x657c8d07b8655cc3!8m2!3d10.9750964!4d77.0558149!16s%252Fg%252F11qk4f5909!5m1!1e1!17m2!4m1!1e3!18m1!1e1%3Fentry%3Dtts%26g_ep%3DEgoyMDI2MDIwMS4wIPu8ASoASAFQAw%253D%253D%26skid%3D056c7259-0afb-4770-91f1-cc62ef43608d&amp;q=EhAkBQIB4C7guzR74cqdAFF6GP_Qy88GIjDWk2xIc3JjB0vOHKVQxZe8whC3swk8AjOVdtcJIqz1GL2Wyeqfo2S9bTBNlEDLA5AyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S384" t="inlineStr"/>
-      <c r="T384" t="inlineStr"/>
+      <c r="S384" t="n">
+        <v>10.976543</v>
+      </c>
+      <c r="T384" t="n">
+        <v>77.0556222</v>
+      </c>
     </row>
     <row r="385">
       <c r="A385" t="n">
@@ -24260,8 +25696,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/10%25C2%25B054%2726.9%2522N%2B77%25C2%25B002%2701.3%2522E/%4010.9074717,77.031117,814m/data%3D!3m2!1e3!4b1!4m4!3m3!8m2!3d10.9074717!4d77.0336919!5m1!1e1%3Fentry%3Dtts%26g_ep%3DEgoyMDI2MDIwMS4wIPu8ASoASAFQAw%253D%253D%26skid%3Dc519d873-52bf-40c7-9f86-57980ad838d6&amp;q=EhAkBQIB4C7guzR74cqdAFF6GIHRy88GIjB0AJSchTwYsqrPzIWVKpD_BRxnCkO_JITPtMiILvQEVraoMPaUZ24NrMwrCq7APcIyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S385" t="inlineStr"/>
-      <c r="T385" t="inlineStr"/>
+      <c r="S385" t="n">
+        <v>10.9074717</v>
+      </c>
+      <c r="T385" t="n">
+        <v>77.03111699999999</v>
+      </c>
     </row>
     <row r="386">
       <c r="A386" t="n">
@@ -24316,8 +25756,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/11%25C2%25B008%2729.1%2522N%2B77%25C2%25B010%2744.6%2522E/%4011.141419,77.179066,814m/data%3D!3m2!1e3!4b1!4m4!3m3!8m2!3d11.141419!4d77.179066!5m1!1e1!17m2!4m1!1e3!18m1!1e1%3Fentry%3Dtts%26g_ep%3DEgoyMDI2MDEyOC4wIPu8ASoASAFQAw%253D%253D%26skid%3D027332ce-028f-48fc-8ec6-6d61703b614c&amp;q=EhAkBQIB4C7guzR74cqdAFF6GILRy88GIjDDrKNR8yoV-b2EWNcsyV_nODltznVTrz1axV42xHKszYGDgdOZ9qu3ZnDYoIO3nf0yAnJSWgFD</t>
         </is>
       </c>
-      <c r="S386" t="inlineStr"/>
-      <c r="T386" t="inlineStr"/>
+      <c r="S386" t="n">
+        <v>11.141419</v>
+      </c>
+      <c r="T386" t="n">
+        <v>77.17906600000001</v>
+      </c>
     </row>
     <row r="387">
       <c r="A387" t="n">
@@ -24428,8 +25872,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/11%25C2%25B008%2702.8%2522N%2B77%25C2%25B007%2736.9%2522E/%4011.1538778,77.0788019,22531m/data%3D!3m1!1e3!4m4!3m3!8m2!3d11.1340992!4d77.1269122!5m1!1e1!18m1!1e1%3Fentry%3Dtts%26g_ep%3DEgoyMDI2MDEyOC4wIPu8ASoASAFQAw%253D%253D%26skid%3Daa41593c-3619-47ec-92a5-4d476ddb34dd&amp;q=EhAkBQIB4C7guzR74cqdAFF6GITRy88GIjBwwHz4K_Tgf90hMqWL9Qq0tf4gb08QazHKTquf_0EOdkiSdGCeasUDB0q8jHkISo8yAnJSWgFD</t>
         </is>
       </c>
-      <c r="S388" t="inlineStr"/>
-      <c r="T388" t="inlineStr"/>
+      <c r="S388" t="n">
+        <v>11.1538778</v>
+      </c>
+      <c r="T388" t="n">
+        <v>77.0788019</v>
+      </c>
     </row>
     <row r="389">
       <c r="A389" t="n">
@@ -24581,8 +26029,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/10%25C2%25B051%2721.6%2522N%2B76%25C2%25B053%2735.5%2522E/%4010.8448765,76.8728554,6515m/data%3D!3m1!1e3!4m4!3m3!8m2!3d10.855985!4d76.8931883!5m1!1e1%3Fentry%3Dtts%26g_ep%3DEgoyMDI2MDIwNC4wIPu8ASoASAFQAw%253D%253D%26skid%3Dd1ac2777-6840-4f83-9a6c-7de40529055e&amp;q=EhAkBQIB4C7guzR74cqdAFF6GIfRy88GIjAbkY-uRufo4OLjUgPBpgQA2Tv_ujcroVkICIHMqBie3tb3g78fILnhFO4XqKh2TyEyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S391" t="inlineStr"/>
-      <c r="T391" t="inlineStr"/>
+      <c r="S391" t="n">
+        <v>10.8448765</v>
+      </c>
+      <c r="T391" t="n">
+        <v>76.87285540000001</v>
+      </c>
     </row>
     <row r="392">
       <c r="A392" t="n">
@@ -24645,8 +26097,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/10%25C2%25B051%2721.6%2522N%2B76%25C2%25B053%2735.5%2522E/%4010.8528357,76.886657,1629m/data%3D!3m1!1e3!4m4!3m3!8m2!3d10.855985!4d76.8931883!5m1!1e1%3Fentry%3Dtts%26g_ep%3DEgoyMDI2MDIwNC4wIPu8ASoASAFQAw%253D%253D%26skid%3D4b562471-db69-49e7-807e-771d1fc40eae&amp;q=EhAkBQIB4C7guzR74cqdAFF6GIrRy88GIjAX5Kh7qCY5qrca6n66MUFXcf2DvdNcuEAySHeOaoY6BYhiMe0mUS_UDV97vAtW87UyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S392" t="inlineStr"/>
-      <c r="T392" t="inlineStr"/>
+      <c r="S392" t="n">
+        <v>10.8528357</v>
+      </c>
+      <c r="T392" t="n">
+        <v>76.886657</v>
+      </c>
     </row>
     <row r="393">
       <c r="A393" t="n">
@@ -24813,8 +26269,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/10.949062,77.113697/data%3D!4m6!3m5!1s0!7e2!8m2!3d10.949061799999999!4d77.1136973%3Futm_source%3Dmstt_1%26entry%3Dgps%26coh%3D192189%26g_ep%3DCAESBzI1LjQ5LjYYACD67A0qdSw5NDI2NzcyNyw5NDI3NTQwNyw5NDI5MjE5NSw5NDI5OTUzMiw5NDI4NDUxMSw5NDI4MDU3Niw5NDIwNzM5NCw5NDIwNzUwNiw5NDIwODUwNiw5NDIxODY1Myw5NDIyOTgzOSw5NDI3NTE2OCw5NDI3OTYxOUICSU4%253D%26skid%3D720c53ba-23d9-4d92-bb34-208edc995f18%26g_st%3Dawb&amp;q=EhAkBQIB4C7guzR74cqdAFF6GI3Ry88GIjCJspmMopXRM_kuDmPyvkvCd9nLyFcF3oPvu8vBGESFm96vqWQRw7hRfHcSAMcRQscyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S396" t="inlineStr"/>
-      <c r="T396" t="inlineStr"/>
+      <c r="S396" t="n">
+        <v>10.9490618</v>
+      </c>
+      <c r="T396" t="n">
+        <v>77.1136973</v>
+      </c>
     </row>
     <row r="397">
       <c r="A397" t="n">
@@ -24853,8 +26313,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/10%25C2%25B055%2735.8%2522N%2B77%25C2%25B001%2717.9%2522E/%4010.9266181,77.0190597,655m/data%3D!3m2!1e3!4b1!4m4!3m3!8m2!3d10.9266181!4d77.0216346%3Fentry%3Dtts%26g_ep%3DEgoyMDI2MDIxMS4wIPu8ASoASAFQAw%253D%253D%26skid%3D6d2bfd50-e3be-4ef1-9e6b-27f45105663a&amp;q=EhAkBQIB4C7guzR74cqdAFF6GI_Ry88GIjA0CFYFjd-vkF6Ny7NE4PiKbpM5Hj7Zue1lDkCbNP0qp-uYBam4GUWd1niB1WOtvlIyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S397" t="inlineStr"/>
-      <c r="T397" t="inlineStr"/>
+      <c r="S397" t="n">
+        <v>10.9266181</v>
+      </c>
+      <c r="T397" t="n">
+        <v>77.0190597</v>
+      </c>
     </row>
     <row r="398">
       <c r="A398" t="n">
@@ -24897,8 +26361,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/10%25C2%25B044%2720.6%2522N%2B76%25C2%25B056%2752.9%2522E/%4010.7390667,76.9454518,655m/data%3D!3m2!1e3!4b1!4m4!3m3!8m2!3d10.7390667!4d76.9480267%3Fentry%3Dtts%26g_ep%3DEgoyMDI2MDIxMS4wIPu8ASoASAFQAw%253D%253D%26skid%3Db993366b-e45a-4f04-9bad-42f5c9c232bc&amp;q=EhAkBQIB4C7guzR74cqdAFF6GJHRy88GIjC0lsDIOqo_Qz8Mc1AUX6OsVvSa6TTI9qiJVxPh4vt7-oo50kNS6WBD2z6I9w_f9UYyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S398" t="inlineStr"/>
-      <c r="T398" t="inlineStr"/>
+      <c r="S398" t="n">
+        <v>10.7390667</v>
+      </c>
+      <c r="T398" t="n">
+        <v>76.9454518</v>
+      </c>
     </row>
     <row r="399">
       <c r="A399" t="n">
@@ -24941,8 +26409,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/10%25C2%25B044%2721.4%2522N%2B76%25C2%25B057%2713.9%2522E/%4010.7392664,76.9512825,655m/data%3D!3m2!1e3!4b1!4m4!3m3!8m2!3d10.7392664!4d76.9538574%3Fentry%3Dtts%26g_ep%3DEgoyMDI2MDIxMS4wIPu8ASoASAFQAw%253D%253D%26skid%3D036ab3bb-77c9-4c41-8e17-04b28299e0d7&amp;q=EhAkBQIB4C7guzR74cqdAFF6GJLRy88GIjCOg99b6kr_iQcJQhBpJO_9GP_L195JAGoRDj3XfKqwSc4CXjMWLUvPUlepOolo04kyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S399" t="inlineStr"/>
-      <c r="T399" t="inlineStr"/>
+      <c r="S399" t="n">
+        <v>10.7392664</v>
+      </c>
+      <c r="T399" t="n">
+        <v>76.9512825</v>
+      </c>
     </row>
     <row r="400">
       <c r="A400" t="n">
@@ -25033,8 +26505,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/10%25C2%25B039%2726.3%2522N%2B77%25C2%25B002%2740.7%2522E/%4010.6573019,77.0420647,655m/data%3D!3m2!1e3!4b1!4m4!3m3!8m2!3d10.6573019!4d77.0446396%3Fentry%3Dtts%26g_ep%3DEgoyMDI2MDIxMS4wIPu8ASoASAFQAw%253D%253D%26skid%3D9a28ff91-d64e-4ad9-8276-9e2a39314c75&amp;q=EhAkBQIB4C7guzR74cqdAFF6GJTRy88GIjBr3PA1nVvRgJ01j3LyB3jh_mC0myVJG9dQl8PlB81Sh2zCmT6SSvGsgBIjDKuKb5MyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S401" t="inlineStr"/>
-      <c r="T401" t="inlineStr"/>
+      <c r="S401" t="n">
+        <v>10.6573019</v>
+      </c>
+      <c r="T401" t="n">
+        <v>77.0420647</v>
+      </c>
     </row>
     <row r="402">
       <c r="A402" t="n">
@@ -25077,8 +26553,12 @@
           <t>https://www.google.com/sorry/index?continue=https://www.google.com/maps/place/11.028515,77.066708/data%3D!4m6!3m5!1s0!7e2!8m2!3d11.0285154!4d77.06670799999999!17m2!4m1!1e3!18m1!1e1%3Futm_source%3Dmstt_1%26entry%3Dgps%26coh%3D192189%26g_ep%3DCAESBjI2LjYuMRgAIPrsDSqKASw5NDI2NzcyNyw5NDI5MjE5NSw5NDI5OTUzMiwxMDA3OTY0OTgsMTAwNzk2NTMxLDk0Mjg0NDcyLDk0MjgwNTc2LDk0MjA3Mzk0LDk0MjA3NTA2LDk0MjA4NTA2LDk0MjE4NjUzLDk0MjI5ODM5LDk0Mjc1MTY4LDk0Mjc5NjE5LDEwMDc5MTQ3OUICSU4%253D%26skid%3D599ba7dc-cc59-47c8-b1e2-fef5381ac519%26g_st%3Daw&amp;q=EhAkBQIB4C7guzR74cqdAFF6GJfRy88GIjDxbGFUWeDrBlOaDwQPneiZH6SlP1_9Rsb3hjLmdgzZXx4_W40r99eYi94RaWIqF5oyAnJSWgFD</t>
         </is>
       </c>
-      <c r="S402" t="inlineStr"/>
-      <c r="T402" t="inlineStr"/>
+      <c r="S402" t="n">
+        <v>11.0285154</v>
+      </c>
+      <c r="T402" t="n">
+        <v>77.06670799999999</v>
+      </c>
     </row>
     <row r="403">
       <c r="A403" t="n">
